--- a/Solid State PLC.xlsx
+++ b/Solid State PLC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b4a63f789af4ef06/Documents/Career/Career Development/Financial Statements/3 Statement Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{C42BB4A9-2FB9-4DC3-8217-8A7070EACCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE4C7227-7375-42E0-8E93-EA5511D2B8BB}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{C42BB4A9-2FB9-4DC3-8217-8A7070EACCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9076EA1F-F59C-4259-A7F3-92765EB9EF91}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{C4FDF26E-8D02-42E6-9BA6-E8E4AB263931}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{C4FDF26E-8D02-42E6-9BA6-E8E4AB263931}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -66,10 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="323">
-  <si>
-    <t>Modelled by Peter Hopkinson</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="322">
   <si>
     <t>Financial Statements - Income Statement</t>
   </si>
@@ -2236,6 +2233,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2583,12 +2584,7 @@
   <sheetData>
     <row r="2" spans="2:2" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>0</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
@@ -2631,7 +2627,7 @@
     <row r="3" spans="1:12" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="48"/>
       <c r="B3" s="52" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C3" s="53"/>
       <c r="D3" s="51"/>
@@ -2668,7 +2664,7 @@
       <c r="D5" s="55"/>
       <c r="E5" s="55"/>
       <c r="F5" s="56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5" s="56"/>
       <c r="H5" s="56"/>
@@ -2714,13 +2710,13 @@
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="48"/>
       <c r="B7" s="59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" s="59"/>
       <c r="D7" s="59"/>
       <c r="E7" s="59"/>
       <c r="F7" s="60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7" s="60"/>
       <c r="H7" s="61"/>
@@ -2728,7 +2724,7 @@
       <c r="J7" s="61"/>
       <c r="K7" s="61"/>
       <c r="L7" s="292" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -2745,7 +2741,7 @@
     </row>
     <row r="9" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B9" s="124" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C9" s="41"/>
       <c r="D9" s="264"/>
@@ -2773,7 +2769,7 @@
     </row>
     <row r="12" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B12" s="284" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C12" s="285"/>
       <c r="D12" s="285"/>
@@ -2801,13 +2797,13 @@
     </row>
     <row r="14" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B14" s="371" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C14" s="65"/>
       <c r="D14" s="65"/>
       <c r="E14" s="65"/>
       <c r="F14" s="288" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G14" s="240"/>
       <c r="H14" s="289">
@@ -2837,7 +2833,7 @@
       <c r="D15" s="200"/>
       <c r="E15" s="240"/>
       <c r="F15" s="136" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G15" s="200"/>
       <c r="H15" s="239">
@@ -2862,7 +2858,7 @@
       <c r="D16" s="65"/>
       <c r="E16" s="268"/>
       <c r="F16" s="136" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G16" s="269"/>
       <c r="H16" s="239">
@@ -2887,7 +2883,7 @@
       <c r="D17" s="65"/>
       <c r="E17" s="268"/>
       <c r="F17" s="136" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G17" s="269"/>
       <c r="H17" s="239">
@@ -2921,13 +2917,13 @@
     </row>
     <row r="19" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B19" s="371" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C19" s="65"/>
       <c r="D19" s="65"/>
       <c r="E19" s="65"/>
       <c r="F19" s="288" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G19" s="240"/>
       <c r="H19" s="289">
@@ -2957,7 +2953,7 @@
       <c r="D20" s="200"/>
       <c r="E20" s="240"/>
       <c r="F20" s="136" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G20" s="200"/>
       <c r="H20" s="239">
@@ -2982,7 +2978,7 @@
       <c r="D21" s="65"/>
       <c r="E21" s="268"/>
       <c r="F21" s="136" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G21" s="269"/>
       <c r="H21" s="239">
@@ -3007,7 +3003,7 @@
       <c r="D22" s="65"/>
       <c r="E22" s="268"/>
       <c r="F22" s="136" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G22" s="269"/>
       <c r="H22" s="239">
@@ -3041,13 +3037,13 @@
     </row>
     <row r="24" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B24" s="371" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C24" s="65"/>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="288" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G24" s="240"/>
       <c r="H24" s="289">
@@ -3077,7 +3073,7 @@
       <c r="D25" s="200"/>
       <c r="E25" s="240"/>
       <c r="F25" s="136" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G25" s="200"/>
       <c r="H25" s="239">
@@ -3102,7 +3098,7 @@
       <c r="D26" s="65"/>
       <c r="E26" s="268"/>
       <c r="F26" s="136" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G26" s="269"/>
       <c r="H26" s="239">
@@ -3127,7 +3123,7 @@
       <c r="D27" s="65"/>
       <c r="E27" s="268"/>
       <c r="F27" s="136" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G27" s="269"/>
       <c r="H27" s="239">
@@ -3174,7 +3170,7 @@
     </row>
     <row r="30" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B30" s="284" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C30" s="285"/>
       <c r="D30" s="285"/>
@@ -3215,13 +3211,13 @@
     </row>
     <row r="33" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B33" s="371" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C33" s="65"/>
       <c r="D33" s="65"/>
       <c r="E33" s="268"/>
       <c r="F33" s="288" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G33" s="269"/>
       <c r="H33" s="289">
@@ -3251,7 +3247,7 @@
       <c r="D34" s="65"/>
       <c r="E34" s="268"/>
       <c r="F34" s="136" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G34" s="269"/>
       <c r="H34" s="395">
@@ -3276,7 +3272,7 @@
       <c r="D35" s="65"/>
       <c r="E35" s="65"/>
       <c r="F35" s="136" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G35" s="200"/>
       <c r="H35" s="395">
@@ -3301,7 +3297,7 @@
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="136" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G36" s="200"/>
       <c r="H36" s="395">
@@ -3335,13 +3331,13 @@
     </row>
     <row r="38" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B38" s="371" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C38" s="65"/>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
       <c r="F38" s="288" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G38" s="273"/>
       <c r="H38" s="289">
@@ -3371,7 +3367,7 @@
       <c r="D39" s="65"/>
       <c r="E39" s="65"/>
       <c r="F39" s="136" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G39" s="274"/>
       <c r="H39" s="179">
@@ -3396,7 +3392,7 @@
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
       <c r="F40" s="136" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G40" s="276"/>
       <c r="H40" s="179">
@@ -3421,7 +3417,7 @@
       <c r="D41" s="65"/>
       <c r="E41" s="65"/>
       <c r="F41" s="136" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G41" s="277"/>
       <c r="H41" s="179">
@@ -3453,13 +3449,13 @@
     </row>
     <row r="43" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B43" s="371" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C43" s="65"/>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="288" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G43" s="273"/>
       <c r="H43" s="289">
@@ -3489,7 +3485,7 @@
       <c r="D44" s="65"/>
       <c r="E44" s="65"/>
       <c r="F44" s="136" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G44" s="274"/>
       <c r="H44" s="395">
@@ -3514,7 +3510,7 @@
       <c r="D45" s="65"/>
       <c r="E45" s="65"/>
       <c r="F45" s="136" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G45" s="276"/>
       <c r="H45" s="395">
@@ -3539,7 +3535,7 @@
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
       <c r="F46" s="136" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G46" s="277"/>
       <c r="H46" s="395">
@@ -3571,13 +3567,13 @@
     </row>
     <row r="48" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B48" s="371" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C48" s="65"/>
       <c r="D48" s="65"/>
       <c r="E48" s="65"/>
       <c r="F48" s="288" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G48" s="273"/>
       <c r="H48" s="289">
@@ -3607,7 +3603,7 @@
       <c r="D49" s="65"/>
       <c r="E49" s="65"/>
       <c r="F49" s="136" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G49" s="274"/>
       <c r="H49" s="179">
@@ -3632,7 +3628,7 @@
       <c r="D50" s="65"/>
       <c r="E50" s="65"/>
       <c r="F50" s="136" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G50" s="276"/>
       <c r="H50" s="179">
@@ -3657,7 +3653,7 @@
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="136" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G51" s="277"/>
       <c r="H51" s="179">
@@ -4268,7 +4264,7 @@
     <row r="4" spans="1:16" ht="21" x14ac:dyDescent="0.5">
       <c r="A4" s="48"/>
       <c r="B4" s="52" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="53"/>
       <c r="D4" s="51"/>
@@ -4305,7 +4301,7 @@
       <c r="D6" s="55"/>
       <c r="E6" s="55"/>
       <c r="F6" s="56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6" s="56"/>
       <c r="H6" s="56"/>
@@ -4350,13 +4346,13 @@
     <row r="8" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="48"/>
       <c r="B8" s="59" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="59"/>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="60"/>
       <c r="H8" s="61"/>
@@ -4364,7 +4360,7 @@
       <c r="J8" s="61"/>
       <c r="K8" s="61"/>
       <c r="L8" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
@@ -4384,7 +4380,7 @@
     <row r="10" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A10" s="48"/>
       <c r="B10" s="64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="64"/>
       <c r="D10" s="65"/>
@@ -4419,7 +4415,7 @@
     <row r="11" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="48"/>
       <c r="B11" s="68" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="68"/>
       <c r="D11" s="68"/>
@@ -4454,7 +4450,7 @@
     <row r="12" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A12" s="48"/>
       <c r="B12" s="70" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" s="70"/>
       <c r="D12" s="70"/>
@@ -4493,7 +4489,7 @@
     <row r="13" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A13" s="48"/>
       <c r="B13" s="65" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" s="65"/>
       <c r="D13" s="70"/>
@@ -4544,7 +4540,7 @@
     <row r="15" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="48"/>
       <c r="B15" s="72" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C15" s="73"/>
       <c r="D15" s="73"/>
@@ -4579,7 +4575,7 @@
     <row r="16" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A16" s="48"/>
       <c r="B16" s="70" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" s="70"/>
       <c r="D16" s="70"/>
@@ -4616,7 +4612,7 @@
     <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A17" s="48"/>
       <c r="B17" s="65" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C17" s="70"/>
       <c r="D17" s="70"/>
@@ -4667,7 +4663,7 @@
     <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A19" s="48"/>
       <c r="B19" s="65" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C19" s="65"/>
       <c r="D19" s="70"/>
@@ -4698,7 +4694,7 @@
     <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A20" s="48"/>
       <c r="B20" s="65" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C20" s="65"/>
       <c r="D20" s="70"/>
@@ -4729,7 +4725,7 @@
     <row r="21" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A21" s="48"/>
       <c r="B21" s="74" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C21" s="74"/>
       <c r="D21" s="74"/>
@@ -4760,7 +4756,7 @@
     <row r="22" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="48"/>
       <c r="B22" s="233" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C22" s="233"/>
       <c r="D22" s="233"/>
@@ -4791,7 +4787,7 @@
     <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A23" s="48"/>
       <c r="B23" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="70"/>
       <c r="D23" s="70"/>
@@ -4828,7 +4824,7 @@
     <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A24" s="48"/>
       <c r="B24" s="65" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C24" s="70"/>
       <c r="D24" s="70"/>
@@ -4879,7 +4875,7 @@
     <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A26" s="48"/>
       <c r="B26" s="74" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" s="74"/>
       <c r="D26" s="78"/>
@@ -4914,7 +4910,7 @@
     <row r="27" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A27" s="48"/>
       <c r="B27" s="79" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" s="79"/>
       <c r="D27" s="79"/>
@@ -4965,7 +4961,7 @@
     <row r="29" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A29" s="48"/>
       <c r="B29" s="70" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C29" s="70"/>
       <c r="D29" s="70"/>
@@ -5016,7 +5012,7 @@
     <row r="31" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="48"/>
       <c r="B31" s="72" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C31" s="72"/>
       <c r="D31" s="72"/>
@@ -5051,7 +5047,7 @@
     <row r="32" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A32" s="48"/>
       <c r="B32" s="70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" s="70"/>
       <c r="D32" s="65"/>
@@ -5088,7 +5084,7 @@
     <row r="33" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A33" s="48"/>
       <c r="B33" s="65" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C33" s="65"/>
       <c r="D33" s="65"/>
@@ -5139,7 +5135,7 @@
     <row r="35" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="48"/>
       <c r="B35" s="73" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" s="73"/>
       <c r="D35" s="72"/>
@@ -5155,11 +5151,11 @@
     <row r="36" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A36" s="48"/>
       <c r="B36" s="65" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" s="65"/>
       <c r="D36" s="65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E36" s="65"/>
       <c r="F36" s="300">
@@ -5206,7 +5202,7 @@
     <row r="38" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A38" s="48"/>
       <c r="B38" s="70" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C38" s="65"/>
       <c r="D38" s="291">
@@ -5283,7 +5279,7 @@
     <row r="43" spans="1:12" ht="21" x14ac:dyDescent="0.5">
       <c r="A43" s="48"/>
       <c r="B43" s="52" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C43" s="53"/>
       <c r="D43" s="51"/>
@@ -5320,7 +5316,7 @@
       <c r="D45" s="55"/>
       <c r="E45" s="55"/>
       <c r="F45" s="56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G45" s="56"/>
       <c r="H45" s="56"/>
@@ -5365,13 +5361,13 @@
     <row r="47" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="48"/>
       <c r="B47" s="59" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C47" s="59"/>
       <c r="D47" s="59"/>
       <c r="E47" s="59"/>
       <c r="F47" s="60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G47" s="60"/>
       <c r="H47" s="61"/>
@@ -5379,7 +5375,7 @@
       <c r="J47" s="61"/>
       <c r="K47" s="61"/>
       <c r="L47" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
@@ -5399,7 +5395,7 @@
     <row r="49" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A49" s="48"/>
       <c r="B49" s="85" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49" s="86"/>
       <c r="D49" s="87"/>
@@ -5429,7 +5425,7 @@
     <row r="51" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A51" s="48"/>
       <c r="B51" s="129" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C51" s="65"/>
       <c r="D51" s="65"/>
@@ -5464,7 +5460,7 @@
     <row r="52" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A52" s="48"/>
       <c r="B52" s="129" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C52" s="65"/>
       <c r="D52" s="65"/>
@@ -5499,7 +5495,7 @@
     <row r="53" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A53" s="48"/>
       <c r="B53" s="129" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C53" s="65"/>
       <c r="D53" s="65"/>
@@ -5534,7 +5530,7 @@
     <row r="54" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A54" s="48"/>
       <c r="B54" s="130" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C54" s="126"/>
       <c r="D54" s="126"/>
@@ -5569,7 +5565,7 @@
     <row r="55" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A55" s="48"/>
       <c r="B55" s="65" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C55" s="65"/>
       <c r="D55" s="65"/>
@@ -5606,7 +5602,7 @@
     <row r="56" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A56" s="48"/>
       <c r="B56" s="65" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C56" s="65"/>
       <c r="D56" s="65"/>
@@ -5624,7 +5620,7 @@
     <row r="57" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A57" s="48"/>
       <c r="B57" s="126" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C57" s="126"/>
       <c r="D57" s="126"/>
@@ -5640,7 +5636,7 @@
     <row r="58" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A58" s="48"/>
       <c r="B58" s="65" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C58" s="65"/>
       <c r="D58" s="65"/>
@@ -5675,7 +5671,7 @@
     <row r="59" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A59" s="48"/>
       <c r="B59" s="65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C59" s="65"/>
       <c r="D59" s="65"/>
@@ -5710,7 +5706,7 @@
     <row r="60" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A60" s="48"/>
       <c r="B60" s="65" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C60" s="65"/>
       <c r="D60" s="65"/>
@@ -5745,7 +5741,7 @@
     <row r="61" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="48"/>
       <c r="B61" s="72" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C61" s="72"/>
       <c r="D61" s="72"/>
@@ -5780,7 +5776,7 @@
     <row r="62" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A62" s="48"/>
       <c r="B62" s="70" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C62" s="70"/>
       <c r="D62" s="65"/>
@@ -5831,7 +5827,7 @@
     <row r="64" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A64" s="48"/>
       <c r="B64" s="95" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C64" s="86"/>
       <c r="D64" s="87"/>
@@ -5861,7 +5857,7 @@
     <row r="66" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A66" s="48"/>
       <c r="B66" s="129" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C66" s="65"/>
       <c r="D66" s="65"/>
@@ -5896,7 +5892,7 @@
     <row r="67" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A67" s="48"/>
       <c r="B67" s="129" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C67" s="65"/>
       <c r="D67" s="65"/>
@@ -5931,7 +5927,7 @@
     <row r="68" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A68" s="48"/>
       <c r="B68" s="129" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C68" s="65"/>
       <c r="D68" s="65"/>
@@ -5966,7 +5962,7 @@
     <row r="69" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A69" s="48"/>
       <c r="B69" s="129" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C69" s="65"/>
       <c r="D69" s="65"/>
@@ -6001,7 +5997,7 @@
     <row r="70" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A70" s="48"/>
       <c r="B70" s="129" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C70" s="65"/>
       <c r="D70" s="65"/>
@@ -6036,7 +6032,7 @@
     <row r="71" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A71" s="48"/>
       <c r="B71" s="129" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C71" s="65"/>
       <c r="D71" s="65"/>
@@ -6071,7 +6067,7 @@
     <row r="72" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A72" s="48"/>
       <c r="B72" s="132" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C72" s="131"/>
       <c r="D72" s="132"/>
@@ -6108,7 +6104,7 @@
     <row r="73" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A73" s="48"/>
       <c r="B73" s="129" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C73" s="70"/>
       <c r="D73" s="65"/>
@@ -6128,7 +6124,7 @@
     <row r="74" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A74" s="48"/>
       <c r="B74" s="130" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C74" s="130"/>
       <c r="D74" s="130"/>
@@ -6163,7 +6159,7 @@
     <row r="75" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A75" s="48"/>
       <c r="B75" s="65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C75" s="65"/>
       <c r="D75" s="65"/>
@@ -6200,7 +6196,7 @@
     <row r="76" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A76" s="48"/>
       <c r="B76" s="65" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C76" s="65"/>
       <c r="D76" s="65"/>
@@ -6235,7 +6231,7 @@
     <row r="77" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A77" s="48"/>
       <c r="B77" s="65" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C77" s="65"/>
       <c r="D77" s="65"/>
@@ -6270,7 +6266,7 @@
     <row r="78" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A78" s="48"/>
       <c r="B78" s="65" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C78" s="65"/>
       <c r="D78" s="65"/>
@@ -6305,7 +6301,7 @@
     <row r="79" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A79" s="48"/>
       <c r="B79" s="65" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C79" s="65"/>
       <c r="D79" s="65"/>
@@ -6340,7 +6336,7 @@
     <row r="80" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A80" s="48"/>
       <c r="B80" s="132" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C80" s="132"/>
       <c r="D80" s="132"/>
@@ -6377,7 +6373,7 @@
     <row r="81" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A81" s="48"/>
       <c r="B81" s="65" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C81" s="65"/>
       <c r="D81" s="65"/>
@@ -6412,7 +6408,7 @@
     <row r="82" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A82" s="48"/>
       <c r="B82" s="65" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C82" s="65"/>
       <c r="D82" s="65"/>
@@ -6447,7 +6443,7 @@
     <row r="83" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A83" s="48"/>
       <c r="B83" s="65" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C83" s="65"/>
       <c r="D83" s="65"/>
@@ -6482,7 +6478,7 @@
     <row r="84" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A84" s="48"/>
       <c r="B84" s="65" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C84" s="65"/>
       <c r="D84" s="65"/>
@@ -6517,7 +6513,7 @@
     <row r="85" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A85" s="48"/>
       <c r="B85" s="65" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C85" s="65"/>
       <c r="D85" s="65"/>
@@ -6552,7 +6548,7 @@
     <row r="86" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="48"/>
       <c r="B86" s="93" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C86" s="93"/>
       <c r="D86" s="93"/>
@@ -6587,7 +6583,7 @@
     <row r="87" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A87" s="48"/>
       <c r="B87" s="70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C87" s="70"/>
       <c r="D87" s="65"/>
@@ -6624,7 +6620,7 @@
     <row r="88" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A88" s="48"/>
       <c r="B88" s="65" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C88" s="65"/>
       <c r="D88" s="65"/>
@@ -6675,7 +6671,7 @@
     <row r="90" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A90" s="48"/>
       <c r="B90" s="65" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C90" s="65"/>
       <c r="D90" s="65"/>
@@ -6764,7 +6760,7 @@
     <row r="96" spans="1:12" ht="21" x14ac:dyDescent="0.5">
       <c r="A96" s="48"/>
       <c r="B96" s="52" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C96" s="53"/>
       <c r="D96" s="51"/>
@@ -6801,7 +6797,7 @@
       <c r="D98" s="55"/>
       <c r="E98" s="55"/>
       <c r="F98" s="56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G98" s="56"/>
       <c r="H98" s="56"/>
@@ -6847,13 +6843,13 @@
     <row r="100" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="48"/>
       <c r="B100" s="59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C100" s="59"/>
       <c r="D100" s="59"/>
       <c r="E100" s="59"/>
       <c r="F100" s="60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G100" s="60"/>
       <c r="H100" s="61"/>
@@ -6861,7 +6857,7 @@
       <c r="J100" s="61"/>
       <c r="K100" s="61"/>
       <c r="L100" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="101" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
@@ -6881,7 +6877,7 @@
     <row r="102" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A102" s="48"/>
       <c r="B102" s="85" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C102" s="86"/>
       <c r="D102" s="87"/>
@@ -6911,7 +6907,7 @@
     <row r="104" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A104" s="48"/>
       <c r="B104" s="65" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C104" s="65"/>
       <c r="D104" s="65"/>
@@ -6942,7 +6938,7 @@
     <row r="105" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A105" s="48"/>
       <c r="B105" s="134" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C105" s="132"/>
       <c r="D105" s="132"/>
@@ -6973,7 +6969,7 @@
     <row r="106" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A106" s="48"/>
       <c r="B106" s="129" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C106" s="65"/>
       <c r="D106" s="65"/>
@@ -7004,7 +7000,7 @@
     <row r="107" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A107" s="48"/>
       <c r="B107" s="129" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C107" s="65"/>
       <c r="D107" s="65"/>
@@ -7035,7 +7031,7 @@
     <row r="108" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A108" s="48"/>
       <c r="B108" s="254" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C108" s="132"/>
       <c r="D108" s="132"/>
@@ -7066,7 +7062,7 @@
     <row r="109" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A109" s="48"/>
       <c r="B109" s="134" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C109" s="132"/>
       <c r="D109" s="132"/>
@@ -7097,7 +7093,7 @@
     <row r="110" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A110" s="48"/>
       <c r="B110" s="389" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C110" s="65"/>
       <c r="D110" s="65"/>
@@ -7128,7 +7124,7 @@
     <row r="111" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A111" s="48"/>
       <c r="B111" s="389" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C111" s="65"/>
       <c r="D111" s="65"/>
@@ -7159,7 +7155,7 @@
     <row r="112" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="48"/>
       <c r="B112" s="230" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C112" s="230"/>
       <c r="D112" s="230"/>
@@ -7175,7 +7171,7 @@
     <row r="113" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A113" s="48"/>
       <c r="B113" s="70" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C113" s="70"/>
       <c r="D113" s="70"/>
@@ -7220,7 +7216,7 @@
     <row r="115" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A115" s="48"/>
       <c r="B115" s="85" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C115" s="86"/>
       <c r="D115" s="87"/>
@@ -7250,7 +7246,7 @@
     <row r="117" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A117" s="48"/>
       <c r="B117" s="65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C117" s="65"/>
       <c r="D117" s="65"/>
@@ -7281,7 +7277,7 @@
     <row r="118" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="48"/>
       <c r="B118" s="72" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C118" s="72"/>
       <c r="D118" s="72"/>
@@ -7312,7 +7308,7 @@
     <row r="119" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A119" s="48"/>
       <c r="B119" s="70" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C119" s="70"/>
       <c r="D119" s="70"/>
@@ -7357,7 +7353,7 @@
     <row r="121" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A121" s="48"/>
       <c r="B121" s="85" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C121" s="86"/>
       <c r="D121" s="87"/>
@@ -7387,7 +7383,7 @@
     <row r="123" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A123" s="48"/>
       <c r="B123" s="65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C123" s="65"/>
       <c r="D123" s="65"/>
@@ -7418,7 +7414,7 @@
     <row r="124" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A124" s="48"/>
       <c r="B124" s="65" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C124" s="65"/>
       <c r="D124" s="65"/>
@@ -7449,7 +7445,7 @@
     <row r="125" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A125" s="48"/>
       <c r="B125" s="65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C125" s="65"/>
       <c r="D125" s="65"/>
@@ -7480,7 +7476,7 @@
     <row r="126" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A126" s="48"/>
       <c r="B126" s="65" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C126" s="65"/>
       <c r="D126" s="65"/>
@@ -7511,7 +7507,7 @@
     <row r="127" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="48"/>
       <c r="B127" s="72" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C127" s="72"/>
       <c r="D127" s="72"/>
@@ -7542,7 +7538,7 @@
     <row r="128" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A128" s="48"/>
       <c r="B128" s="70" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C128" s="70"/>
       <c r="D128" s="70"/>
@@ -7587,7 +7583,7 @@
     <row r="130" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A130" s="48"/>
       <c r="B130" s="74" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C130" s="74"/>
       <c r="D130" s="74"/>
@@ -7618,7 +7614,7 @@
     <row r="131" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A131" s="48"/>
       <c r="B131" s="65" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C131" s="65"/>
       <c r="D131" s="65"/>
@@ -7649,7 +7645,7 @@
     <row r="132" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A132" s="48"/>
       <c r="B132" s="156" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C132" s="156"/>
       <c r="D132" s="156"/>
@@ -7753,7 +7749,7 @@
     <row r="138" spans="1:12" ht="21" x14ac:dyDescent="0.5">
       <c r="A138" s="48"/>
       <c r="B138" s="52" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C138" s="53"/>
       <c r="D138" s="51"/>
@@ -7800,13 +7796,13 @@
     <row r="142" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="48"/>
       <c r="B142" s="59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C142" s="59"/>
       <c r="D142" s="59"/>
       <c r="E142" s="59"/>
       <c r="F142" s="60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G142" s="60"/>
       <c r="H142" s="61"/>
@@ -7814,7 +7810,7 @@
       <c r="J142" s="61"/>
       <c r="K142" s="61"/>
       <c r="L142" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="143" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
@@ -7834,7 +7830,7 @@
     <row r="144" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A144" s="48"/>
       <c r="B144" s="85" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C144" s="86"/>
       <c r="D144" s="87"/>
@@ -7864,7 +7860,7 @@
     <row r="146" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A146" s="48"/>
       <c r="B146" s="65" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C146" s="65"/>
       <c r="D146" s="65"/>
@@ -7898,7 +7894,7 @@
     <row r="147" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A147" s="48"/>
       <c r="B147" s="65" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C147" s="65"/>
       <c r="D147" s="65"/>
@@ -7935,7 +7931,7 @@
     <row r="148" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A148" s="48"/>
       <c r="B148" s="65" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C148" s="65"/>
       <c r="D148" s="65"/>
@@ -7972,7 +7968,7 @@
     <row r="149" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A149" s="48"/>
       <c r="B149" s="65" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C149" s="65"/>
       <c r="D149" s="65"/>
@@ -8010,7 +8006,7 @@
     <row r="150" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A150" s="48"/>
       <c r="B150" s="65" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C150" s="65"/>
       <c r="D150" s="65"/>
@@ -8061,7 +8057,7 @@
     <row r="152" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A152" s="48"/>
       <c r="B152" s="85" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C152" s="86"/>
       <c r="D152" s="87"/>
@@ -8091,81 +8087,81 @@
     <row r="154" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A154" s="48"/>
       <c r="B154" s="65" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C154" s="65"/>
       <c r="D154" s="65"/>
       <c r="E154" s="65"/>
       <c r="F154" s="259">
-        <f>F16/ABS(F26)</f>
+        <f t="shared" ref="F154:L154" si="83">F16/ABS(F26)</f>
         <v>1.3155818540433926</v>
       </c>
       <c r="G154" s="259">
-        <f>G16/ABS(G26)</f>
+        <f t="shared" si="83"/>
         <v>6.3039927404718696</v>
       </c>
       <c r="H154" s="259">
-        <f>H16/ABS(H26)</f>
+        <f t="shared" si="83"/>
         <v>8.1867606916077698</v>
       </c>
       <c r="I154" s="259">
-        <f>I16/ABS(I26)</f>
+        <f t="shared" si="83"/>
         <v>3.3534307942054054</v>
       </c>
       <c r="J154" s="259">
-        <f>J16/ABS(J26)</f>
+        <f t="shared" si="83"/>
         <v>0.10790514646067864</v>
       </c>
       <c r="K154" s="259">
-        <f>K16/ABS(K26)</f>
+        <f t="shared" si="83"/>
         <v>-1.2695115858589514</v>
       </c>
       <c r="L154" s="259">
-        <f>L16/ABS(L26)</f>
+        <f t="shared" si="83"/>
         <v>-2.0205279774246727</v>
       </c>
     </row>
     <row r="155" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A155" s="48"/>
       <c r="B155" s="65" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C155" s="65"/>
       <c r="D155" s="65"/>
       <c r="E155" s="65"/>
       <c r="F155" s="260" t="str">
-        <f>IF(F507=0, "N/A", ABS(F23/F507))</f>
+        <f t="shared" ref="F155:L155" si="84">IF(F507=0, "N/A", ABS(F23/F507))</f>
         <v>N/A</v>
       </c>
       <c r="G155" s="260" t="str">
-        <f>IF(G507=0, "N/A", ABS(G23/G507))</f>
+        <f t="shared" si="84"/>
         <v>N/A</v>
       </c>
       <c r="H155" s="260">
-        <f>IF(H507=0, "N/A", ABS(H23/H507))</f>
+        <f t="shared" si="84"/>
         <v>14.913846495543153</v>
       </c>
       <c r="I155" s="260">
-        <f>IF(I507=0, "N/A", ABS(I23/I507))</f>
+        <f t="shared" si="84"/>
         <v>29.612900034348847</v>
       </c>
       <c r="J155" s="260">
-        <f>IF(J507=0, "N/A", ABS(J23/J507))</f>
+        <f t="shared" si="84"/>
         <v>25.250733338164736</v>
       </c>
       <c r="K155" s="260">
-        <f>IF(K507=0, "N/A", ABS(K23/K507))</f>
+        <f t="shared" si="84"/>
         <v>10.77113606976663</v>
       </c>
       <c r="L155" s="260">
-        <f>IF(L507=0, "N/A", ABS(L23/L507))</f>
+        <f t="shared" si="84"/>
         <v>5.9661128868484932</v>
       </c>
     </row>
     <row r="156" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A156" s="48"/>
       <c r="B156" s="65" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C156" s="65"/>
       <c r="D156" s="65"/>
@@ -8210,7 +8206,7 @@
     <row r="158" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A158" s="48"/>
       <c r="B158" s="85" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C158" s="86"/>
       <c r="D158" s="87"/>
@@ -8240,7 +8236,7 @@
     <row r="160" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A160" s="48"/>
       <c r="B160" s="65" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C160" s="65"/>
       <c r="D160" s="65"/>
@@ -8285,7 +8281,7 @@
     <row r="162" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A162" s="48"/>
       <c r="B162" s="85" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C162" s="86"/>
       <c r="D162" s="87"/>
@@ -8315,111 +8311,111 @@
     <row r="164" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A164" s="48"/>
       <c r="B164" s="65" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C164" s="70"/>
       <c r="D164" s="65"/>
       <c r="E164" s="65"/>
       <c r="F164" s="151">
-        <f>F55/ABS(F72)</f>
+        <f t="shared" ref="F164:L164" si="85">F55/ABS(F72)</f>
         <v>2.1856126100768023</v>
       </c>
       <c r="G164" s="151">
-        <f>G55/ABS(G72)</f>
+        <f t="shared" si="85"/>
         <v>2.2903077100380318</v>
       </c>
       <c r="H164" s="151">
-        <f>H55/ABS(H72)</f>
+        <f t="shared" si="85"/>
         <v>2.1613270518242089</v>
       </c>
       <c r="I164" s="151">
-        <f>I55/ABS(I72)</f>
+        <f t="shared" si="85"/>
         <v>2.091539652248795</v>
       </c>
       <c r="J164" s="151">
-        <f>J55/ABS(J72)</f>
+        <f t="shared" si="85"/>
         <v>2.1154781886380443</v>
       </c>
       <c r="K164" s="151">
-        <f>K55/ABS(K72)</f>
+        <f t="shared" si="85"/>
         <v>2.1374291460832522</v>
       </c>
       <c r="L164" s="151">
-        <f>L55/ABS(L72)</f>
+        <f t="shared" si="85"/>
         <v>2.1529754766239533</v>
       </c>
     </row>
     <row r="165" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A165" s="48"/>
       <c r="B165" s="65" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C165" s="70"/>
       <c r="D165" s="65"/>
       <c r="E165" s="65"/>
       <c r="F165" s="151">
-        <f>(F55-F51)/ABS(F72)</f>
+        <f t="shared" ref="F165:L165" si="86">(F55-F51)/ABS(F72)</f>
         <v>1.050102537295428</v>
       </c>
       <c r="G165" s="151">
-        <f>(G55-G51)/ABS(G72)</f>
+        <f t="shared" si="86"/>
         <v>1.1185509584725903</v>
       </c>
       <c r="H165" s="151">
-        <f>(H55-H51)/ABS(H72)</f>
+        <f t="shared" si="86"/>
         <v>1.0009696055174822</v>
       </c>
       <c r="I165" s="151">
-        <f>(I55-I51)/ABS(I72)</f>
+        <f t="shared" si="86"/>
         <v>0.89960816767445739</v>
       </c>
       <c r="J165" s="151">
-        <f>(J55-J51)/ABS(J72)</f>
+        <f t="shared" si="86"/>
         <v>0.91090478997089175</v>
       </c>
       <c r="K165" s="151">
-        <f>(K55-K51)/ABS(K72)</f>
+        <f t="shared" si="86"/>
         <v>0.92300678315166973</v>
       </c>
       <c r="L165" s="151">
-        <f>(L55-L51)/ABS(L72)</f>
+        <f t="shared" si="86"/>
         <v>0.93218045504891378</v>
       </c>
     </row>
     <row r="166" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A166" s="48"/>
       <c r="B166" s="65" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C166" s="70"/>
       <c r="D166" s="65"/>
       <c r="E166" s="65"/>
       <c r="F166" s="151">
-        <f>F54/ABS(F72)</f>
+        <f t="shared" ref="F166:L166" si="87">F54/ABS(F72)</f>
         <v>0.14126020346616269</v>
       </c>
       <c r="G166" s="151">
-        <f>G54/ABS(G72)</f>
+        <f t="shared" si="87"/>
         <v>0.25231454803887671</v>
       </c>
       <c r="H166" s="151">
-        <f>H54/ABS(H72)</f>
+        <f t="shared" si="87"/>
         <v>0.18287939104601161</v>
       </c>
       <c r="I166" s="151">
-        <f>I54/ABS(I72)</f>
+        <f t="shared" si="87"/>
         <v>0.11170234913746585</v>
       </c>
       <c r="J166" s="151">
-        <f>J54/ABS(J72)</f>
+        <f t="shared" si="87"/>
         <v>0.11829624331667557</v>
       </c>
       <c r="K166" s="151">
-        <f>K54/ABS(K72)</f>
+        <f t="shared" si="87"/>
         <v>0.12389168116883829</v>
       </c>
       <c r="L166" s="151">
-        <f>L54/ABS(L72)</f>
+        <f t="shared" si="87"/>
         <v>0.12884243146877514</v>
       </c>
     </row>
@@ -8440,7 +8436,7 @@
     <row r="168" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A168" s="48"/>
       <c r="B168" s="85" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C168" s="86"/>
       <c r="D168" s="87"/>
@@ -8470,7 +8466,7 @@
     <row r="170" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A170" s="48"/>
       <c r="B170" s="65" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C170" s="65"/>
       <c r="D170" s="65"/>
@@ -8501,7 +8497,7 @@
     <row r="171" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A171" s="48"/>
       <c r="B171" s="65" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C171" s="65"/>
       <c r="D171" s="65"/>
@@ -8532,7 +8528,7 @@
     <row r="172" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A172" s="48"/>
       <c r="B172" s="65" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C172" s="65"/>
       <c r="D172" s="65"/>
@@ -8577,7 +8573,7 @@
     <row r="174" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A174" s="48"/>
       <c r="B174" s="85" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C174" s="86"/>
       <c r="D174" s="87"/>
@@ -8607,7 +8603,7 @@
     <row r="176" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A176" s="48"/>
       <c r="B176" s="65" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C176" s="65"/>
       <c r="D176" s="65"/>
@@ -8638,7 +8634,7 @@
     <row r="177" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A177" s="48"/>
       <c r="B177" s="65" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C177" s="65"/>
       <c r="D177" s="65"/>
@@ -8669,7 +8665,7 @@
     <row r="178" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A178" s="48"/>
       <c r="B178" s="65" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C178" s="65"/>
       <c r="D178" s="65"/>
@@ -8745,7 +8741,7 @@
     <row r="182" spans="1:12" ht="21" x14ac:dyDescent="0.5">
       <c r="A182" s="48"/>
       <c r="B182" s="52" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C182" s="53"/>
       <c r="D182" s="51"/>
@@ -8782,7 +8778,7 @@
       <c r="D184" s="55"/>
       <c r="E184" s="55"/>
       <c r="F184" s="56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G184" s="56"/>
       <c r="H184" s="56"/>
@@ -8810,32 +8806,32 @@
         <v>2027</v>
       </c>
       <c r="I185" s="58">
-        <f t="shared" ref="I185" si="83">H185+1</f>
+        <f t="shared" ref="I185" si="88">H185+1</f>
         <v>2028</v>
       </c>
       <c r="J185" s="58">
-        <f t="shared" ref="J185" si="84">I185+1</f>
+        <f t="shared" ref="J185" si="89">I185+1</f>
         <v>2029</v>
       </c>
       <c r="K185" s="58">
-        <f t="shared" ref="K185" si="85">J185+1</f>
+        <f t="shared" ref="K185" si="90">J185+1</f>
         <v>2030</v>
       </c>
       <c r="L185" s="58">
-        <f t="shared" ref="L185" si="86">K185+1</f>
+        <f t="shared" ref="L185" si="91">K185+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="186" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="48"/>
       <c r="B186" s="59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C186" s="59"/>
       <c r="D186" s="59"/>
       <c r="E186" s="59"/>
       <c r="F186" s="60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G186" s="60"/>
       <c r="H186" s="61"/>
@@ -8843,7 +8839,7 @@
       <c r="J186" s="61"/>
       <c r="K186" s="61"/>
       <c r="L186" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="187" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
@@ -8863,7 +8859,7 @@
     <row r="188" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A188" s="48"/>
       <c r="B188" s="85" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C188" s="86"/>
       <c r="D188" s="87"/>
@@ -8893,7 +8889,7 @@
     <row r="190" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A190" s="48"/>
       <c r="B190" s="65" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C190" s="70"/>
       <c r="D190" s="70"/>
@@ -8905,26 +8901,26 @@
         <v>21925</v>
       </c>
       <c r="I190" s="304">
-        <f t="shared" ref="I190:L190" si="87">H193</f>
+        <f t="shared" ref="I190:L190" si="92">H193</f>
         <v>23034.404999999999</v>
       </c>
       <c r="J190" s="304">
-        <f t="shared" si="87"/>
+        <f t="shared" si="92"/>
         <v>24199.945893</v>
       </c>
       <c r="K190" s="304">
-        <f t="shared" si="87"/>
+        <f t="shared" si="92"/>
         <v>25424.4631551858</v>
       </c>
       <c r="L190" s="304">
-        <f t="shared" si="87"/>
+        <f t="shared" si="92"/>
         <v>26710.940990838204</v>
       </c>
     </row>
     <row r="191" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A191" s="48"/>
       <c r="B191" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C191" s="65"/>
       <c r="D191" s="65"/>
@@ -8955,7 +8951,7 @@
     <row r="192" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="48"/>
       <c r="B192" s="72" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C192" s="72"/>
       <c r="D192" s="72"/>
@@ -8981,7 +8977,7 @@
     <row r="193" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A193" s="48"/>
       <c r="B193" s="70" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C193" s="70"/>
       <c r="D193" s="70"/>
@@ -8997,19 +8993,19 @@
         <v>23034.404999999999</v>
       </c>
       <c r="I193" s="302">
-        <f t="shared" ref="I193:L193" si="88">I190*(1+I191)*(1+I192)</f>
+        <f t="shared" ref="I193:L193" si="93">I190*(1+I191)*(1+I192)</f>
         <v>24199.945893</v>
       </c>
       <c r="J193" s="302">
-        <f t="shared" si="88"/>
+        <f t="shared" si="93"/>
         <v>25424.4631551858</v>
       </c>
       <c r="K193" s="302">
-        <f t="shared" si="88"/>
+        <f t="shared" si="93"/>
         <v>26710.940990838204</v>
       </c>
       <c r="L193" s="302">
-        <f t="shared" si="88"/>
+        <f t="shared" si="93"/>
         <v>28062.514604974618</v>
       </c>
     </row>
@@ -9030,7 +9026,7 @@
     <row r="195" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A195" s="48"/>
       <c r="B195" s="85" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C195" s="86"/>
       <c r="D195" s="87"/>
@@ -9060,7 +9056,7 @@
     <row r="197" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A197" s="48"/>
       <c r="B197" s="65" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C197" s="70"/>
       <c r="D197" s="70"/>
@@ -9075,26 +9071,26 @@
         <v>17292</v>
       </c>
       <c r="I197" s="302">
-        <f t="shared" ref="I197:L197" si="89">H200</f>
+        <f t="shared" ref="I197:L197" si="94">H200</f>
         <v>17990.596799999999</v>
       </c>
       <c r="J197" s="302">
-        <f t="shared" si="89"/>
+        <f t="shared" si="94"/>
         <v>18717.416910720003</v>
       </c>
       <c r="K197" s="302">
-        <f t="shared" si="89"/>
+        <f t="shared" si="94"/>
         <v>19473.600553913093</v>
       </c>
       <c r="L197" s="302">
-        <f t="shared" si="89"/>
+        <f t="shared" si="94"/>
         <v>20260.334016291181</v>
       </c>
     </row>
     <row r="198" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A198" s="48"/>
       <c r="B198" s="156" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C198" s="79"/>
       <c r="D198" s="79"/>
@@ -9125,7 +9121,7 @@
     <row r="199" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A199" s="48"/>
       <c r="B199" s="74" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C199" s="74"/>
       <c r="D199" s="74"/>
@@ -9153,7 +9149,7 @@
     <row r="200" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A200" s="48"/>
       <c r="B200" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C200" s="65"/>
       <c r="D200" s="65"/>
@@ -9169,26 +9165,26 @@
         <v>17990.596799999999</v>
       </c>
       <c r="I200" s="304">
-        <f t="shared" ref="I200:L200" si="90">I197*(1+I198)*(1+I199)</f>
+        <f t="shared" ref="I200:L200" si="95">I197*(1+I198)*(1+I199)</f>
         <v>18717.416910720003</v>
       </c>
       <c r="J200" s="304">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>19473.600553913093</v>
       </c>
       <c r="K200" s="304">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>20260.334016291181</v>
       </c>
       <c r="L200" s="304">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>21078.851510549346</v>
       </c>
     </row>
     <row r="201" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A201" s="48"/>
       <c r="B201" s="65" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C201" s="65"/>
       <c r="D201" s="65"/>
@@ -9199,23 +9195,23 @@
         <v>-0.12666666666666668</v>
       </c>
       <c r="H201" s="145">
-        <f t="shared" ref="H201:L201" si="91">(H200-G200)/G200</f>
+        <f t="shared" ref="H201:L201" si="96">(H200-G200)/G200</f>
         <v>4.0399999999999964E-2</v>
       </c>
       <c r="I201" s="145">
-        <f t="shared" si="91"/>
+        <f t="shared" si="96"/>
         <v>4.0400000000000214E-2</v>
       </c>
       <c r="J201" s="145">
-        <f t="shared" si="91"/>
+        <f t="shared" si="96"/>
         <v>4.0400000000000082E-2</v>
       </c>
       <c r="K201" s="145">
-        <f t="shared" si="91"/>
+        <f t="shared" si="96"/>
         <v>4.039999999999995E-2</v>
       </c>
       <c r="L201" s="145">
-        <f t="shared" si="91"/>
+        <f t="shared" si="96"/>
         <v>4.0400000000000075E-2</v>
       </c>
     </row>
@@ -9236,7 +9232,7 @@
     <row r="203" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A203" s="48"/>
       <c r="B203" s="65" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C203" s="65"/>
       <c r="D203" s="65"/>
@@ -9264,7 +9260,7 @@
     <row r="204" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A204" s="48"/>
       <c r="B204" s="65" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C204" s="65"/>
       <c r="D204" s="65"/>
@@ -9292,7 +9288,7 @@
     <row r="205" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="48"/>
       <c r="B205" s="72" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C205" s="72"/>
       <c r="D205" s="72"/>
@@ -9320,7 +9316,7 @@
     <row r="206" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A206" s="48"/>
       <c r="B206" s="70" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C206" s="70"/>
       <c r="D206" s="70"/>
@@ -9337,26 +9333,26 @@
         <v>25990.596799999999</v>
       </c>
       <c r="I206" s="308">
-        <f t="shared" ref="I206:L206" si="92">I200+SUM(I203:I205)</f>
+        <f t="shared" ref="I206:L206" si="97">I200+SUM(I203:I205)</f>
         <v>18717.416910720003</v>
       </c>
       <c r="J206" s="308">
-        <f t="shared" si="92"/>
+        <f t="shared" si="97"/>
         <v>19473.600553913093</v>
       </c>
       <c r="K206" s="308">
-        <f t="shared" si="92"/>
+        <f t="shared" si="97"/>
         <v>20260.334016291181</v>
       </c>
       <c r="L206" s="308">
-        <f t="shared" si="92"/>
+        <f t="shared" si="97"/>
         <v>21078.851510549346</v>
       </c>
     </row>
     <row r="207" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A207" s="48"/>
       <c r="B207" s="65" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C207" s="65"/>
       <c r="D207" s="65"/>
@@ -9367,23 +9363,23 @@
         <v>1.0501010101010102</v>
       </c>
       <c r="H207" s="160">
-        <f t="shared" ref="H207:L207" si="93">(H206-G206)/G206</f>
+        <f t="shared" ref="H207:L207" si="98">(H206-G206)/G206</f>
         <v>-0.35971135199054005</v>
       </c>
       <c r="I207" s="160">
-        <f t="shared" si="93"/>
+        <f t="shared" si="98"/>
         <v>-0.27983889501452297</v>
       </c>
       <c r="J207" s="160">
-        <f t="shared" si="93"/>
+        <f t="shared" si="98"/>
         <v>4.0400000000000082E-2</v>
       </c>
       <c r="K207" s="160">
-        <f t="shared" si="93"/>
+        <f t="shared" si="98"/>
         <v>4.039999999999995E-2</v>
       </c>
       <c r="L207" s="160">
-        <f t="shared" si="93"/>
+        <f t="shared" si="98"/>
         <v>4.0400000000000075E-2</v>
       </c>
     </row>
@@ -9404,7 +9400,7 @@
     <row r="209" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A209" s="48"/>
       <c r="B209" s="85" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C209" s="86"/>
       <c r="D209" s="87"/>
@@ -9434,7 +9430,7 @@
     <row r="211" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A211" s="48"/>
       <c r="B211" s="65" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C211" s="65"/>
       <c r="D211" s="65"/>
@@ -9445,30 +9441,30 @@
         <v>29041</v>
       </c>
       <c r="H211" s="311">
-        <f t="shared" ref="H211:L211" si="94">G214</f>
+        <f t="shared" ref="H211:L211" si="99">G214</f>
         <v>31794</v>
       </c>
       <c r="I211" s="311">
-        <f t="shared" si="94"/>
+        <f t="shared" si="99"/>
         <v>35024.270400000001</v>
       </c>
       <c r="J211" s="311">
-        <f t="shared" si="94"/>
+        <f t="shared" si="99"/>
         <v>38582.736272640002</v>
       </c>
       <c r="K211" s="311">
-        <f t="shared" si="94"/>
+        <f t="shared" si="99"/>
         <v>42502.742277940233</v>
       </c>
       <c r="L211" s="311">
-        <f t="shared" si="94"/>
+        <f t="shared" si="99"/>
         <v>46604.256907761461</v>
       </c>
     </row>
     <row r="212" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A212" s="48"/>
       <c r="B212" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C212" s="65"/>
       <c r="D212" s="65"/>
@@ -9499,7 +9495,7 @@
     <row r="213" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="48"/>
       <c r="B213" s="72" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C213" s="72"/>
       <c r="D213" s="72"/>
@@ -9525,7 +9521,7 @@
     <row r="214" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A214" s="48"/>
       <c r="B214" s="70" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C214" s="70"/>
       <c r="D214" s="70"/>
@@ -9541,26 +9537,26 @@
         <v>35024.270400000001</v>
       </c>
       <c r="I214" s="311">
-        <f t="shared" ref="I214:L214" si="95">I211*(1+I212)*(1+I213)</f>
+        <f t="shared" ref="I214:L214" si="100">I211*(1+I212)*(1+I213)</f>
         <v>38582.736272640002</v>
       </c>
       <c r="J214" s="311">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>42502.742277940233</v>
       </c>
       <c r="K214" s="311">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>46604.256907761461</v>
       </c>
       <c r="L214" s="311">
-        <f t="shared" si="95"/>
+        <f t="shared" si="100"/>
         <v>51101.567699360443</v>
       </c>
     </row>
     <row r="215" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A215" s="48"/>
       <c r="B215" s="65" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C215" s="65"/>
       <c r="D215" s="65"/>
@@ -9571,23 +9567,23 @@
         <v>9.4797011122206537E-2</v>
       </c>
       <c r="H215" s="160">
-        <f t="shared" ref="H215:L215" si="96">(H214-G214)/G214</f>
+        <f t="shared" ref="H215:L215" si="101">(H214-G214)/G214</f>
         <v>0.10160000000000004</v>
       </c>
       <c r="I215" s="160">
-        <f t="shared" si="96"/>
+        <f t="shared" si="101"/>
         <v>0.10160000000000002</v>
       </c>
       <c r="J215" s="160">
-        <f t="shared" si="96"/>
+        <f t="shared" si="101"/>
         <v>0.10160000000000016</v>
       </c>
       <c r="K215" s="160">
-        <f t="shared" si="96"/>
+        <f t="shared" si="101"/>
         <v>9.6499999999999878E-2</v>
       </c>
       <c r="L215" s="160">
-        <f t="shared" si="96"/>
+        <f t="shared" si="101"/>
         <v>9.650000000000003E-2</v>
       </c>
     </row>
@@ -9608,7 +9604,7 @@
     <row r="217" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A217" s="48"/>
       <c r="B217" s="85" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C217" s="86"/>
       <c r="D217" s="87"/>
@@ -9638,7 +9634,7 @@
     <row r="219" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A219" s="48"/>
       <c r="B219" s="65" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C219" s="65"/>
       <c r="D219" s="65"/>
@@ -9658,22 +9654,22 @@
         <v>65325.669400000006</v>
       </c>
       <c r="J219" s="311">
-        <f t="shared" ref="J219:L219" si="97">I222</f>
+        <f t="shared" ref="J219:L219" si="102">I222</f>
         <v>71322.56585092</v>
       </c>
       <c r="K219" s="311">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>77502.666181902227</v>
       </c>
       <c r="L219" s="311">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>83819.133475727256</v>
       </c>
     </row>
     <row r="220" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A220" s="48"/>
       <c r="B220" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C220" s="65"/>
       <c r="D220" s="65"/>
@@ -9704,7 +9700,7 @@
     <row r="221" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="48"/>
       <c r="B221" s="72" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C221" s="72"/>
       <c r="D221" s="72"/>
@@ -9730,7 +9726,7 @@
     <row r="222" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A222" s="48"/>
       <c r="B222" s="70" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C222" s="65"/>
       <c r="D222" s="65"/>
@@ -9740,7 +9736,7 @@
         <v>53924</v>
       </c>
       <c r="G222" s="311">
-        <f t="shared" ref="G222" si="98">G219</f>
+        <f t="shared" ref="G222" si="103">G219</f>
         <v>59833</v>
       </c>
       <c r="H222" s="311">
@@ -9748,26 +9744,26 @@
         <v>65325.669400000006</v>
       </c>
       <c r="I222" s="311">
-        <f t="shared" ref="I222:L222" si="99">I219*(1+I220)*(1+I221)</f>
+        <f t="shared" ref="I222:L222" si="104">I219*(1+I220)*(1+I221)</f>
         <v>71322.56585092</v>
       </c>
       <c r="J222" s="311">
-        <f t="shared" si="99"/>
+        <f t="shared" si="104"/>
         <v>77502.666181902227</v>
       </c>
       <c r="K222" s="311">
-        <f t="shared" si="99"/>
+        <f t="shared" si="104"/>
         <v>83819.133475727256</v>
       </c>
       <c r="L222" s="311">
-        <f t="shared" si="99"/>
+        <f t="shared" si="104"/>
         <v>90650.39285399903</v>
       </c>
     </row>
     <row r="223" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A223" s="48"/>
       <c r="B223" s="65" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C223" s="65"/>
       <c r="D223" s="65"/>
@@ -9778,23 +9774,23 @@
         <v>0.10958014984051628</v>
       </c>
       <c r="H223" s="160">
-        <f t="shared" ref="H223:L223" si="100">(H222-G222)/G222</f>
+        <f t="shared" ref="H223:L223" si="105">(H222-G222)/G222</f>
         <v>9.1800000000000104E-2</v>
       </c>
       <c r="I223" s="160">
-        <f t="shared" si="100"/>
+        <f t="shared" si="105"/>
         <v>9.1799999999999896E-2</v>
       </c>
       <c r="J223" s="160">
-        <f t="shared" si="100"/>
+        <f t="shared" si="105"/>
         <v>8.6650000000000116E-2</v>
       </c>
       <c r="K223" s="160">
-        <f t="shared" si="100"/>
+        <f t="shared" si="105"/>
         <v>8.1499999999999975E-2</v>
       </c>
       <c r="L223" s="160">
-        <f t="shared" si="100"/>
+        <f t="shared" si="105"/>
         <v>8.1500000000000031E-2</v>
       </c>
     </row>
@@ -9815,7 +9811,7 @@
     <row r="225" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A225" s="48"/>
       <c r="B225" s="319" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C225" s="320"/>
       <c r="D225" s="321"/>
@@ -9845,7 +9841,7 @@
     <row r="227" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A227" s="48"/>
       <c r="B227" s="129" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C227" s="70"/>
       <c r="D227" s="65"/>
@@ -9855,44 +9851,44 @@
         <v>22299</v>
       </c>
       <c r="G227" s="193">
-        <f t="shared" ref="G227:L227" si="101">G193</f>
+        <f t="shared" ref="G227:L227" si="106">G193</f>
         <v>21925</v>
       </c>
       <c r="H227" s="193">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>23034.404999999999</v>
       </c>
       <c r="I227" s="193">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>24199.945893</v>
       </c>
       <c r="J227" s="193">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>25424.4631551858</v>
       </c>
       <c r="K227" s="193">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>26710.940990838204</v>
       </c>
       <c r="L227" s="193">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>28062.514604974618</v>
       </c>
     </row>
     <row r="228" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A228" s="48"/>
       <c r="B228" s="129" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C228" s="65"/>
       <c r="D228" s="65"/>
       <c r="E228" s="65"/>
       <c r="F228" s="193">
-        <f t="shared" ref="F228:L228" si="102">F206</f>
+        <f t="shared" ref="F228:L228" si="107">F206</f>
         <v>19800</v>
       </c>
       <c r="G228" s="193">
-        <f t="shared" si="102"/>
+        <f t="shared" si="107"/>
         <v>40592</v>
       </c>
       <c r="H228" s="311">
@@ -9900,63 +9896,63 @@
         <v>25990.596799999999</v>
       </c>
       <c r="I228" s="311">
-        <f t="shared" si="102"/>
+        <f t="shared" si="107"/>
         <v>18717.416910720003</v>
       </c>
       <c r="J228" s="311">
-        <f t="shared" si="102"/>
+        <f t="shared" si="107"/>
         <v>19473.600553913093</v>
       </c>
       <c r="K228" s="311">
-        <f t="shared" si="102"/>
+        <f t="shared" si="107"/>
         <v>20260.334016291181</v>
       </c>
       <c r="L228" s="311">
-        <f t="shared" si="102"/>
+        <f t="shared" si="107"/>
         <v>21078.851510549346</v>
       </c>
     </row>
     <row r="229" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A229" s="48"/>
       <c r="B229" s="129" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C229" s="65"/>
       <c r="D229" s="65"/>
       <c r="E229" s="65"/>
       <c r="F229" s="193">
-        <f t="shared" ref="F229:L229" si="103">F214</f>
+        <f t="shared" ref="F229:L229" si="108">F214</f>
         <v>29041</v>
       </c>
       <c r="G229" s="193">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>31794</v>
       </c>
       <c r="H229" s="311">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>35024.270400000001</v>
       </c>
       <c r="I229" s="311">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>38582.736272640002</v>
       </c>
       <c r="J229" s="311">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>42502.742277940233</v>
       </c>
       <c r="K229" s="311">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>46604.256907761461</v>
       </c>
       <c r="L229" s="311">
-        <f t="shared" si="103"/>
+        <f t="shared" si="108"/>
         <v>51101.567699360443</v>
       </c>
     </row>
     <row r="230" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="48"/>
       <c r="B230" s="347" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C230" s="72"/>
       <c r="D230" s="72"/>
@@ -9966,7 +9962,7 @@
         <v>53924</v>
       </c>
       <c r="G230" s="316">
-        <f t="shared" ref="G230" si="104">G222</f>
+        <f t="shared" ref="G230" si="109">G222</f>
         <v>59833</v>
       </c>
       <c r="H230" s="326">
@@ -9974,26 +9970,26 @@
         <v>65325.669400000006</v>
       </c>
       <c r="I230" s="326">
-        <f t="shared" ref="I230:L230" si="105">I222</f>
+        <f t="shared" ref="I230:L230" si="110">I222</f>
         <v>71322.56585092</v>
       </c>
       <c r="J230" s="326">
-        <f t="shared" si="105"/>
+        <f t="shared" si="110"/>
         <v>77502.666181902227</v>
       </c>
       <c r="K230" s="326">
-        <f t="shared" si="105"/>
+        <f t="shared" si="110"/>
         <v>83819.133475727256</v>
       </c>
       <c r="L230" s="326">
-        <f t="shared" si="105"/>
+        <f t="shared" si="110"/>
         <v>90650.39285399903</v>
       </c>
     </row>
     <row r="231" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A231" s="48"/>
       <c r="B231" s="65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C231" s="65"/>
       <c r="D231" s="65"/>
@@ -10011,26 +10007,26 @@
         <v>149374.94160000002</v>
       </c>
       <c r="I231" s="311">
-        <f t="shared" ref="I231:L231" si="106">SUM(I227:I230)</f>
+        <f t="shared" ref="I231:L231" si="111">SUM(I227:I230)</f>
         <v>152822.66492727998</v>
       </c>
       <c r="J231" s="311">
-        <f t="shared" si="106"/>
+        <f t="shared" si="111"/>
         <v>164903.47216894134</v>
       </c>
       <c r="K231" s="311">
-        <f t="shared" si="106"/>
+        <f t="shared" si="111"/>
         <v>177394.66539061809</v>
       </c>
       <c r="L231" s="311">
-        <f t="shared" si="106"/>
+        <f t="shared" si="111"/>
         <v>190893.32666888344</v>
       </c>
     </row>
     <row r="232" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A232" s="48"/>
       <c r="B232" s="65" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C232" s="65"/>
       <c r="D232" s="65"/>
@@ -10041,23 +10037,23 @@
         <v>0.23252094927397174</v>
       </c>
       <c r="H232" s="197">
-        <f t="shared" ref="H232:L232" si="107">(H231-G231)/G231</f>
+        <f t="shared" ref="H232:L232" si="112">(H231-G231)/G231</f>
         <v>-3.0938981731367939E-2</v>
       </c>
       <c r="I232" s="197">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>2.3081002009777279E-2</v>
       </c>
       <c r="J232" s="197">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>7.9051148907853155E-2</v>
       </c>
       <c r="K232" s="197">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>7.5748515524765234E-2</v>
       </c>
       <c r="L232" s="197">
-        <f t="shared" si="107"/>
+        <f t="shared" si="112"/>
         <v>7.609395270450596E-2</v>
       </c>
     </row>
@@ -10078,7 +10074,7 @@
     <row r="234" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A234" s="48"/>
       <c r="B234" s="65" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C234" s="70"/>
       <c r="D234" s="70"/>
@@ -10094,7 +10090,7 @@
     <row r="235" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A235" s="48"/>
       <c r="B235" s="129" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C235" s="70"/>
       <c r="D235" s="70"/>
@@ -10104,7 +10100,7 @@
         <v>0.33661965073882172</v>
       </c>
       <c r="G235" s="108">
-        <f t="shared" ref="G235:L235" si="108">SUM(G227, G228)/G$231</f>
+        <f t="shared" ref="G235:L235" si="113">SUM(G227, G228)/G$231</f>
         <v>0.40557530620718291</v>
       </c>
       <c r="H235" s="108">
@@ -10112,93 +10108,93 @@
         <v>0.32820097718451585</v>
       </c>
       <c r="I235" s="108">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>0.28083113734564208</v>
       </c>
       <c r="J235" s="108">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>0.27226875892037883</v>
       </c>
       <c r="K235" s="108">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>0.26478403340765605</v>
       </c>
       <c r="L235" s="108">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>0.25742841288927182</v>
       </c>
     </row>
     <row r="236" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A236" s="48"/>
       <c r="B236" s="129" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C236" s="70"/>
       <c r="D236" s="70"/>
       <c r="E236" s="70"/>
       <c r="F236" s="108">
-        <f t="shared" ref="F236:L237" si="109">F229/F$231</f>
+        <f t="shared" ref="F236:L237" si="114">F229/F$231</f>
         <v>0.23220910893622465</v>
       </c>
       <c r="G236" s="108">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>0.20626167739256798</v>
       </c>
       <c r="H236" s="108">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>0.23447219476603295</v>
       </c>
       <c r="I236" s="108">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>0.25246736988259844</v>
       </c>
       <c r="J236" s="108">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>0.25774316161394561</v>
       </c>
       <c r="K236" s="108">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>0.26271509802811821</v>
       </c>
       <c r="L236" s="108">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>0.26769698339428777</v>
       </c>
     </row>
     <row r="237" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A237" s="48"/>
       <c r="B237" s="129" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C237" s="70"/>
       <c r="D237" s="70"/>
       <c r="E237" s="70"/>
       <c r="F237" s="108">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>0.43117124032495363</v>
       </c>
       <c r="G237" s="108">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>0.38816301640024914</v>
       </c>
       <c r="H237" s="108">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>0.43732682804945106</v>
       </c>
       <c r="I237" s="108">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>0.4667014927717596</v>
       </c>
       <c r="J237" s="108">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>0.46998807946567561</v>
       </c>
       <c r="K237" s="108">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>0.4725008685642258</v>
       </c>
       <c r="L237" s="108">
-        <f t="shared" si="109"/>
+        <f t="shared" si="114"/>
         <v>0.47487460371644041</v>
       </c>
     </row>
@@ -10236,7 +10232,7 @@
     <row r="240" spans="1:12" ht="21" x14ac:dyDescent="0.5">
       <c r="A240" s="48"/>
       <c r="B240" s="52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C240" s="53"/>
       <c r="D240" s="51"/>
@@ -10273,7 +10269,7 @@
       <c r="D242" s="55"/>
       <c r="E242" s="55"/>
       <c r="F242" s="56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G242" s="56"/>
       <c r="H242" s="56"/>
@@ -10301,32 +10297,32 @@
         <v>2027</v>
       </c>
       <c r="I243" s="58">
-        <f t="shared" ref="I243" si="110">H243+1</f>
+        <f t="shared" ref="I243" si="115">H243+1</f>
         <v>2028</v>
       </c>
       <c r="J243" s="58">
-        <f t="shared" ref="J243" si="111">I243+1</f>
+        <f t="shared" ref="J243" si="116">I243+1</f>
         <v>2029</v>
       </c>
       <c r="K243" s="58">
-        <f t="shared" ref="K243" si="112">J243+1</f>
+        <f t="shared" ref="K243" si="117">J243+1</f>
         <v>2030</v>
       </c>
       <c r="L243" s="58">
-        <f t="shared" ref="L243" si="113">K243+1</f>
+        <f t="shared" ref="L243" si="118">K243+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="244" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="48"/>
       <c r="B244" s="59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C244" s="59"/>
       <c r="D244" s="59"/>
       <c r="E244" s="59"/>
       <c r="F244" s="60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G244" s="60"/>
       <c r="H244" s="61"/>
@@ -10334,7 +10330,7 @@
       <c r="J244" s="61"/>
       <c r="K244" s="61"/>
       <c r="L244" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="245" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
@@ -10354,7 +10350,7 @@
     <row r="246" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A246" s="48"/>
       <c r="B246" s="85" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C246" s="86"/>
       <c r="D246" s="87"/>
@@ -10384,15 +10380,15 @@
     <row r="248" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A248" s="48"/>
       <c r="B248" s="65" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C248" s="70"/>
       <c r="D248" s="65"/>
       <c r="E248" s="65" t="s">
+        <v>297</v>
+      </c>
+      <c r="F248" s="365" t="s">
         <v>298</v>
-      </c>
-      <c r="F248" s="365" t="s">
-        <v>299</v>
       </c>
       <c r="G248" s="91"/>
       <c r="H248" s="92"/>
@@ -10404,7 +10400,7 @@
     <row r="249" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A249" s="48"/>
       <c r="B249" s="129" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C249" s="70"/>
       <c r="D249" s="65"/>
@@ -10424,7 +10420,7 @@
     <row r="250" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A250" s="48"/>
       <c r="B250" s="129" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C250" s="70"/>
       <c r="D250" s="65"/>
@@ -10444,7 +10440,7 @@
     <row r="251" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A251" s="48"/>
       <c r="B251" s="129" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C251" s="70"/>
       <c r="D251" s="65"/>
@@ -10478,7 +10474,7 @@
     <row r="253" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A253" s="48"/>
       <c r="B253" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C253" s="70"/>
       <c r="D253" s="65"/>
@@ -10509,7 +10505,7 @@
     <row r="254" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A254" s="48"/>
       <c r="B254" s="65" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C254" s="70"/>
       <c r="D254" s="65"/>
@@ -10540,7 +10536,7 @@
     <row r="255" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A255" s="48"/>
       <c r="B255" s="65" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C255" s="70"/>
       <c r="D255" s="65"/>
@@ -10571,7 +10567,7 @@
     <row r="256" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A256" s="48"/>
       <c r="B256" s="65" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C256" s="70"/>
       <c r="D256" s="65"/>
@@ -10603,7 +10599,7 @@
     <row r="257" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A257" s="48"/>
       <c r="B257" s="132" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C257" s="131"/>
       <c r="D257" s="131"/>
@@ -10637,7 +10633,7 @@
     <row r="258" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A258" s="48"/>
       <c r="B258" s="65" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C258" s="70"/>
       <c r="D258" s="70"/>
@@ -10671,7 +10667,7 @@
     <row r="259" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A259" s="48"/>
       <c r="B259" s="74" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C259" s="78"/>
       <c r="D259" s="78"/>
@@ -10705,7 +10701,7 @@
     <row r="260" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A260" s="48"/>
       <c r="B260" s="65" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C260" s="70"/>
       <c r="D260" s="65"/>
@@ -10719,19 +10715,19 @@
         <v>22527.543999999998</v>
       </c>
       <c r="I260" s="193">
-        <f t="shared" ref="I260:L260" si="114">SUM(I257:I259)</f>
+        <f t="shared" ref="I260:L260" si="119">SUM(I257:I259)</f>
         <v>23938.793486399998</v>
       </c>
       <c r="J260" s="193">
-        <f t="shared" si="114"/>
+        <f t="shared" si="119"/>
         <v>25316.756118994857</v>
       </c>
       <c r="K260" s="193">
-        <f t="shared" si="114"/>
+        <f t="shared" si="119"/>
         <v>26645.327458196167</v>
       </c>
       <c r="L260" s="193">
-        <f t="shared" si="114"/>
+        <f t="shared" si="119"/>
         <v>28044.28333899278</v>
       </c>
       <c r="Q260" s="35"/>
@@ -10753,15 +10749,15 @@
     <row r="262" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A262" s="48"/>
       <c r="B262" s="65" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C262" s="70"/>
       <c r="D262" s="65"/>
       <c r="E262" s="65" t="s">
+        <v>297</v>
+      </c>
+      <c r="F262" s="365" t="s">
         <v>298</v>
-      </c>
-      <c r="F262" s="365" t="s">
-        <v>299</v>
       </c>
       <c r="G262" s="309"/>
       <c r="H262" s="193"/>
@@ -10773,7 +10769,7 @@
     <row r="263" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A263" s="48"/>
       <c r="B263" s="129" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C263" s="70"/>
       <c r="D263" s="65"/>
@@ -10793,7 +10789,7 @@
     <row r="264" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A264" s="48"/>
       <c r="B264" s="129" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C264" s="70"/>
       <c r="D264" s="65"/>
@@ -10813,7 +10809,7 @@
     <row r="265" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A265" s="48"/>
       <c r="B265" s="129" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C265" s="70"/>
       <c r="D265" s="65"/>
@@ -10847,7 +10843,7 @@
     <row r="267" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A267" s="48"/>
       <c r="B267" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C267" s="70"/>
       <c r="D267" s="65"/>
@@ -10878,7 +10874,7 @@
     <row r="268" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A268" s="48"/>
       <c r="B268" s="65" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C268" s="70"/>
       <c r="D268" s="65"/>
@@ -10909,7 +10905,7 @@
     <row r="269" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A269" s="48"/>
       <c r="B269" s="65" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C269" s="70"/>
       <c r="D269" s="65"/>
@@ -10940,7 +10936,7 @@
     <row r="270" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A270" s="48"/>
       <c r="B270" s="65" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C270" s="70"/>
       <c r="D270" s="65"/>
@@ -10971,7 +10967,7 @@
     <row r="271" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A271" s="48"/>
       <c r="B271" s="132" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C271" s="131"/>
       <c r="D271" s="131"/>
@@ -10986,26 +10982,26 @@
         <v>33774.890240000001</v>
       </c>
       <c r="I271" s="352">
-        <f t="shared" ref="I271:L271" si="115">H271*(1+(I267*$F263))*(1+I268)</f>
+        <f t="shared" ref="I271:L271" si="120">H271*(1+(I267*$F263))*(1+I268)</f>
         <v>37233.439000576</v>
       </c>
       <c r="J271" s="352">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>40656.122880703944</v>
       </c>
       <c r="K271" s="352">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>43969.596895481314</v>
       </c>
       <c r="L271" s="352">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>47553.119042463048</v>
       </c>
     </row>
     <row r="272" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A272" s="48"/>
       <c r="B272" s="65" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C272" s="70"/>
       <c r="D272" s="70"/>
@@ -11020,26 +11016,26 @@
         <v>9431.4787840000008</v>
       </c>
       <c r="I272" s="311">
-        <f t="shared" ref="I272:L272" si="116">H272*(1+(I267*$F264))*(1+I269)</f>
+        <f t="shared" ref="I272:L272" si="121">H272*(1+(I267*$F264))*(1+I269)</f>
         <v>10161.852501032961</v>
       </c>
       <c r="J272" s="311">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>10864.595410741895</v>
       </c>
       <c r="K272" s="311">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>11526.249271256076</v>
       </c>
       <c r="L272" s="311">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>12228.197851875573</v>
       </c>
     </row>
     <row r="273" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A273" s="48"/>
       <c r="B273" s="74" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C273" s="78"/>
       <c r="D273" s="78"/>
@@ -11054,26 +11050,26 @@
         <v>4688.4281600000004</v>
       </c>
       <c r="I273" s="353">
-        <f t="shared" ref="I273:L273" si="117">H273*(1+(I267*$F265))*(1+I270)</f>
+        <f t="shared" ref="I273:L273" si="122">H273*(1+(I267*$F265))*(1+I270)</f>
         <v>5022.2442449920009</v>
       </c>
       <c r="J273" s="353">
-        <f t="shared" si="117"/>
+        <f t="shared" si="122"/>
         <v>5340.9684203898059</v>
       </c>
       <c r="K273" s="353">
-        <f t="shared" si="117"/>
+        <f t="shared" si="122"/>
         <v>5638.727409826538</v>
       </c>
       <c r="L273" s="353">
-        <f t="shared" si="117"/>
+        <f t="shared" si="122"/>
         <v>5953.0864629243679</v>
       </c>
     </row>
     <row r="274" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A274" s="48"/>
       <c r="B274" s="65" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C274" s="70"/>
       <c r="D274" s="65"/>
@@ -11087,19 +11083,19 @@
         <v>47894.797184000003</v>
       </c>
       <c r="I274" s="193">
-        <f t="shared" ref="I274" si="118">SUM(I271:I273)</f>
+        <f t="shared" ref="I274" si="123">SUM(I271:I273)</f>
         <v>52417.535746600959</v>
       </c>
       <c r="J274" s="193">
-        <f t="shared" ref="J274" si="119">SUM(J271:J273)</f>
+        <f t="shared" ref="J274" si="124">SUM(J271:J273)</f>
         <v>56861.686711835646</v>
       </c>
       <c r="K274" s="193">
-        <f t="shared" ref="K274" si="120">SUM(K271:K273)</f>
+        <f t="shared" ref="K274" si="125">SUM(K271:K273)</f>
         <v>61134.573576563933</v>
       </c>
       <c r="L274" s="193">
-        <f t="shared" ref="L274" si="121">SUM(L271:L273)</f>
+        <f t="shared" ref="L274" si="126">SUM(L271:L273)</f>
         <v>65734.403357262985</v>
       </c>
     </row>
@@ -11120,15 +11116,15 @@
     <row r="276" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A276" s="48"/>
       <c r="B276" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C276" s="70"/>
       <c r="D276" s="65"/>
       <c r="E276" s="65" t="s">
+        <v>297</v>
+      </c>
+      <c r="F276" s="365" t="s">
         <v>298</v>
-      </c>
-      <c r="F276" s="365" t="s">
-        <v>299</v>
       </c>
       <c r="G276" s="309"/>
       <c r="H276" s="193"/>
@@ -11140,7 +11136,7 @@
     <row r="277" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A277" s="48"/>
       <c r="B277" s="129" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C277" s="70"/>
       <c r="D277" s="65"/>
@@ -11160,7 +11156,7 @@
     <row r="278" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A278" s="48"/>
       <c r="B278" s="129" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C278" s="70"/>
       <c r="D278" s="65"/>
@@ -11180,7 +11176,7 @@
     <row r="279" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A279" s="48"/>
       <c r="B279" s="129" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C279" s="70"/>
       <c r="D279" s="65"/>
@@ -11214,7 +11210,7 @@
     <row r="281" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A281" s="48"/>
       <c r="B281" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C281" s="70"/>
       <c r="D281" s="65"/>
@@ -11245,7 +11241,7 @@
     <row r="282" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A282" s="48"/>
       <c r="B282" s="65" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C282" s="70"/>
       <c r="D282" s="65"/>
@@ -11276,7 +11272,7 @@
     <row r="283" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A283" s="48"/>
       <c r="B283" s="65" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C283" s="70"/>
       <c r="D283" s="65"/>
@@ -11307,7 +11303,7 @@
     <row r="284" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A284" s="48"/>
       <c r="B284" s="65" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C284" s="70"/>
       <c r="D284" s="65"/>
@@ -11338,7 +11334,7 @@
     <row r="285" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A285" s="48"/>
       <c r="B285" s="132" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C285" s="131"/>
       <c r="D285" s="131"/>
@@ -11353,26 +11349,26 @@
         <v>16048.730880000001</v>
       </c>
       <c r="I285" s="352">
-        <f t="shared" ref="I285:L285" si="122">H285*(1+(I281*$F277))*(1+I282)</f>
+        <f t="shared" ref="I285:L285" si="127">H285*(1+(I281*$F277))*(1+I282)</f>
         <v>18025.934524416003</v>
       </c>
       <c r="J285" s="352">
-        <f t="shared" si="122"/>
+        <f t="shared" si="127"/>
         <v>20149.389611392209</v>
       </c>
       <c r="K285" s="352">
-        <f t="shared" si="122"/>
+        <f t="shared" si="127"/>
         <v>22310.411647214023</v>
       </c>
       <c r="L285" s="352">
-        <f t="shared" si="122"/>
+        <f t="shared" si="127"/>
         <v>24703.203296377727</v>
       </c>
     </row>
     <row r="286" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A286" s="48"/>
       <c r="B286" s="65" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C286" s="70"/>
       <c r="D286" s="70"/>
@@ -11387,26 +11383,26 @@
         <v>4449.4894080000004</v>
       </c>
       <c r="I286" s="311">
-        <f t="shared" ref="I286:L286" si="123">H286*(1+(I281*$F278))*(1+I283)</f>
+        <f t="shared" ref="I286:L286" si="128">H286*(1+(I281*$F278))*(1+I283)</f>
         <v>4849.5874955673607</v>
       </c>
       <c r="J286" s="311">
-        <f t="shared" si="123"/>
+        <f t="shared" si="128"/>
         <v>5260.2505646920054</v>
       </c>
       <c r="K286" s="311">
-        <f t="shared" si="123"/>
+        <f t="shared" si="128"/>
         <v>5661.8706953062392</v>
       </c>
       <c r="L286" s="311">
-        <f t="shared" si="123"/>
+        <f t="shared" si="128"/>
         <v>6094.1545228928699</v>
       </c>
     </row>
     <row r="287" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A287" s="48"/>
       <c r="B287" s="74" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C287" s="78"/>
       <c r="D287" s="78"/>
@@ -11421,26 +11417,26 @@
         <v>2207.7619199999999</v>
       </c>
       <c r="I287" s="353">
-        <f t="shared" ref="I287:L287" si="124">H287*(1+(I281*$F279))*(1+I284)</f>
+        <f t="shared" ref="I287:L287" si="129">H287*(1+(I281*$F279))*(1+I284)</f>
         <v>2387.9152926720003</v>
       </c>
       <c r="J287" s="353">
-        <f t="shared" si="124"/>
+        <f t="shared" si="129"/>
         <v>2570.3520210321412</v>
       </c>
       <c r="K287" s="353">
-        <f t="shared" si="124"/>
+        <f t="shared" si="129"/>
         <v>2746.742428475472</v>
       </c>
       <c r="L287" s="353">
-        <f t="shared" si="124"/>
+        <f t="shared" si="129"/>
         <v>2935.2376276296018</v>
       </c>
     </row>
     <row r="288" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A288" s="48"/>
       <c r="B288" s="65" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C288" s="70"/>
       <c r="D288" s="65"/>
@@ -11454,19 +11450,19 @@
         <v>22705.982208000001</v>
       </c>
       <c r="I288" s="193">
-        <f t="shared" ref="I288" si="125">SUM(I285:I287)</f>
+        <f t="shared" ref="I288" si="130">SUM(I285:I287)</f>
         <v>25263.437312655366</v>
       </c>
       <c r="J288" s="193">
-        <f t="shared" ref="J288" si="126">SUM(J285:J287)</f>
+        <f t="shared" ref="J288" si="131">SUM(J285:J287)</f>
         <v>27979.992197116353</v>
       </c>
       <c r="K288" s="193">
-        <f t="shared" ref="K288" si="127">SUM(K285:K287)</f>
+        <f t="shared" ref="K288" si="132">SUM(K285:K287)</f>
         <v>30719.024770995733</v>
       </c>
       <c r="L288" s="193">
-        <f t="shared" ref="L288" si="128">SUM(L285:L287)</f>
+        <f t="shared" ref="L288" si="133">SUM(L285:L287)</f>
         <v>33732.595446900203</v>
       </c>
     </row>
@@ -11487,136 +11483,136 @@
     <row r="290" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A290" s="48"/>
       <c r="B290" s="65" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C290" s="70"/>
       <c r="D290" s="65"/>
       <c r="E290" s="65"/>
       <c r="F290" s="193"/>
       <c r="G290" s="193">
-        <f t="shared" ref="G290:L290" si="129">G260</f>
+        <f t="shared" ref="G290:L290" si="134">G260</f>
         <v>21200</v>
       </c>
       <c r="H290" s="193">
-        <f t="shared" si="129"/>
+        <f t="shared" si="134"/>
         <v>22527.543999999998</v>
       </c>
       <c r="I290" s="193">
-        <f t="shared" si="129"/>
+        <f t="shared" si="134"/>
         <v>23938.793486399998</v>
       </c>
       <c r="J290" s="193">
-        <f t="shared" si="129"/>
+        <f t="shared" si="134"/>
         <v>25316.756118994857</v>
       </c>
       <c r="K290" s="193">
-        <f t="shared" si="129"/>
+        <f t="shared" si="134"/>
         <v>26645.327458196167</v>
       </c>
       <c r="L290" s="193">
-        <f t="shared" si="129"/>
+        <f t="shared" si="134"/>
         <v>28044.28333899278</v>
       </c>
     </row>
     <row r="291" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A291" s="48"/>
       <c r="B291" s="65" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C291" s="70"/>
       <c r="D291" s="65"/>
       <c r="E291" s="65"/>
       <c r="F291" s="193"/>
       <c r="G291" s="193">
-        <f t="shared" ref="G291:L291" si="130">G274</f>
+        <f t="shared" ref="G291:L291" si="135">G274</f>
         <v>43768</v>
       </c>
       <c r="H291" s="193">
-        <f t="shared" si="130"/>
+        <f t="shared" si="135"/>
         <v>47894.797184000003</v>
       </c>
       <c r="I291" s="193">
-        <f t="shared" si="130"/>
+        <f t="shared" si="135"/>
         <v>52417.535746600959</v>
       </c>
       <c r="J291" s="193">
-        <f t="shared" si="130"/>
+        <f t="shared" si="135"/>
         <v>56861.686711835646</v>
       </c>
       <c r="K291" s="193">
-        <f t="shared" si="130"/>
+        <f t="shared" si="135"/>
         <v>61134.573576563933</v>
       </c>
       <c r="L291" s="193">
-        <f t="shared" si="130"/>
+        <f t="shared" si="135"/>
         <v>65734.403357262985</v>
       </c>
     </row>
     <row r="292" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="48"/>
       <c r="B292" s="72" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C292" s="72"/>
       <c r="D292" s="72"/>
       <c r="E292" s="72"/>
       <c r="F292" s="316"/>
       <c r="G292" s="316">
-        <f t="shared" ref="G292:L292" si="131">G288</f>
+        <f t="shared" ref="G292:L292" si="136">G288</f>
         <v>20412</v>
       </c>
       <c r="H292" s="316">
-        <f t="shared" si="131"/>
+        <f t="shared" si="136"/>
         <v>22705.982208000001</v>
       </c>
       <c r="I292" s="316">
-        <f t="shared" si="131"/>
+        <f t="shared" si="136"/>
         <v>25263.437312655366</v>
       </c>
       <c r="J292" s="316">
-        <f t="shared" si="131"/>
+        <f t="shared" si="136"/>
         <v>27979.992197116353</v>
       </c>
       <c r="K292" s="316">
-        <f t="shared" si="131"/>
+        <f t="shared" si="136"/>
         <v>30719.024770995733</v>
       </c>
       <c r="L292" s="316">
-        <f t="shared" si="131"/>
+        <f t="shared" si="136"/>
         <v>33732.595446900203</v>
       </c>
     </row>
     <row r="293" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A293" s="48"/>
       <c r="B293" s="65" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C293" s="65"/>
       <c r="D293" s="65"/>
       <c r="E293" s="65"/>
       <c r="F293" s="193"/>
       <c r="G293" s="193">
-        <f t="shared" ref="G293:L293" si="132">SUM(G290:G292)</f>
+        <f t="shared" ref="G293:L293" si="137">SUM(G290:G292)</f>
         <v>85380</v>
       </c>
       <c r="H293" s="193">
-        <f t="shared" si="132"/>
+        <f t="shared" si="137"/>
         <v>93128.323392000006</v>
       </c>
       <c r="I293" s="193">
-        <f t="shared" si="132"/>
+        <f t="shared" si="137"/>
         <v>101619.76654565633</v>
       </c>
       <c r="J293" s="193">
-        <f t="shared" si="132"/>
+        <f t="shared" si="137"/>
         <v>110158.43502794686</v>
       </c>
       <c r="K293" s="193">
-        <f t="shared" si="132"/>
+        <f t="shared" si="137"/>
         <v>118498.92580575583</v>
       </c>
       <c r="L293" s="193">
-        <f t="shared" si="132"/>
+        <f t="shared" si="137"/>
         <v>127511.28214315597</v>
       </c>
     </row>
@@ -11651,7 +11647,7 @@
     <row r="296" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A296" s="48"/>
       <c r="B296" s="85" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C296" s="86"/>
       <c r="D296" s="87"/>
@@ -11695,7 +11691,7 @@
     <row r="299" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A299" s="48"/>
       <c r="B299" s="195" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C299" s="195"/>
       <c r="D299" s="195"/>
@@ -11707,26 +11703,26 @@
         <v>44669</v>
       </c>
       <c r="I299" s="359">
-        <f t="shared" ref="I299:L299" si="133">H303</f>
+        <f t="shared" ref="I299:L299" si="138">H303</f>
         <v>46455.76</v>
       </c>
       <c r="J299" s="359">
-        <f t="shared" si="133"/>
+        <f t="shared" si="138"/>
         <v>49317.612178570496</v>
       </c>
       <c r="K299" s="359">
-        <f t="shared" si="133"/>
+        <f t="shared" si="138"/>
         <v>54675.28745649699</v>
       </c>
       <c r="L299" s="359">
-        <f t="shared" si="133"/>
+        <f t="shared" si="138"/>
         <v>60154.783195078846</v>
       </c>
     </row>
     <row r="300" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A300" s="48"/>
       <c r="B300" s="195" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C300" s="195"/>
       <c r="D300" s="195"/>
@@ -11757,7 +11753,7 @@
     <row r="301" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A301" s="48"/>
       <c r="B301" s="195" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C301" s="195"/>
       <c r="D301" s="195"/>
@@ -11788,7 +11784,7 @@
     <row r="302" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A302" s="48"/>
       <c r="B302" s="355" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C302" s="195"/>
       <c r="D302" s="195"/>
@@ -11814,7 +11810,7 @@
     <row r="303" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A303" s="48"/>
       <c r="B303" s="356" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C303" s="357"/>
       <c r="D303" s="357"/>
@@ -11832,19 +11828,19 @@
         <v>46455.76</v>
       </c>
       <c r="I303" s="358">
-        <f t="shared" ref="I303:L303" si="134">I299*(1+(MAX(I301, 0)*I302))*(1+I300)</f>
+        <f t="shared" ref="I303:L303" si="139">I299*(1+(MAX(I301, 0)*I302))*(1+I300)</f>
         <v>49317.612178570496</v>
       </c>
       <c r="J303" s="358">
-        <f t="shared" si="134"/>
+        <f t="shared" si="139"/>
         <v>54675.28745649699</v>
       </c>
       <c r="K303" s="358">
-        <f t="shared" si="134"/>
+        <f t="shared" si="139"/>
         <v>60154.783195078846</v>
       </c>
       <c r="L303" s="358">
-        <f t="shared" si="134"/>
+        <f t="shared" si="139"/>
         <v>66202.690606727439</v>
       </c>
     </row>
@@ -11980,7 +11976,7 @@
     <row r="313" spans="1:12" ht="21" x14ac:dyDescent="0.5">
       <c r="A313" s="48"/>
       <c r="B313" s="52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C313" s="53"/>
       <c r="D313" s="51"/>
@@ -12017,7 +12013,7 @@
       <c r="D315" s="55"/>
       <c r="E315" s="55"/>
       <c r="F315" s="56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G315" s="56"/>
       <c r="H315" s="56"/>
@@ -12045,32 +12041,32 @@
         <v>2027</v>
       </c>
       <c r="I316" s="58">
-        <f t="shared" ref="I316" si="135">H316+1</f>
+        <f t="shared" ref="I316" si="140">H316+1</f>
         <v>2028</v>
       </c>
       <c r="J316" s="58">
-        <f t="shared" ref="J316" si="136">I316+1</f>
+        <f t="shared" ref="J316" si="141">I316+1</f>
         <v>2029</v>
       </c>
       <c r="K316" s="58">
-        <f t="shared" ref="K316" si="137">J316+1</f>
+        <f t="shared" ref="K316" si="142">J316+1</f>
         <v>2030</v>
       </c>
       <c r="L316" s="58">
-        <f t="shared" ref="L316" si="138">K316+1</f>
+        <f t="shared" ref="L316" si="143">K316+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="317" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A317" s="48"/>
       <c r="B317" s="59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C317" s="59"/>
       <c r="D317" s="59"/>
       <c r="E317" s="59"/>
       <c r="F317" s="60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G317" s="60"/>
       <c r="H317" s="61"/>
@@ -12078,7 +12074,7 @@
       <c r="J317" s="61"/>
       <c r="K317" s="61"/>
       <c r="L317" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="318" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
@@ -12098,7 +12094,7 @@
     <row r="319" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A319" s="48"/>
       <c r="B319" s="65" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C319" s="70"/>
       <c r="D319" s="70"/>
@@ -12130,7 +12126,7 @@
     <row r="321" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A321" s="48"/>
       <c r="B321" s="85" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C321" s="86"/>
       <c r="D321" s="87"/>
@@ -12160,7 +12156,7 @@
     <row r="323" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A323" s="48"/>
       <c r="B323" s="129" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C323" s="65"/>
       <c r="D323" s="65"/>
@@ -12178,26 +12174,26 @@
         <v>19533.362945240817</v>
       </c>
       <c r="I323" s="193">
-        <f t="shared" ref="I323:L323" si="139">I338*I335</f>
+        <f t="shared" ref="I323:L323" si="144">I338*I335</f>
         <v>19984.212534637631</v>
       </c>
       <c r="J323" s="193">
-        <f t="shared" si="139"/>
+        <f t="shared" si="144"/>
         <v>21563.987495519454</v>
       </c>
       <c r="K323" s="193">
-        <f t="shared" si="139"/>
+        <f t="shared" si="144"/>
         <v>23197.427537099655</v>
       </c>
       <c r="L323" s="193">
-        <f t="shared" si="139"/>
+        <f t="shared" si="144"/>
         <v>24962.611490973919</v>
       </c>
     </row>
     <row r="324" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A324" s="48"/>
       <c r="B324" s="129" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C324" s="65"/>
       <c r="D324" s="65"/>
@@ -12215,26 +12211,26 @@
         <v>27705.603543449441</v>
       </c>
       <c r="I324" s="193">
-        <f t="shared" ref="I324:L324" si="140">ABS(I339*I336)</f>
+        <f t="shared" ref="I324:L324" si="145">ABS(I339*I336)</f>
         <v>30231.801256004303</v>
       </c>
       <c r="J324" s="193">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>32772.048466979119</v>
       </c>
       <c r="K324" s="193">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>35253.337965503713</v>
       </c>
       <c r="L324" s="193">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>37934.506943767003</v>
       </c>
     </row>
     <row r="325" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A325" s="48"/>
       <c r="B325" s="132" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C325" s="132"/>
       <c r="D325" s="132"/>
@@ -12244,34 +12240,34 @@
         <v>49855</v>
       </c>
       <c r="G325" s="314">
-        <f t="shared" ref="G325:L325" si="141">SUM(G323:G324)</f>
+        <f t="shared" ref="G325:L325" si="146">SUM(G323:G324)</f>
         <v>50659</v>
       </c>
       <c r="H325" s="314">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>47238.966488690261</v>
       </c>
       <c r="I325" s="314">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>50216.013790641933</v>
       </c>
       <c r="J325" s="314">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>54336.035962498572</v>
       </c>
       <c r="K325" s="314">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>58450.765502603368</v>
       </c>
       <c r="L325" s="314">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>62897.118434740922</v>
       </c>
     </row>
     <row r="326" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A326" s="48"/>
       <c r="B326" s="129" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C326" s="70"/>
       <c r="D326" s="70"/>
@@ -12289,26 +12285,26 @@
         <v>15447.813240556181</v>
       </c>
       <c r="I326" s="193">
-        <f t="shared" ref="I326:L326" si="142">I340*ABS(I336)</f>
+        <f t="shared" ref="I326:L326" si="147">I340*ABS(I336)</f>
         <v>16856.345287550495</v>
       </c>
       <c r="J326" s="193">
-        <f t="shared" si="142"/>
+        <f t="shared" si="147"/>
         <v>18272.710913314339</v>
       </c>
       <c r="K326" s="193">
-        <f t="shared" si="142"/>
+        <f t="shared" si="147"/>
         <v>19656.203487617913</v>
       </c>
       <c r="L326" s="193">
-        <f t="shared" si="142"/>
+        <f t="shared" si="147"/>
         <v>21151.142862521981</v>
       </c>
     </row>
     <row r="327" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A327" s="48"/>
       <c r="B327" s="281" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C327" s="78"/>
       <c r="D327" s="78"/>
@@ -12326,26 +12322,26 @@
         <v>6083.7650726904722</v>
       </c>
       <c r="I327" s="315">
-        <f t="shared" ref="I327:L327" si="143">I335*I341</f>
+        <f t="shared" ref="I327:L327" si="148">I335*I341</f>
         <v>6224.1844665602539</v>
       </c>
       <c r="J327" s="315">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>6716.2133996562543</v>
       </c>
       <c r="K327" s="315">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>7224.9565946277526</v>
       </c>
       <c r="L327" s="315">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>7774.7321000314651</v>
       </c>
     </row>
     <row r="328" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A328" s="48"/>
       <c r="B328" s="233" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C328" s="73"/>
       <c r="D328" s="73"/>
@@ -12363,26 +12359,26 @@
         <v>21531.578313246653</v>
       </c>
       <c r="I328" s="316">
-        <f t="shared" ref="I328:L328" si="144">SUM(I326:I327)</f>
+        <f t="shared" ref="I328:L328" si="149">SUM(I326:I327)</f>
         <v>23080.52975411075</v>
       </c>
       <c r="J328" s="316">
-        <f t="shared" si="144"/>
+        <f t="shared" si="149"/>
         <v>24988.924312970594</v>
       </c>
       <c r="K328" s="316">
-        <f t="shared" si="144"/>
+        <f t="shared" si="149"/>
         <v>26881.160082245668</v>
       </c>
       <c r="L328" s="316">
-        <f t="shared" si="144"/>
+        <f t="shared" si="149"/>
         <v>28925.874962553447</v>
       </c>
     </row>
     <row r="329" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A329" s="48"/>
       <c r="B329" s="65" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C329" s="70"/>
       <c r="D329" s="70"/>
@@ -12400,26 +12396,26 @@
         <v>25707.388175443608</v>
       </c>
       <c r="I329" s="193">
-        <f t="shared" ref="I329:L329" si="145">I325-I328</f>
+        <f t="shared" ref="I329:L329" si="150">I325-I328</f>
         <v>27135.484036531183</v>
       </c>
       <c r="J329" s="193">
-        <f t="shared" si="145"/>
+        <f t="shared" si="150"/>
         <v>29347.111649527978</v>
       </c>
       <c r="K329" s="193">
-        <f t="shared" si="145"/>
+        <f t="shared" si="150"/>
         <v>31569.6054203577</v>
       </c>
       <c r="L329" s="193">
-        <f t="shared" si="145"/>
+        <f t="shared" si="150"/>
         <v>33971.243472187474</v>
       </c>
     </row>
     <row r="330" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A330" s="48"/>
       <c r="B330" s="65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C330" s="70"/>
       <c r="D330" s="70"/>
@@ -12431,19 +12427,19 @@
         <v>1666.6118245563921</v>
       </c>
       <c r="I330" s="193">
-        <f t="shared" ref="I330:L330" si="146">H329-I329</f>
+        <f t="shared" ref="I330:L330" si="151">H329-I329</f>
         <v>-1428.095861087575</v>
       </c>
       <c r="J330" s="193">
-        <f t="shared" si="146"/>
+        <f t="shared" si="151"/>
         <v>-2211.6276129967955</v>
       </c>
       <c r="K330" s="193">
-        <f t="shared" si="146"/>
+        <f t="shared" si="151"/>
         <v>-2222.4937708297221</v>
       </c>
       <c r="L330" s="193">
-        <f t="shared" si="146"/>
+        <f t="shared" si="151"/>
         <v>-2401.6380518297738</v>
       </c>
     </row>
@@ -12478,7 +12474,7 @@
     <row r="333" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A333" s="48"/>
       <c r="B333" s="85" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C333" s="86"/>
       <c r="D333" s="87"/>
@@ -12508,74 +12504,74 @@
     <row r="335" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A335" s="48"/>
       <c r="B335" s="65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C335" s="65"/>
       <c r="D335" s="65"/>
       <c r="E335" s="65"/>
       <c r="F335" s="366">
-        <f t="shared" ref="F335:L336" si="147">F10</f>
+        <f t="shared" ref="F335:L336" si="152">F10</f>
         <v>125064</v>
       </c>
       <c r="G335" s="366">
-        <f t="shared" si="147"/>
+        <f t="shared" si="152"/>
         <v>154144</v>
       </c>
       <c r="H335" s="366">
-        <f t="shared" si="147"/>
+        <f t="shared" si="152"/>
         <v>149374.94160000002</v>
       </c>
       <c r="I335" s="366">
-        <f t="shared" si="147"/>
+        <f t="shared" si="152"/>
         <v>152822.66492727998</v>
       </c>
       <c r="J335" s="366">
-        <f t="shared" si="147"/>
+        <f t="shared" si="152"/>
         <v>164903.47216894134</v>
       </c>
       <c r="K335" s="366">
-        <f t="shared" si="147"/>
+        <f t="shared" si="152"/>
         <v>177394.66539061809</v>
       </c>
       <c r="L335" s="366">
-        <f t="shared" si="147"/>
+        <f t="shared" si="152"/>
         <v>190893.32666888344</v>
       </c>
     </row>
     <row r="336" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A336" s="48"/>
       <c r="B336" s="65" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C336" s="65"/>
       <c r="D336" s="65"/>
       <c r="E336" s="65"/>
       <c r="F336" s="366">
-        <f t="shared" si="147"/>
+        <f t="shared" si="152"/>
         <v>-85737</v>
       </c>
       <c r="G336" s="366">
-        <f t="shared" si="147"/>
+        <f t="shared" si="152"/>
         <v>-102528</v>
       </c>
       <c r="H336" s="366">
-        <f t="shared" si="147"/>
+        <f t="shared" si="152"/>
         <v>-93128.323392000006</v>
       </c>
       <c r="I336" s="366">
-        <f t="shared" si="147"/>
+        <f t="shared" si="152"/>
         <v>-101619.76654565633</v>
       </c>
       <c r="J336" s="366">
-        <f t="shared" si="147"/>
+        <f t="shared" si="152"/>
         <v>-110158.43502794686</v>
       </c>
       <c r="K336" s="366">
-        <f t="shared" si="147"/>
+        <f t="shared" si="152"/>
         <v>-118498.92580575583</v>
       </c>
       <c r="L336" s="366">
-        <f t="shared" si="147"/>
+        <f t="shared" si="152"/>
         <v>-127511.28214315597</v>
       </c>
     </row>
@@ -12596,7 +12592,7 @@
     <row r="338" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A338" s="48"/>
       <c r="B338" s="65" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C338" s="65"/>
       <c r="D338" s="65"/>
@@ -12614,26 +12610,26 @@
         <v>0.13076733444052316</v>
       </c>
       <c r="I338" s="192">
-        <f t="shared" ref="I338:L338" si="148">H338</f>
+        <f t="shared" ref="I338:L338" si="153">H338</f>
         <v>0.13076733444052316</v>
       </c>
       <c r="J338" s="192">
-        <f t="shared" si="148"/>
+        <f t="shared" si="153"/>
         <v>0.13076733444052316</v>
       </c>
       <c r="K338" s="192">
-        <f t="shared" si="148"/>
+        <f t="shared" si="153"/>
         <v>0.13076733444052316</v>
       </c>
       <c r="L338" s="192">
-        <f t="shared" si="148"/>
+        <f t="shared" si="153"/>
         <v>0.13076733444052316</v>
       </c>
     </row>
     <row r="339" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A339" s="48"/>
       <c r="B339" s="65" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C339" s="65"/>
       <c r="D339" s="65"/>
@@ -12651,26 +12647,26 @@
         <v>0.29749921972534332</v>
       </c>
       <c r="I339" s="192">
-        <f t="shared" ref="I339:L341" si="149">H339</f>
+        <f t="shared" ref="I339:L341" si="154">H339</f>
         <v>0.29749921972534332</v>
       </c>
       <c r="J339" s="192">
-        <f t="shared" si="149"/>
+        <f t="shared" si="154"/>
         <v>0.29749921972534332</v>
       </c>
       <c r="K339" s="192">
-        <f t="shared" si="149"/>
+        <f t="shared" si="154"/>
         <v>0.29749921972534332</v>
       </c>
       <c r="L339" s="192">
-        <f t="shared" si="149"/>
+        <f t="shared" si="154"/>
         <v>0.29749921972534332</v>
       </c>
     </row>
     <row r="340" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A340" s="48"/>
       <c r="B340" s="65" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C340" s="48"/>
       <c r="D340" s="48"/>
@@ -12688,26 +12684,26 @@
         <v>0.16587663857677903</v>
       </c>
       <c r="I340" s="201">
-        <f t="shared" si="149"/>
+        <f t="shared" si="154"/>
         <v>0.16587663857677903</v>
       </c>
       <c r="J340" s="201">
-        <f t="shared" si="149"/>
+        <f t="shared" si="154"/>
         <v>0.16587663857677903</v>
       </c>
       <c r="K340" s="201">
-        <f t="shared" si="149"/>
+        <f t="shared" si="154"/>
         <v>0.16587663857677903</v>
       </c>
       <c r="L340" s="201">
-        <f t="shared" si="149"/>
+        <f t="shared" si="154"/>
         <v>0.16587663857677903</v>
       </c>
     </row>
     <row r="341" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A341" s="48"/>
       <c r="B341" s="65" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C341" s="48"/>
       <c r="D341" s="48"/>
@@ -12717,7 +12713,7 @@
         <v>4.6752062943772786E-2</v>
       </c>
       <c r="G341" s="160">
-        <f t="shared" ref="G341" si="150">G327/G335</f>
+        <f t="shared" ref="G341" si="155">G327/G335</f>
         <v>4.072815030101723E-2</v>
       </c>
       <c r="H341" s="201">
@@ -12725,19 +12721,19 @@
         <v>4.072815030101723E-2</v>
       </c>
       <c r="I341" s="201">
-        <f t="shared" si="149"/>
+        <f t="shared" si="154"/>
         <v>4.072815030101723E-2</v>
       </c>
       <c r="J341" s="201">
-        <f t="shared" si="149"/>
+        <f t="shared" si="154"/>
         <v>4.072815030101723E-2</v>
       </c>
       <c r="K341" s="201">
-        <f t="shared" si="149"/>
+        <f t="shared" si="154"/>
         <v>4.072815030101723E-2</v>
       </c>
       <c r="L341" s="201">
-        <f t="shared" si="149"/>
+        <f t="shared" si="154"/>
         <v>4.072815030101723E-2</v>
       </c>
     </row>
@@ -12758,44 +12754,44 @@
     <row r="343" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A343" s="48"/>
       <c r="B343" s="65" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C343" s="48"/>
       <c r="D343" s="48"/>
       <c r="E343" s="48"/>
       <c r="F343" s="317">
-        <f t="shared" ref="F343:L343" si="151">F323/F335*$G$319</f>
+        <f t="shared" ref="F343:L343" si="156">F323/F335*$G$319</f>
         <v>63.086419753086417</v>
       </c>
       <c r="G343" s="317">
-        <f t="shared" si="151"/>
+        <f t="shared" si="156"/>
         <v>47.730077070790955</v>
       </c>
       <c r="H343" s="317">
-        <f t="shared" si="151"/>
+        <f t="shared" si="156"/>
         <v>47.730077070790955</v>
       </c>
       <c r="I343" s="317">
-        <f t="shared" si="151"/>
+        <f t="shared" si="156"/>
         <v>47.730077070790955</v>
       </c>
       <c r="J343" s="317">
-        <f t="shared" si="151"/>
+        <f t="shared" si="156"/>
         <v>47.730077070790955</v>
       </c>
       <c r="K343" s="317">
-        <f t="shared" si="151"/>
+        <f t="shared" si="156"/>
         <v>47.730077070790955</v>
       </c>
       <c r="L343" s="317">
-        <f t="shared" si="151"/>
+        <f t="shared" si="156"/>
         <v>47.730077070790955</v>
       </c>
     </row>
     <row r="344" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A344" s="48"/>
       <c r="B344" s="65" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C344" s="48"/>
       <c r="D344" s="48"/>
@@ -12813,63 +12809,63 @@
         <v>108.58721519975032</v>
       </c>
       <c r="I344" s="317">
-        <f t="shared" ref="I344:L344" si="152">H344</f>
+        <f t="shared" ref="I344:L344" si="157">H344</f>
         <v>108.58721519975032</v>
       </c>
       <c r="J344" s="317">
-        <f t="shared" si="152"/>
+        <f t="shared" si="157"/>
         <v>108.58721519975032</v>
       </c>
       <c r="K344" s="317">
-        <f t="shared" si="152"/>
+        <f t="shared" si="157"/>
         <v>108.58721519975032</v>
       </c>
       <c r="L344" s="317">
-        <f t="shared" si="152"/>
+        <f t="shared" si="157"/>
         <v>108.58721519975032</v>
       </c>
     </row>
     <row r="345" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A345" s="48"/>
       <c r="B345" s="65" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C345" s="48"/>
       <c r="D345" s="48"/>
       <c r="E345" s="48"/>
       <c r="F345" s="317">
-        <f t="shared" ref="F345:L345" si="153">F326/ABS(F336)*$G$319</f>
+        <f t="shared" ref="F345:L345" si="158">F326/ABS(F336)*$G$319</f>
         <v>72.457632060837213</v>
       </c>
       <c r="G345" s="317">
-        <f t="shared" si="153"/>
+        <f t="shared" si="158"/>
         <v>60.54497308052435</v>
       </c>
       <c r="H345" s="317">
-        <f t="shared" si="153"/>
+        <f t="shared" si="158"/>
         <v>60.54497308052435</v>
       </c>
       <c r="I345" s="317">
-        <f t="shared" si="153"/>
+        <f t="shared" si="158"/>
         <v>60.54497308052435</v>
       </c>
       <c r="J345" s="317">
-        <f t="shared" si="153"/>
+        <f t="shared" si="158"/>
         <v>60.54497308052435</v>
       </c>
       <c r="K345" s="317">
-        <f t="shared" si="153"/>
+        <f t="shared" si="158"/>
         <v>60.54497308052435</v>
       </c>
       <c r="L345" s="317">
-        <f t="shared" si="153"/>
+        <f t="shared" si="158"/>
         <v>60.54497308052435</v>
       </c>
     </row>
     <row r="346" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A346" s="48"/>
       <c r="B346" s="65" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C346" s="48"/>
       <c r="D346" s="48"/>
@@ -12879,7 +12875,7 @@
         <v>17.064502974477065</v>
       </c>
       <c r="G346" s="317">
-        <f t="shared" ref="G346" si="154">(G327/G335)*$G$319</f>
+        <f t="shared" ref="G346" si="159">(G327/G335)*$G$319</f>
         <v>14.865774859871289</v>
       </c>
       <c r="H346" s="317">
@@ -12887,19 +12883,19 @@
         <v>14.865774859871289</v>
       </c>
       <c r="I346" s="317">
-        <f t="shared" ref="I346:L346" si="155">H346</f>
+        <f t="shared" ref="I346:L346" si="160">H346</f>
         <v>14.865774859871289</v>
       </c>
       <c r="J346" s="317">
-        <f t="shared" si="155"/>
+        <f t="shared" si="160"/>
         <v>14.865774859871289</v>
       </c>
       <c r="K346" s="317">
-        <f t="shared" si="155"/>
+        <f t="shared" si="160"/>
         <v>14.865774859871289</v>
       </c>
       <c r="L346" s="317">
-        <f t="shared" si="155"/>
+        <f t="shared" si="160"/>
         <v>14.865774859871289</v>
       </c>
     </row>
@@ -12965,7 +12961,7 @@
     <row r="351" spans="1:12" ht="21" x14ac:dyDescent="0.5">
       <c r="A351" s="48"/>
       <c r="B351" s="52" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C351" s="53"/>
       <c r="D351" s="51"/>
@@ -13002,7 +12998,7 @@
       <c r="D353" s="55"/>
       <c r="E353" s="55"/>
       <c r="F353" s="56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G353" s="56"/>
       <c r="H353" s="56"/>
@@ -13030,32 +13026,32 @@
         <v>2027</v>
       </c>
       <c r="I354" s="58">
-        <f t="shared" ref="I354" si="156">H354+1</f>
+        <f t="shared" ref="I354" si="161">H354+1</f>
         <v>2028</v>
       </c>
       <c r="J354" s="58">
-        <f t="shared" ref="J354" si="157">I354+1</f>
+        <f t="shared" ref="J354" si="162">I354+1</f>
         <v>2029</v>
       </c>
       <c r="K354" s="58">
-        <f t="shared" ref="K354" si="158">J354+1</f>
+        <f t="shared" ref="K354" si="163">J354+1</f>
         <v>2030</v>
       </c>
       <c r="L354" s="58">
-        <f t="shared" ref="L354" si="159">K354+1</f>
+        <f t="shared" ref="L354" si="164">K354+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="355" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A355" s="48"/>
       <c r="B355" s="59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C355" s="59"/>
       <c r="D355" s="59"/>
       <c r="E355" s="59"/>
       <c r="F355" s="60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G355" s="60"/>
       <c r="H355" s="61"/>
@@ -13063,7 +13059,7 @@
       <c r="J355" s="61"/>
       <c r="K355" s="61"/>
       <c r="L355" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="356" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
@@ -13083,7 +13079,7 @@
     <row r="357" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A357" s="48"/>
       <c r="B357" s="85" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C357" s="86"/>
       <c r="D357" s="87"/>
@@ -13113,7 +13109,7 @@
     <row r="359" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A359" s="48"/>
       <c r="B359" s="156" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C359" s="156"/>
       <c r="D359" s="156"/>
@@ -13157,7 +13153,7 @@
     <row r="361" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A361" s="48"/>
       <c r="B361" s="85" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C361" s="86"/>
       <c r="D361" s="87"/>
@@ -13187,7 +13183,7 @@
     <row r="363" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A363" s="48"/>
       <c r="B363" s="65" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C363" s="65"/>
       <c r="D363" s="65"/>
@@ -13205,14 +13201,14 @@
     <row r="364" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A364" s="48"/>
       <c r="B364" s="65" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C364" s="65"/>
       <c r="D364" s="65"/>
       <c r="E364" s="65"/>
       <c r="F364" s="91"/>
       <c r="G364" s="173" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H364" s="172"/>
       <c r="I364" s="172"/>
@@ -13374,7 +13370,7 @@
     <row r="371" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A371" s="48"/>
       <c r="B371" s="132" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C371" s="65"/>
       <c r="D371" s="132"/>
@@ -13386,15 +13382,15 @@
         <v>150</v>
       </c>
       <c r="I371" s="314">
-        <f t="shared" ref="I371:K371" si="160">SUM(I366:I370)</f>
+        <f t="shared" ref="I371:K371" si="165">SUM(I366:I370)</f>
         <v>500</v>
       </c>
       <c r="J371" s="314">
-        <f t="shared" si="160"/>
+        <f t="shared" si="165"/>
         <v>900</v>
       </c>
       <c r="K371" s="314">
-        <f t="shared" si="160"/>
+        <f t="shared" si="165"/>
         <v>1300</v>
       </c>
       <c r="L371" s="314">
@@ -13405,7 +13401,7 @@
     <row r="372" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A372" s="48"/>
       <c r="B372" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C372" s="65"/>
       <c r="D372" s="65"/>
@@ -13436,7 +13432,7 @@
     <row r="373" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A373" s="48"/>
       <c r="B373" s="156" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C373" s="156"/>
       <c r="D373" s="156"/>
@@ -13448,19 +13444,19 @@
         <v>1262.5999999999999</v>
       </c>
       <c r="I373" s="328">
-        <f t="shared" ref="I373:L373" si="161">SUM(I371:I372)</f>
+        <f t="shared" ref="I373:L373" si="166">SUM(I371:I372)</f>
         <v>1612.6</v>
       </c>
       <c r="J373" s="328">
-        <f t="shared" si="161"/>
+        <f t="shared" si="166"/>
         <v>2012.6</v>
       </c>
       <c r="K373" s="328">
-        <f t="shared" si="161"/>
+        <f t="shared" si="166"/>
         <v>2412.6</v>
       </c>
       <c r="L373" s="328">
-        <f t="shared" si="161"/>
+        <f t="shared" si="166"/>
         <v>2812.6</v>
       </c>
     </row>
@@ -13495,7 +13491,7 @@
     <row r="376" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A376" s="48"/>
       <c r="B376" s="85" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C376" s="86"/>
       <c r="D376" s="87"/>
@@ -13525,7 +13521,7 @@
     <row r="378" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A378" s="48"/>
       <c r="B378" s="65" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C378" s="65"/>
       <c r="D378" s="65"/>
@@ -13541,22 +13537,22 @@
         <v>5800.4</v>
       </c>
       <c r="J378" s="331">
-        <f t="shared" ref="J378:L378" si="162">I381</f>
+        <f t="shared" ref="J378:L378" si="167">I381</f>
         <v>6187.7999999999993</v>
       </c>
       <c r="K378" s="331">
-        <f t="shared" si="162"/>
+        <f t="shared" si="167"/>
         <v>6175.1999999999989</v>
       </c>
       <c r="L378" s="331">
-        <f t="shared" si="162"/>
+        <f t="shared" si="167"/>
         <v>5762.5999999999985</v>
       </c>
     </row>
     <row r="379" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A379" s="48"/>
       <c r="B379" s="156" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C379" s="79"/>
       <c r="D379" s="79"/>
@@ -13568,26 +13564,26 @@
         <v>1500</v>
       </c>
       <c r="I379" s="332">
-        <f t="shared" ref="I379:L379" si="163">I359</f>
+        <f t="shared" ref="I379:L379" si="168">I359</f>
         <v>2000</v>
       </c>
       <c r="J379" s="332">
-        <f t="shared" si="163"/>
+        <f t="shared" si="168"/>
         <v>2000</v>
       </c>
       <c r="K379" s="332">
-        <f t="shared" si="163"/>
+        <f t="shared" si="168"/>
         <v>2000</v>
       </c>
       <c r="L379" s="332">
-        <f t="shared" si="163"/>
+        <f t="shared" si="168"/>
         <v>2000</v>
       </c>
     </row>
     <row r="380" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A380" s="48"/>
       <c r="B380" s="74" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C380" s="74"/>
       <c r="D380" s="74"/>
@@ -13599,26 +13595,26 @@
         <v>-1262.5999999999999</v>
       </c>
       <c r="I380" s="392">
-        <f t="shared" ref="I380:L380" si="164">-I373</f>
+        <f t="shared" ref="I380:L380" si="169">-I373</f>
         <v>-1612.6</v>
       </c>
       <c r="J380" s="392">
-        <f t="shared" si="164"/>
+        <f t="shared" si="169"/>
         <v>-2012.6</v>
       </c>
       <c r="K380" s="392">
-        <f t="shared" si="164"/>
+        <f t="shared" si="169"/>
         <v>-2412.6</v>
       </c>
       <c r="L380" s="392">
-        <f t="shared" si="164"/>
+        <f t="shared" si="169"/>
         <v>-2812.6</v>
       </c>
     </row>
     <row r="381" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A381" s="48"/>
       <c r="B381" s="65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C381" s="70"/>
       <c r="D381" s="70"/>
@@ -13663,7 +13659,7 @@
     <row r="383" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A383" s="48"/>
       <c r="B383" s="85" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C383" s="86"/>
       <c r="D383" s="87"/>
@@ -13693,7 +13689,7 @@
     <row r="385" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A385" s="48"/>
       <c r="B385" s="65" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C385" s="70"/>
       <c r="D385" s="65"/>
@@ -13705,26 +13701,26 @@
         <v>-5893</v>
       </c>
       <c r="I385" s="193">
-        <f t="shared" ref="I385:L385" si="165">I389</f>
+        <f t="shared" ref="I385:L385" si="170">I389</f>
         <v>-6396.58</v>
       </c>
       <c r="J385" s="193">
-        <f t="shared" si="165"/>
+        <f t="shared" si="170"/>
         <v>-7430.3747999999996</v>
       </c>
       <c r="K385" s="193">
-        <f t="shared" si="165"/>
+        <f t="shared" si="170"/>
         <v>-8526.1972879999994</v>
       </c>
       <c r="L385" s="193">
-        <f t="shared" si="165"/>
+        <f t="shared" si="170"/>
         <v>-9687.7691252799996</v>
       </c>
     </row>
     <row r="386" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A386" s="48"/>
       <c r="B386" s="65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C386" s="70"/>
       <c r="D386" s="65"/>
@@ -13750,7 +13746,7 @@
     <row r="387" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A387" s="48"/>
       <c r="B387" s="132" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C387" s="131"/>
       <c r="D387" s="132"/>
@@ -13762,19 +13758,19 @@
         <v>-353.58</v>
       </c>
       <c r="I387" s="314">
-        <f t="shared" ref="I387:L387" si="166">I385*I386</f>
+        <f t="shared" ref="I387:L387" si="171">I385*I386</f>
         <v>-383.79480000000001</v>
       </c>
       <c r="J387" s="314">
-        <f t="shared" si="166"/>
+        <f t="shared" si="171"/>
         <v>-445.82248799999996</v>
       </c>
       <c r="K387" s="314">
-        <f t="shared" si="166"/>
+        <f t="shared" si="171"/>
         <v>-511.57183727999995</v>
       </c>
       <c r="L387" s="314">
-        <f t="shared" si="166"/>
+        <f t="shared" si="171"/>
         <v>-581.26614751679995</v>
       </c>
     </row>
@@ -13795,7 +13791,7 @@
     <row r="389" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A389" s="48"/>
       <c r="B389" s="65" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C389" s="65"/>
       <c r="D389" s="65"/>
@@ -13811,22 +13807,22 @@
         <v>-6396.58</v>
       </c>
       <c r="J389" s="331">
-        <f t="shared" ref="J389:L389" si="167">I393</f>
+        <f t="shared" ref="J389:L389" si="172">I393</f>
         <v>-7430.3747999999996</v>
       </c>
       <c r="K389" s="331">
-        <f t="shared" si="167"/>
+        <f t="shared" si="172"/>
         <v>-8526.1972879999994</v>
       </c>
       <c r="L389" s="331">
-        <f t="shared" si="167"/>
+        <f t="shared" si="172"/>
         <v>-9687.7691252799996</v>
       </c>
     </row>
     <row r="390" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A390" s="48"/>
       <c r="B390" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C390" s="65"/>
       <c r="D390" s="65"/>
@@ -13857,7 +13853,7 @@
     <row r="391" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A391" s="48"/>
       <c r="B391" s="65" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C391" s="70"/>
       <c r="D391" s="70"/>
@@ -13869,26 +13865,26 @@
         <v>-353.58</v>
       </c>
       <c r="I391" s="331">
-        <f t="shared" ref="I391:L391" si="168">I387</f>
+        <f t="shared" ref="I391:L391" si="173">I387</f>
         <v>-383.79480000000001</v>
       </c>
       <c r="J391" s="331">
-        <f t="shared" si="168"/>
+        <f t="shared" si="173"/>
         <v>-445.82248799999996</v>
       </c>
       <c r="K391" s="331">
-        <f t="shared" si="168"/>
+        <f t="shared" si="173"/>
         <v>-511.57183727999995</v>
       </c>
       <c r="L391" s="331">
-        <f t="shared" si="168"/>
+        <f t="shared" si="173"/>
         <v>-581.26614751679995</v>
       </c>
     </row>
     <row r="392" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A392" s="48"/>
       <c r="B392" s="65" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C392" s="65"/>
       <c r="D392" s="65"/>
@@ -13914,7 +13910,7 @@
     <row r="393" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A393" s="48"/>
       <c r="B393" s="156" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C393" s="156"/>
       <c r="D393" s="156"/>
@@ -13926,19 +13922,19 @@
         <v>-6396.58</v>
       </c>
       <c r="I393" s="331">
-        <f t="shared" ref="I393:L393" si="169">SUM(I389:I392)</f>
+        <f t="shared" ref="I393:L393" si="174">SUM(I389:I392)</f>
         <v>-7430.3747999999996</v>
       </c>
       <c r="J393" s="331">
-        <f t="shared" si="169"/>
+        <f t="shared" si="174"/>
         <v>-8526.1972879999994</v>
       </c>
       <c r="K393" s="331">
-        <f t="shared" si="169"/>
+        <f t="shared" si="174"/>
         <v>-9687.7691252799996</v>
       </c>
       <c r="L393" s="331">
-        <f t="shared" si="169"/>
+        <f t="shared" si="174"/>
         <v>-10919.0352727968</v>
       </c>
     </row>
@@ -13959,7 +13955,7 @@
     <row r="395" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A395" s="48"/>
       <c r="B395" s="65" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C395" s="65"/>
       <c r="D395" s="65"/>
@@ -13971,19 +13967,19 @@
         <v>996.42000000000007</v>
       </c>
       <c r="I395" s="331">
-        <f t="shared" ref="I395:L395" si="170">I392+I391</f>
+        <f t="shared" ref="I395:L395" si="175">I392+I391</f>
         <v>966.20519999999999</v>
       </c>
       <c r="J395" s="331">
-        <f t="shared" si="170"/>
+        <f t="shared" si="175"/>
         <v>904.17751199999998</v>
       </c>
       <c r="K395" s="331">
-        <f t="shared" si="170"/>
+        <f t="shared" si="175"/>
         <v>838.42816272000005</v>
       </c>
       <c r="L395" s="331">
-        <f t="shared" si="170"/>
+        <f t="shared" si="175"/>
         <v>768.73385248320005</v>
       </c>
     </row>
@@ -14004,7 +14000,7 @@
     <row r="397" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A397" s="48"/>
       <c r="B397" s="65" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C397" s="65"/>
       <c r="D397" s="65"/>
@@ -14035,7 +14031,7 @@
     <row r="398" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A398" s="48"/>
       <c r="B398" s="65" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C398" s="65"/>
       <c r="D398" s="65"/>
@@ -14139,7 +14135,7 @@
     <row r="404" spans="1:12" ht="21" x14ac:dyDescent="0.5">
       <c r="A404" s="48"/>
       <c r="B404" s="52" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C404" s="53"/>
       <c r="D404" s="51"/>
@@ -14176,7 +14172,7 @@
       <c r="D406" s="55"/>
       <c r="E406" s="55"/>
       <c r="F406" s="56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G406" s="56"/>
       <c r="H406" s="56"/>
@@ -14204,32 +14200,32 @@
         <v>2027</v>
       </c>
       <c r="I407" s="58">
-        <f t="shared" ref="I407" si="171">H407+1</f>
+        <f t="shared" ref="I407" si="176">H407+1</f>
         <v>2028</v>
       </c>
       <c r="J407" s="58">
-        <f t="shared" ref="J407" si="172">I407+1</f>
+        <f t="shared" ref="J407" si="177">I407+1</f>
         <v>2029</v>
       </c>
       <c r="K407" s="58">
-        <f t="shared" ref="K407" si="173">J407+1</f>
+        <f t="shared" ref="K407" si="178">J407+1</f>
         <v>2030</v>
       </c>
       <c r="L407" s="58">
-        <f t="shared" ref="L407" si="174">K407+1</f>
+        <f t="shared" ref="L407" si="179">K407+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="408" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A408" s="48"/>
       <c r="B408" s="59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C408" s="59"/>
       <c r="D408" s="59"/>
       <c r="E408" s="59"/>
       <c r="F408" s="60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G408" s="60"/>
       <c r="H408" s="61"/>
@@ -14237,7 +14233,7 @@
       <c r="J408" s="61"/>
       <c r="K408" s="61"/>
       <c r="L408" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="409" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
@@ -14257,7 +14253,7 @@
     <row r="410" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A410" s="48"/>
       <c r="B410" s="65" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C410" s="65"/>
       <c r="D410" s="65"/>
@@ -14292,7 +14288,7 @@
     <row r="411" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A411" s="48"/>
       <c r="B411" s="65" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C411" s="70"/>
       <c r="D411" s="70"/>
@@ -14338,7 +14334,7 @@
     <row r="413" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A413" s="48"/>
       <c r="B413" s="65" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C413" s="70"/>
       <c r="D413" s="70"/>
@@ -14373,7 +14369,7 @@
     <row r="414" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A414" s="48"/>
       <c r="B414" s="65" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C414" s="70"/>
       <c r="D414" s="70"/>
@@ -14419,7 +14415,7 @@
     <row r="416" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A416" s="48"/>
       <c r="B416" s="85" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C416" s="86"/>
       <c r="D416" s="87"/>
@@ -14449,7 +14445,7 @@
     <row r="418" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A418" s="48"/>
       <c r="B418" s="65" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C418" s="65"/>
       <c r="D418" s="65"/>
@@ -14467,14 +14463,14 @@
     <row r="419" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A419" s="48"/>
       <c r="B419" s="65" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C419" s="65"/>
       <c r="D419" s="65"/>
       <c r="E419" s="185"/>
       <c r="F419" s="117"/>
       <c r="G419" s="182" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H419" s="118"/>
       <c r="I419" s="118"/>
@@ -14636,7 +14632,7 @@
     <row r="426" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A426" s="48"/>
       <c r="B426" s="132" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C426" s="131"/>
       <c r="D426" s="132"/>
@@ -14644,19 +14640,19 @@
       <c r="F426" s="183"/>
       <c r="G426" s="183"/>
       <c r="H426" s="337">
-        <f t="shared" ref="H426:K426" si="175">SUM(H421:H425)</f>
+        <f t="shared" ref="H426:K426" si="180">SUM(H421:H425)</f>
         <v>141.90619452000001</v>
       </c>
       <c r="I426" s="337">
-        <f t="shared" si="175"/>
+        <f t="shared" si="180"/>
         <v>428.99392072091598</v>
       </c>
       <c r="J426" s="337">
-        <f t="shared" si="175"/>
+        <f t="shared" si="180"/>
         <v>730.83375096232623</v>
       </c>
       <c r="K426" s="337">
-        <f t="shared" si="175"/>
+        <f t="shared" si="180"/>
         <v>1056.0169816439077</v>
       </c>
       <c r="L426" s="337">
@@ -14667,7 +14663,7 @@
     <row r="427" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A427" s="48"/>
       <c r="B427" s="65" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C427" s="65"/>
       <c r="D427" s="65"/>
@@ -14698,7 +14694,7 @@
     <row r="428" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A428" s="48"/>
       <c r="B428" s="132" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C428" s="132"/>
       <c r="D428" s="132"/>
@@ -14710,19 +14706,19 @@
         <v>777.30619451999996</v>
       </c>
       <c r="I428" s="337">
-        <f t="shared" ref="I428:L428" si="176">SUM(I426:I427)</f>
+        <f t="shared" ref="I428:L428" si="181">SUM(I426:I427)</f>
         <v>1064.393920720916</v>
       </c>
       <c r="J428" s="337">
-        <f t="shared" si="176"/>
+        <f t="shared" si="181"/>
         <v>1366.2337509623262</v>
       </c>
       <c r="K428" s="337">
-        <f t="shared" si="176"/>
+        <f t="shared" si="181"/>
         <v>1691.4169816439075</v>
       </c>
       <c r="L428" s="337">
-        <f t="shared" si="176"/>
+        <f t="shared" si="181"/>
         <v>2041.2905741004342</v>
       </c>
     </row>
@@ -14743,7 +14739,7 @@
     <row r="430" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A430" s="48"/>
       <c r="B430" s="85" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C430" s="86"/>
       <c r="D430" s="87"/>
@@ -14773,7 +14769,7 @@
     <row r="432" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A432" s="48"/>
       <c r="B432" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C432" s="70"/>
       <c r="D432" s="70"/>
@@ -14789,22 +14785,22 @@
         <v>8414.8176958799995</v>
       </c>
       <c r="J432" s="193">
-        <f t="shared" ref="J432:L432" si="177">I435</f>
+        <f t="shared" ref="J432:L432" si="182">I435</f>
         <v>10254.054408777403</v>
       </c>
       <c r="K432" s="193">
-        <f t="shared" si="177"/>
+        <f t="shared" si="182"/>
         <v>12020.986629024961</v>
       </c>
       <c r="L432" s="193">
-        <f t="shared" si="177"/>
+        <f t="shared" si="182"/>
         <v>13700.068289802797</v>
       </c>
     </row>
     <row r="433" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A433" s="48"/>
       <c r="B433" s="65" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C433" s="70"/>
       <c r="D433" s="70"/>
@@ -14816,26 +14812,26 @@
         <v>2838.1238904000002</v>
       </c>
       <c r="I433" s="193">
-        <f t="shared" ref="I433:L433" si="178">I410</f>
+        <f t="shared" ref="I433:L433" si="183">I410</f>
         <v>2903.6306336183197</v>
       </c>
       <c r="J433" s="193">
-        <f t="shared" si="178"/>
+        <f t="shared" si="183"/>
         <v>3133.1659712098854</v>
       </c>
       <c r="K433" s="193">
-        <f t="shared" si="178"/>
+        <f t="shared" si="183"/>
         <v>3370.4986424217436</v>
       </c>
       <c r="L433" s="193">
-        <f t="shared" si="178"/>
+        <f t="shared" si="183"/>
         <v>3626.9732067087853</v>
       </c>
     </row>
     <row r="434" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A434" s="48"/>
       <c r="B434" s="126" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C434" s="187"/>
       <c r="D434" s="187"/>
@@ -14847,26 +14843,26 @@
         <v>-777.30619451999996</v>
       </c>
       <c r="I434" s="329">
-        <f t="shared" ref="I434:L434" si="179">-I428</f>
+        <f t="shared" ref="I434:L434" si="184">-I428</f>
         <v>-1064.393920720916</v>
       </c>
       <c r="J434" s="329">
-        <f t="shared" si="179"/>
+        <f t="shared" si="184"/>
         <v>-1366.2337509623262</v>
       </c>
       <c r="K434" s="329">
-        <f t="shared" si="179"/>
+        <f t="shared" si="184"/>
         <v>-1691.4169816439075</v>
       </c>
       <c r="L434" s="329">
-        <f t="shared" si="179"/>
+        <f t="shared" si="184"/>
         <v>-2041.2905741004342</v>
       </c>
     </row>
     <row r="435" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A435" s="48"/>
       <c r="B435" s="65" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C435" s="65"/>
       <c r="D435" s="65"/>
@@ -14911,7 +14907,7 @@
     <row r="437" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A437" s="48"/>
       <c r="B437" s="85" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C437" s="86"/>
       <c r="D437" s="87"/>
@@ -14941,7 +14937,7 @@
     <row r="439" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A439" s="48"/>
       <c r="B439" s="70" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C439" s="70"/>
       <c r="D439" s="65"/>
@@ -14957,7 +14953,7 @@
     <row r="440" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A440" s="48"/>
       <c r="B440" s="65" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C440" s="70"/>
       <c r="D440" s="65"/>
@@ -14987,7 +14983,7 @@
     <row r="442" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A442" s="48"/>
       <c r="B442" s="65" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C442" s="65"/>
       <c r="D442" s="65"/>
@@ -15005,14 +15001,14 @@
     <row r="443" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A443" s="48"/>
       <c r="B443" s="70" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C443" s="70"/>
       <c r="D443" s="70"/>
       <c r="E443" s="70"/>
       <c r="F443" s="70"/>
       <c r="G443" s="182" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H443" s="102"/>
       <c r="I443" s="102"/>
@@ -15174,7 +15170,7 @@
     <row r="450" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A450" s="48"/>
       <c r="B450" s="132" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C450" s="131"/>
       <c r="D450" s="131"/>
@@ -15182,19 +15178,19 @@
       <c r="F450" s="186"/>
       <c r="G450" s="186"/>
       <c r="H450" s="337">
-        <f t="shared" ref="H450:K450" si="180">SUM(H445:H449)</f>
+        <f t="shared" ref="H450:K450" si="185">SUM(H445:H449)</f>
         <v>149.37494160000003</v>
       </c>
       <c r="I450" s="337">
-        <f t="shared" si="180"/>
+        <f t="shared" si="185"/>
         <v>451.57254812728002</v>
       </c>
       <c r="J450" s="337">
-        <f t="shared" si="180"/>
+        <f t="shared" si="185"/>
         <v>769.29868522350137</v>
       </c>
       <c r="K450" s="337">
-        <f t="shared" si="180"/>
+        <f t="shared" si="185"/>
         <v>1111.5968227830608</v>
       </c>
       <c r="L450" s="337">
@@ -15205,7 +15201,7 @@
     <row r="451" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A451" s="48"/>
       <c r="B451" s="126" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C451" s="187"/>
       <c r="D451" s="187"/>
@@ -15236,7 +15232,7 @@
     <row r="452" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A452" s="48"/>
       <c r="B452" s="65" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C452" s="70"/>
       <c r="D452" s="70"/>
@@ -15248,19 +15244,19 @@
         <v>1711.5749416000001</v>
       </c>
       <c r="I452" s="337">
-        <f t="shared" ref="I452:L452" si="181">SUM(I450:I451)</f>
+        <f t="shared" ref="I452:L452" si="186">SUM(I450:I451)</f>
         <v>2013.7725481272801</v>
       </c>
       <c r="J452" s="337">
-        <f t="shared" si="181"/>
+        <f t="shared" si="186"/>
         <v>2331.4986852235015</v>
       </c>
       <c r="K452" s="337">
-        <f t="shared" si="181"/>
+        <f t="shared" si="186"/>
         <v>2673.7968227830606</v>
       </c>
       <c r="L452" s="337">
-        <f t="shared" si="181"/>
+        <f t="shared" si="186"/>
         <v>3042.0848148425621</v>
       </c>
     </row>
@@ -15281,7 +15277,7 @@
     <row r="454" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A454" s="48"/>
       <c r="B454" s="85" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C454" s="86"/>
       <c r="D454" s="87"/>
@@ -15311,7 +15307,7 @@
     <row r="456" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A456" s="48"/>
       <c r="B456" s="65" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C456" s="70"/>
       <c r="D456" s="70"/>
@@ -15327,22 +15323,22 @@
         <v>34425.174474400003</v>
       </c>
       <c r="J456" s="193">
-        <f t="shared" ref="J456:L456" si="182">I462</f>
+        <f t="shared" ref="J456:L456" si="187">I462</f>
         <v>33939.628575545525</v>
       </c>
       <c r="K456" s="193">
-        <f t="shared" si="182"/>
+        <f t="shared" si="187"/>
         <v>33257.164612011438</v>
       </c>
       <c r="L456" s="193">
-        <f t="shared" si="182"/>
+        <f t="shared" si="187"/>
         <v>32357.314443134557</v>
       </c>
     </row>
     <row r="457" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A457" s="48"/>
       <c r="B457" s="74" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C457" s="78"/>
       <c r="D457" s="78"/>
@@ -15357,22 +15353,22 @@
         <v>26832</v>
       </c>
       <c r="J457" s="315">
-        <f t="shared" ref="J457:L457" si="183">I457</f>
+        <f t="shared" ref="J457:L457" si="188">I457</f>
         <v>26832</v>
       </c>
       <c r="K457" s="315">
-        <f t="shared" si="183"/>
+        <f t="shared" si="188"/>
         <v>26832</v>
       </c>
       <c r="L457" s="315">
-        <f t="shared" si="183"/>
+        <f t="shared" si="188"/>
         <v>26832</v>
       </c>
     </row>
     <row r="458" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A458" s="48"/>
       <c r="B458" s="65" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C458" s="70"/>
       <c r="D458" s="70"/>
@@ -15384,26 +15380,26 @@
         <v>7811</v>
       </c>
       <c r="I458" s="193">
-        <f t="shared" ref="I458:L458" si="184">I456-I457</f>
+        <f t="shared" ref="I458:L458" si="189">I456-I457</f>
         <v>7593.1744744000025</v>
       </c>
       <c r="J458" s="193">
-        <f t="shared" si="184"/>
+        <f t="shared" si="189"/>
         <v>7107.6285755455247</v>
       </c>
       <c r="K458" s="193">
-        <f t="shared" si="184"/>
+        <f t="shared" si="189"/>
         <v>6425.1646120114383</v>
       </c>
       <c r="L458" s="193">
-        <f t="shared" si="184"/>
+        <f t="shared" si="189"/>
         <v>5525.3144431345572</v>
       </c>
     </row>
     <row r="459" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A459" s="48"/>
       <c r="B459" s="65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C459" s="70"/>
       <c r="D459" s="70"/>
@@ -15434,7 +15430,7 @@
     <row r="460" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A460" s="48"/>
       <c r="B460" s="65" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C460" s="70"/>
       <c r="D460" s="70"/>
@@ -15446,26 +15442,26 @@
         <v>-1711.5749416000001</v>
       </c>
       <c r="I460" s="193">
-        <f t="shared" ref="I460:L460" si="185">-I452</f>
+        <f t="shared" ref="I460:L460" si="190">-I452</f>
         <v>-2013.7725481272801</v>
       </c>
       <c r="J460" s="193">
-        <f t="shared" si="185"/>
+        <f t="shared" si="190"/>
         <v>-2331.4986852235015</v>
       </c>
       <c r="K460" s="193">
-        <f t="shared" si="185"/>
+        <f t="shared" si="190"/>
         <v>-2673.7968227830606</v>
       </c>
       <c r="L460" s="193">
-        <f t="shared" si="185"/>
+        <f t="shared" si="190"/>
         <v>-3042.0848148425621</v>
       </c>
     </row>
     <row r="461" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A461" s="48"/>
       <c r="B461" s="156" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C461" s="156"/>
       <c r="D461" s="156"/>
@@ -15477,26 +15473,26 @@
         <v>7593.1744744000007</v>
       </c>
       <c r="I461" s="328">
-        <f t="shared" ref="I461:L461" si="186">SUM(I458:I460)</f>
+        <f t="shared" ref="I461:L461" si="191">SUM(I458:I460)</f>
         <v>7107.6285755455219</v>
       </c>
       <c r="J461" s="328">
-        <f t="shared" si="186"/>
+        <f t="shared" si="191"/>
         <v>6425.1646120114365</v>
       </c>
       <c r="K461" s="328">
-        <f t="shared" si="186"/>
+        <f t="shared" si="191"/>
         <v>5525.314443134559</v>
       </c>
       <c r="L461" s="328">
-        <f t="shared" si="186"/>
+        <f t="shared" si="191"/>
         <v>4392.1628949808301</v>
       </c>
     </row>
     <row r="462" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A462" s="48"/>
       <c r="B462" s="65" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C462" s="70"/>
       <c r="D462" s="70"/>
@@ -15508,19 +15504,19 @@
         <v>34425.174474400003</v>
       </c>
       <c r="I462" s="193">
-        <f t="shared" ref="I462:L462" si="187">I461+I457</f>
+        <f t="shared" ref="I462:L462" si="192">I461+I457</f>
         <v>33939.628575545525</v>
       </c>
       <c r="J462" s="193">
-        <f t="shared" si="187"/>
+        <f t="shared" si="192"/>
         <v>33257.164612011438</v>
       </c>
       <c r="K462" s="193">
-        <f t="shared" si="187"/>
+        <f t="shared" si="192"/>
         <v>32357.314443134557</v>
       </c>
       <c r="L462" s="193">
-        <f t="shared" si="187"/>
+        <f t="shared" si="192"/>
         <v>31224.162894980829</v>
       </c>
     </row>
@@ -15572,7 +15568,7 @@
     <row r="466" spans="1:12" ht="21" x14ac:dyDescent="0.5">
       <c r="A466" s="48"/>
       <c r="B466" s="52" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C466" s="53"/>
       <c r="D466" s="51"/>
@@ -15609,7 +15605,7 @@
       <c r="D468" s="55"/>
       <c r="E468" s="55"/>
       <c r="F468" s="56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G468" s="56"/>
       <c r="H468" s="56"/>
@@ -15637,32 +15633,32 @@
         <v>2027</v>
       </c>
       <c r="I469" s="58">
-        <f t="shared" ref="I469" si="188">H469+1</f>
+        <f t="shared" ref="I469" si="193">H469+1</f>
         <v>2028</v>
       </c>
       <c r="J469" s="58">
-        <f t="shared" ref="J469" si="189">I469+1</f>
+        <f t="shared" ref="J469" si="194">I469+1</f>
         <v>2029</v>
       </c>
       <c r="K469" s="58">
-        <f t="shared" ref="K469" si="190">J469+1</f>
+        <f t="shared" ref="K469" si="195">J469+1</f>
         <v>2030</v>
       </c>
       <c r="L469" s="58">
-        <f t="shared" ref="L469" si="191">K469+1</f>
+        <f t="shared" ref="L469" si="196">K469+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="470" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A470" s="48"/>
       <c r="B470" s="59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C470" s="59"/>
       <c r="D470" s="59"/>
       <c r="E470" s="59"/>
       <c r="F470" s="60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G470" s="60"/>
       <c r="H470" s="61"/>
@@ -15670,7 +15666,7 @@
       <c r="J470" s="61"/>
       <c r="K470" s="61"/>
       <c r="L470" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="471" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
@@ -15690,7 +15686,7 @@
     <row r="472" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A472" s="48"/>
       <c r="B472" s="65" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C472" s="70"/>
       <c r="D472" s="70"/>
@@ -15721,7 +15717,7 @@
     <row r="473" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A473" s="48"/>
       <c r="B473" s="65" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C473" s="70"/>
       <c r="D473" s="70"/>
@@ -15747,7 +15743,7 @@
     <row r="474" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A474" s="48"/>
       <c r="B474" s="65" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C474" s="70"/>
       <c r="D474" s="70"/>
@@ -15778,7 +15774,7 @@
     <row r="475" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A475" s="48"/>
       <c r="B475" s="132" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C475" s="132"/>
       <c r="D475" s="131"/>
@@ -15790,26 +15786,26 @@
         <v>2833.6264599999995</v>
       </c>
       <c r="I475" s="314">
-        <f t="shared" ref="I475:L475" si="192">I472-I474</f>
+        <f t="shared" ref="I475:L475" si="197">I472-I474</f>
         <v>546.00500585799819</v>
       </c>
       <c r="J475" s="314">
-        <f t="shared" si="192"/>
+        <f t="shared" si="197"/>
         <v>-1289.4011197639511</v>
       </c>
       <c r="K475" s="314">
-        <f t="shared" si="192"/>
+        <f t="shared" si="197"/>
         <v>-1216.4573425419194</v>
       </c>
       <c r="L475" s="314">
-        <f t="shared" si="192"/>
+        <f t="shared" si="197"/>
         <v>-1175.8946946766337</v>
       </c>
     </row>
     <row r="476" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A476" s="48"/>
       <c r="B476" s="65" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C476" s="65"/>
       <c r="D476" s="65"/>
@@ -15840,7 +15836,7 @@
     <row r="477" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A477" s="48"/>
       <c r="B477" s="132" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C477" s="131"/>
       <c r="D477" s="132"/>
@@ -15852,26 +15848,26 @@
         <v>12183.290259876399</v>
       </c>
       <c r="I477" s="315">
-        <f t="shared" ref="I477:L477" si="193">SUM(I475:I476)</f>
+        <f t="shared" ref="I477:L477" si="198">SUM(I475:I476)</f>
         <v>302.98130080455121</v>
       </c>
       <c r="J477" s="315">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-3149.5454313432574</v>
       </c>
       <c r="K477" s="315">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-4056.3805438789714</v>
       </c>
       <c r="L477" s="315">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-5434.1044799724332</v>
       </c>
     </row>
     <row r="478" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A478" s="48"/>
       <c r="B478" s="79" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C478" s="156"/>
       <c r="D478" s="156"/>
@@ -15883,19 +15879,19 @@
         <v>12183.290259876399</v>
       </c>
       <c r="I478" s="340">
-        <f t="shared" ref="I478:L478" si="194">I477</f>
+        <f t="shared" ref="I478:L478" si="199">I477</f>
         <v>302.98130080455121</v>
       </c>
       <c r="J478" s="340">
-        <f t="shared" si="194"/>
+        <f t="shared" si="199"/>
         <v>-3149.5454313432574</v>
       </c>
       <c r="K478" s="340">
-        <f t="shared" si="194"/>
+        <f t="shared" si="199"/>
         <v>-4056.3805438789714</v>
       </c>
       <c r="L478" s="340">
-        <f t="shared" si="194"/>
+        <f t="shared" si="199"/>
         <v>-5434.1044799724332</v>
       </c>
     </row>
@@ -15916,7 +15912,7 @@
     <row r="480" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A480" s="48"/>
       <c r="B480" s="205" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C480" s="70"/>
       <c r="D480" s="70"/>
@@ -15932,7 +15928,7 @@
     <row r="481" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A481" s="48"/>
       <c r="B481" s="65" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C481" s="65"/>
       <c r="D481" s="70"/>
@@ -15960,7 +15956,7 @@
         <v>0</v>
       </c>
       <c r="R481" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="482" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
@@ -15980,7 +15976,7 @@
     <row r="483" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A483" s="48"/>
       <c r="B483" s="85" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C483" s="86"/>
       <c r="D483" s="87"/>
@@ -16010,7 +16006,7 @@
     <row r="485" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A485" s="48"/>
       <c r="B485" s="208" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C485" s="65"/>
       <c r="D485" s="65"/>
@@ -16026,7 +16022,7 @@
     <row r="486" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A486" s="48"/>
       <c r="B486" s="156" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C486" s="156"/>
       <c r="D486" s="156"/>
@@ -16042,22 +16038,22 @@
         <v>1710.0832801236011</v>
       </c>
       <c r="J486" s="203">
-        <f t="shared" ref="J486:L486" si="195">I489</f>
+        <f t="shared" ref="J486:L486" si="200">I489</f>
         <v>1710.0832801236011</v>
       </c>
       <c r="K486" s="203">
-        <f t="shared" si="195"/>
+        <f t="shared" si="200"/>
         <v>4859.6287114668585</v>
       </c>
       <c r="L486" s="203">
-        <f t="shared" si="195"/>
+        <f t="shared" si="200"/>
         <v>8916.0092553458308</v>
       </c>
     </row>
     <row r="487" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A487" s="48"/>
       <c r="B487" s="65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C487" s="70"/>
       <c r="D487" s="70"/>
@@ -16069,26 +16065,26 @@
         <v>0</v>
       </c>
       <c r="I487" s="92">
-        <f t="shared" ref="I487:L487" si="196">MIN(MAX(0, -I478), I491-I486)</f>
+        <f t="shared" ref="I487:L487" si="201">MIN(MAX(0, -I478), I491-I486)</f>
         <v>0</v>
       </c>
       <c r="J487" s="92">
-        <f t="shared" si="196"/>
+        <f t="shared" si="201"/>
         <v>3149.5454313432574</v>
       </c>
       <c r="K487" s="92">
-        <f t="shared" si="196"/>
+        <f t="shared" si="201"/>
         <v>4056.3805438789714</v>
       </c>
       <c r="L487" s="92">
-        <f t="shared" si="196"/>
+        <f t="shared" si="201"/>
         <v>5434.1044799724332</v>
       </c>
     </row>
     <row r="488" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A488" s="48"/>
       <c r="B488" s="74" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C488" s="78"/>
       <c r="D488" s="78"/>
@@ -16100,26 +16096,26 @@
         <v>-8448.9167198763989</v>
       </c>
       <c r="I488" s="199">
-        <f t="shared" ref="I488:L488" si="197">I481</f>
+        <f t="shared" ref="I488:L488" si="202">I481</f>
         <v>0</v>
       </c>
       <c r="J488" s="199">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0</v>
       </c>
       <c r="K488" s="199">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0</v>
       </c>
       <c r="L488" s="199">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0</v>
       </c>
     </row>
     <row r="489" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A489" s="48"/>
       <c r="B489" s="65" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C489" s="70"/>
       <c r="D489" s="65"/>
@@ -16133,19 +16129,19 @@
         <v>1710.0832801236011</v>
       </c>
       <c r="I489" s="202">
-        <f t="shared" ref="I489:L489" si="198">SUM(I486:I488)</f>
+        <f t="shared" ref="I489:L489" si="203">SUM(I486:I488)</f>
         <v>1710.0832801236011</v>
       </c>
       <c r="J489" s="202">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>4859.6287114668585</v>
       </c>
       <c r="K489" s="202">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>8916.0092553458308</v>
       </c>
       <c r="L489" s="202">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>14350.113735318264</v>
       </c>
     </row>
@@ -16166,7 +16162,7 @@
     <row r="491" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A491" s="48"/>
       <c r="B491" s="65" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C491" s="70"/>
       <c r="D491" s="65"/>
@@ -16180,26 +16176,26 @@
         <v>15000</v>
       </c>
       <c r="I491" s="193">
-        <f t="shared" ref="I491:L491" si="199">H491</f>
+        <f t="shared" ref="I491:L491" si="204">H491</f>
         <v>15000</v>
       </c>
       <c r="J491" s="193">
-        <f t="shared" si="199"/>
+        <f t="shared" si="204"/>
         <v>15000</v>
       </c>
       <c r="K491" s="193">
-        <f t="shared" si="199"/>
+        <f t="shared" si="204"/>
         <v>15000</v>
       </c>
       <c r="L491" s="193">
-        <f t="shared" si="199"/>
+        <f t="shared" si="204"/>
         <v>15000</v>
       </c>
     </row>
     <row r="492" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A492" s="48"/>
       <c r="B492" s="65" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C492" s="65"/>
       <c r="D492" s="65"/>
@@ -16210,23 +16206,23 @@
         <v>4841</v>
       </c>
       <c r="H492" s="193">
-        <f t="shared" ref="H492:L492" si="200">H491-H489</f>
+        <f t="shared" ref="H492:L492" si="205">H491-H489</f>
         <v>13289.916719876399</v>
       </c>
       <c r="I492" s="193">
-        <f t="shared" si="200"/>
+        <f t="shared" si="205"/>
         <v>13289.916719876399</v>
       </c>
       <c r="J492" s="193">
-        <f t="shared" si="200"/>
+        <f t="shared" si="205"/>
         <v>10140.371288533141</v>
       </c>
       <c r="K492" s="193">
-        <f t="shared" si="200"/>
+        <f t="shared" si="205"/>
         <v>6083.9907446541692</v>
       </c>
       <c r="L492" s="193">
-        <f t="shared" si="200"/>
+        <f t="shared" si="205"/>
         <v>649.88626468173607</v>
       </c>
     </row>
@@ -16247,7 +16243,7 @@
     <row r="494" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="48"/>
       <c r="B494" s="85" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C494" s="86"/>
       <c r="D494" s="87"/>
@@ -16277,7 +16273,7 @@
     <row r="496" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="48"/>
       <c r="B496" s="65" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C496" s="65"/>
       <c r="D496" s="65"/>
@@ -16303,7 +16299,7 @@
     <row r="497" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A497" s="48"/>
       <c r="B497" s="65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C497" s="65"/>
       <c r="D497" s="65"/>
@@ -16318,22 +16314,22 @@
         <v>0.01</v>
       </c>
       <c r="J497" s="223">
-        <f t="shared" ref="J497:L497" si="201">I497</f>
+        <f t="shared" ref="J497:L497" si="206">I497</f>
         <v>0.01</v>
       </c>
       <c r="K497" s="223">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>0.01</v>
       </c>
       <c r="L497" s="223">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>0.01</v>
       </c>
     </row>
     <row r="498" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A498" s="48"/>
       <c r="B498" s="65" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C498" s="65"/>
       <c r="D498" s="65"/>
@@ -16348,15 +16344,15 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="J498" s="225">
-        <f t="shared" ref="J498:L498" si="202">I498</f>
+        <f t="shared" ref="J498:L498" si="207">I498</f>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="K498" s="225">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L498" s="225">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
@@ -16377,7 +16373,7 @@
     <row r="500" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A500" s="48"/>
       <c r="B500" s="65" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C500" s="65"/>
       <c r="D500" s="65"/>
@@ -16422,7 +16418,7 @@
     <row r="502" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A502" s="48"/>
       <c r="B502" s="85" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C502" s="86"/>
       <c r="D502" s="87"/>
@@ -16452,7 +16448,7 @@
     <row r="504" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A504" s="48"/>
       <c r="B504" s="65" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C504" s="65"/>
       <c r="D504" s="65"/>
@@ -16460,7 +16456,7 @@
       <c r="F504" s="65"/>
       <c r="G504" s="120"/>
       <c r="H504" s="92">
-        <f t="shared" ref="H504" si="203">G492*H498</f>
+        <f t="shared" ref="H504" si="208">G492*H498</f>
         <v>24.205000000000002</v>
       </c>
       <c r="I504" s="92">
@@ -16468,15 +16464,15 @@
         <v>66.449583599381995</v>
       </c>
       <c r="J504" s="92">
-        <f t="shared" ref="J504:L504" si="204">I492*J498</f>
+        <f t="shared" ref="J504:L504" si="209">I492*J498</f>
         <v>66.449583599381995</v>
       </c>
       <c r="K504" s="92">
-        <f t="shared" si="204"/>
+        <f t="shared" si="209"/>
         <v>50.701856442665701</v>
       </c>
       <c r="L504" s="92">
-        <f t="shared" si="204"/>
+        <f t="shared" si="209"/>
         <v>30.419953723270847</v>
       </c>
     </row>
@@ -16497,7 +16493,7 @@
     <row r="506" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A506" s="48"/>
       <c r="B506" s="65" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C506" s="65"/>
       <c r="D506" s="65"/>
@@ -16509,26 +16505,26 @@
         <v>883.83299999999997</v>
       </c>
       <c r="I506" s="92">
-        <f t="shared" ref="I506:L506" si="205">I500*I486</f>
+        <f t="shared" ref="I506:L506" si="210">I500*I486</f>
         <v>155.61757849124768</v>
       </c>
       <c r="J506" s="92">
-        <f t="shared" si="205"/>
+        <f t="shared" si="210"/>
         <v>162.45791161174211</v>
       </c>
       <c r="K506" s="92">
-        <f t="shared" si="205"/>
+        <f t="shared" si="210"/>
         <v>461.66472758935157</v>
       </c>
       <c r="L506" s="92">
-        <f t="shared" si="205"/>
+        <f t="shared" si="210"/>
         <v>820.27285149181637</v>
       </c>
     </row>
     <row r="507" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A507" s="48"/>
       <c r="B507" s="156" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C507" s="156"/>
       <c r="D507" s="156"/>
@@ -16540,19 +16536,19 @@
         <v>908.03800000000001</v>
       </c>
       <c r="I507" s="238">
-        <f t="shared" ref="I507:L507" si="206">SUM(I504:I506)</f>
+        <f t="shared" ref="I507:L507" si="211">SUM(I504:I506)</f>
         <v>222.06716209062967</v>
       </c>
       <c r="J507" s="238">
-        <f t="shared" si="206"/>
+        <f t="shared" si="211"/>
         <v>228.90749521112411</v>
       </c>
       <c r="K507" s="238">
-        <f t="shared" si="206"/>
+        <f t="shared" si="211"/>
         <v>512.36658403201727</v>
       </c>
       <c r="L507" s="238">
-        <f t="shared" si="206"/>
+        <f t="shared" si="211"/>
         <v>850.69280521508722</v>
       </c>
     </row>
@@ -16573,7 +16569,7 @@
     <row r="509" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A509" s="48"/>
       <c r="B509" s="85" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C509" s="86"/>
       <c r="D509" s="87"/>
@@ -16617,7 +16613,7 @@
     <row r="512" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A512" s="48"/>
       <c r="B512" s="65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C512" s="65"/>
       <c r="D512" s="65"/>
@@ -16648,7 +16644,7 @@
     <row r="513" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A513" s="48"/>
       <c r="B513" s="156" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C513" s="156"/>
       <c r="D513" s="156"/>
@@ -16660,19 +16656,19 @@
         <v>65.680000000000007</v>
       </c>
       <c r="I513" s="238">
-        <f t="shared" ref="I513" si="207">SUM(I512)</f>
+        <f t="shared" ref="I513" si="212">SUM(I512)</f>
         <v>43.665716290399978</v>
       </c>
       <c r="J513" s="238">
-        <f t="shared" ref="J513" si="208">SUM(J512)</f>
+        <f t="shared" ref="J513" si="213">SUM(J512)</f>
         <v>28.331856844595823</v>
       </c>
       <c r="K513" s="238">
-        <f t="shared" ref="K513" si="209">SUM(K512)</f>
+        <f t="shared" ref="K513" si="214">SUM(K512)</f>
         <v>32.18409292223533</v>
       </c>
       <c r="L513" s="238">
-        <f t="shared" ref="L513" si="210">SUM(L512)</f>
+        <f t="shared" ref="L513" si="215">SUM(L512)</f>
         <v>35.964384720454525</v>
       </c>
     </row>
@@ -16693,7 +16689,7 @@
     <row r="515" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A515" s="48"/>
       <c r="B515" s="85" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C515" s="86"/>
       <c r="D515" s="87"/>
@@ -16728,22 +16724,22 @@
       <c r="E517" s="209"/>
       <c r="F517" s="209"/>
       <c r="G517" s="209" t="s">
+        <v>152</v>
+      </c>
+      <c r="H517" s="209" t="s">
+        <v>157</v>
+      </c>
+      <c r="I517" s="210" t="s">
         <v>153</v>
       </c>
-      <c r="H517" s="209" t="s">
-        <v>158</v>
-      </c>
-      <c r="I517" s="210" t="s">
+      <c r="J517" s="210" t="s">
         <v>154</v>
       </c>
-      <c r="J517" s="210" t="s">
-        <v>155</v>
-      </c>
       <c r="K517" s="210" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L517" s="210" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="518" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
@@ -16754,22 +16750,22 @@
       <c r="E518" s="212"/>
       <c r="F518" s="212"/>
       <c r="G518" s="212" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H518" s="212" t="s">
+        <v>158</v>
+      </c>
+      <c r="I518" s="213" t="s">
         <v>159</v>
       </c>
-      <c r="I518" s="213" t="s">
-        <v>160</v>
-      </c>
       <c r="J518" s="213" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K518" s="213" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L518" s="213" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="519" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
@@ -16789,7 +16785,7 @@
     <row r="520" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A520" s="48"/>
       <c r="B520" s="216" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C520" s="216"/>
       <c r="D520" s="216"/>
@@ -16802,13 +16798,13 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="I520" s="217" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J520" s="217" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K520" s="217" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L520" s="219">
         <v>1</v>
@@ -16890,7 +16886,7 @@
     <row r="526" spans="1:12" ht="21" x14ac:dyDescent="0.5">
       <c r="A526" s="48"/>
       <c r="B526" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C526" s="53"/>
       <c r="D526" s="51"/>
@@ -16927,7 +16923,7 @@
       <c r="D528" s="55"/>
       <c r="E528" s="55"/>
       <c r="F528" s="56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G528" s="56"/>
       <c r="H528" s="56"/>
@@ -16953,32 +16949,32 @@
         <v>2027</v>
       </c>
       <c r="I529" s="58">
-        <f t="shared" ref="I529" si="211">H529+1</f>
+        <f t="shared" ref="I529" si="216">H529+1</f>
         <v>2028</v>
       </c>
       <c r="J529" s="58">
-        <f t="shared" ref="J529" si="212">I529+1</f>
+        <f t="shared" ref="J529" si="217">I529+1</f>
         <v>2029</v>
       </c>
       <c r="K529" s="58">
-        <f t="shared" ref="K529" si="213">J529+1</f>
+        <f t="shared" ref="K529" si="218">J529+1</f>
         <v>2030</v>
       </c>
       <c r="L529" s="58">
-        <f t="shared" ref="L529" si="214">K529+1</f>
+        <f t="shared" ref="L529" si="219">K529+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="530" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A530" s="48"/>
       <c r="B530" s="59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C530" s="59"/>
       <c r="D530" s="59"/>
       <c r="E530" s="59"/>
       <c r="F530" s="60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G530" s="60"/>
       <c r="H530" s="61"/>
@@ -16986,7 +16982,7 @@
       <c r="J530" s="61"/>
       <c r="K530" s="61"/>
       <c r="L530" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="531" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
@@ -17006,7 +17002,7 @@
     <row r="532" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A532" s="48"/>
       <c r="B532" s="85" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C532" s="86"/>
       <c r="D532" s="87"/>
@@ -17036,44 +17032,44 @@
     <row r="534" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A534" s="48"/>
       <c r="B534" s="65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C534" s="65"/>
       <c r="D534" s="65"/>
       <c r="E534" s="65"/>
       <c r="F534" s="293">
-        <f t="shared" ref="F534:L534" si="215">F29</f>
+        <f t="shared" ref="F534:L534" si="220">F29</f>
         <v>320</v>
       </c>
       <c r="G534" s="293">
-        <f t="shared" si="215"/>
+        <f t="shared" si="220"/>
         <v>5845</v>
       </c>
       <c r="H534" s="304">
-        <f t="shared" si="215"/>
+        <f t="shared" si="220"/>
         <v>8594.9202080000123</v>
       </c>
       <c r="I534" s="304">
-        <f t="shared" si="215"/>
+        <f t="shared" si="220"/>
         <v>1323.0899572529318</v>
       </c>
       <c r="J534" s="304">
-        <f t="shared" si="215"/>
+        <f t="shared" si="220"/>
         <v>-576.64844186903974</v>
       </c>
       <c r="K534" s="304">
-        <f t="shared" si="215"/>
+        <f t="shared" si="220"/>
         <v>-2250.7979386063735</v>
       </c>
       <c r="L534" s="304">
-        <f t="shared" si="215"/>
+        <f t="shared" si="220"/>
         <v>-4216.6406490114023</v>
       </c>
     </row>
     <row r="535" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A535" s="48"/>
       <c r="B535" s="65" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C535" s="65"/>
       <c r="D535" s="65"/>
@@ -17103,7 +17099,7 @@
     <row r="536" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A536" s="48"/>
       <c r="B536" s="72" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C536" s="73"/>
       <c r="D536" s="73"/>
@@ -17135,7 +17131,7 @@
     <row r="537" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A537" s="48"/>
       <c r="B537" s="371" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C537" s="70"/>
       <c r="D537" s="70"/>
@@ -17166,7 +17162,7 @@
     <row r="538" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A538" s="48"/>
       <c r="B538" s="374" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C538" s="70"/>
       <c r="D538" s="70"/>
@@ -17192,7 +17188,7 @@
     <row r="539" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A539" s="48"/>
       <c r="B539" s="377" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C539" s="73"/>
       <c r="D539" s="73"/>
@@ -17204,26 +17200,26 @@
         <v>-2247</v>
       </c>
       <c r="I539" s="379">
-        <f t="shared" ref="I539:L539" si="216">I544</f>
+        <f t="shared" ref="I539:L539" si="221">I544</f>
         <v>0</v>
       </c>
       <c r="J539" s="379">
-        <f t="shared" si="216"/>
+        <f t="shared" si="221"/>
         <v>0</v>
       </c>
       <c r="K539" s="379">
-        <f t="shared" si="216"/>
+        <f t="shared" si="221"/>
         <v>0</v>
       </c>
       <c r="L539" s="379">
-        <f t="shared" si="216"/>
+        <f t="shared" si="221"/>
         <v>0</v>
       </c>
     </row>
     <row r="540" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A540" s="48"/>
       <c r="B540" s="371" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C540" s="70"/>
       <c r="D540" s="70"/>
@@ -17268,7 +17264,7 @@
     <row r="542" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A542" s="48"/>
       <c r="B542" s="85" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C542" s="86"/>
       <c r="D542" s="87"/>
@@ -17298,7 +17294,7 @@
     <row r="544" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A544" s="48"/>
       <c r="B544" s="65" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C544" s="65"/>
       <c r="D544" s="65"/>
@@ -17329,7 +17325,7 @@
     <row r="545" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A545" s="48"/>
       <c r="B545" s="65" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C545" s="65"/>
       <c r="D545" s="65"/>
@@ -17360,7 +17356,7 @@
     <row r="546" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A546" s="48"/>
       <c r="B546" s="72" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C546" s="72"/>
       <c r="D546" s="72"/>
@@ -17372,26 +17368,26 @@
         <v>-331.47606240000368</v>
       </c>
       <c r="I546" s="379">
-        <f t="shared" ref="I546:L546" si="217">-I540</f>
+        <f t="shared" ref="I546:L546" si="222">-I540</f>
         <v>-396.9269871758795</v>
       </c>
       <c r="J546" s="379">
-        <f t="shared" si="217"/>
+        <f t="shared" si="222"/>
         <v>0</v>
       </c>
       <c r="K546" s="379">
-        <f t="shared" si="217"/>
+        <f t="shared" si="222"/>
         <v>0</v>
       </c>
       <c r="L546" s="379">
-        <f t="shared" si="217"/>
+        <f t="shared" si="222"/>
         <v>0</v>
       </c>
     </row>
     <row r="547" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A547" s="48"/>
       <c r="B547" s="70" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C547" s="70"/>
       <c r="D547" s="70"/>
@@ -17403,19 +17399,19 @@
         <v>0</v>
       </c>
       <c r="I547" s="381">
-        <f t="shared" ref="I547:L547" si="218">SUM(I544:I546)</f>
+        <f t="shared" ref="I547:L547" si="223">SUM(I544:I546)</f>
         <v>0</v>
       </c>
       <c r="J547" s="381">
-        <f t="shared" si="218"/>
+        <f t="shared" si="223"/>
         <v>0</v>
       </c>
       <c r="K547" s="381">
-        <f t="shared" si="218"/>
+        <f t="shared" si="223"/>
         <v>0</v>
       </c>
       <c r="L547" s="381">
-        <f t="shared" si="218"/>
+        <f t="shared" si="223"/>
         <v>0</v>
       </c>
     </row>
@@ -17436,7 +17432,7 @@
     <row r="549" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A549" s="48"/>
       <c r="B549" s="382" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C549" s="86"/>
       <c r="D549" s="87"/>
@@ -17466,7 +17462,7 @@
     <row r="551" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A551" s="48"/>
       <c r="B551" s="371" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C551" s="65"/>
       <c r="D551" s="65"/>
@@ -17482,7 +17478,7 @@
     <row r="552" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A552" s="48"/>
       <c r="B552" s="156" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C552" s="156"/>
       <c r="D552" s="156"/>
@@ -17513,7 +17509,7 @@
     <row r="553" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A553" s="48"/>
       <c r="B553" s="385" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C553" s="74"/>
       <c r="D553" s="74"/>
@@ -17544,7 +17540,7 @@
     <row r="554" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A554" s="48"/>
       <c r="B554" s="371" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C554" s="371"/>
       <c r="D554" s="371"/>
@@ -17556,26 +17552,26 @@
         <v>-749</v>
       </c>
       <c r="I554" s="383">
-        <f t="shared" ref="I554:L554" si="219">SUM(I552:I553)</f>
+        <f t="shared" ref="I554:L554" si="224">SUM(I552:I553)</f>
         <v>-749</v>
       </c>
       <c r="J554" s="383">
-        <f t="shared" si="219"/>
+        <f t="shared" si="224"/>
         <v>-749</v>
       </c>
       <c r="K554" s="383">
-        <f t="shared" si="219"/>
+        <f t="shared" si="224"/>
         <v>-749</v>
       </c>
       <c r="L554" s="383">
-        <f t="shared" si="219"/>
+        <f t="shared" si="224"/>
         <v>-749</v>
       </c>
     </row>
     <row r="555" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A555" s="48"/>
       <c r="B555" s="74" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C555" s="74"/>
       <c r="D555" s="74"/>
@@ -17587,26 +17583,26 @@
         <v>0</v>
       </c>
       <c r="I555" s="384">
-        <f t="shared" ref="I555:L555" si="220">I538</f>
+        <f t="shared" ref="I555:L555" si="225">I538</f>
         <v>0</v>
       </c>
       <c r="J555" s="384">
-        <f t="shared" si="220"/>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
       <c r="K555" s="384">
-        <f t="shared" si="220"/>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
       <c r="L555" s="384">
-        <f t="shared" si="220"/>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
     </row>
     <row r="556" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A556" s="48"/>
       <c r="B556" s="371" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C556" s="371"/>
       <c r="D556" s="371"/>
@@ -17618,19 +17614,19 @@
         <v>-749</v>
       </c>
       <c r="I556" s="383">
-        <f t="shared" ref="I556:L556" si="221">SUM(I554:I555)</f>
+        <f t="shared" ref="I556:L556" si="226">SUM(I554:I555)</f>
         <v>-749</v>
       </c>
       <c r="J556" s="383">
-        <f t="shared" si="221"/>
+        <f t="shared" si="226"/>
         <v>-749</v>
       </c>
       <c r="K556" s="383">
-        <f t="shared" si="221"/>
+        <f t="shared" si="226"/>
         <v>-749</v>
       </c>
       <c r="L556" s="383">
-        <f t="shared" si="221"/>
+        <f t="shared" si="226"/>
         <v>-749</v>
       </c>
     </row>
@@ -17710,7 +17706,7 @@
     <row r="562" spans="1:12" ht="21" x14ac:dyDescent="0.5">
       <c r="A562" s="48"/>
       <c r="B562" s="52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C562" s="53"/>
       <c r="D562" s="51"/>
@@ -17747,7 +17743,7 @@
       <c r="D564" s="55"/>
       <c r="E564" s="55"/>
       <c r="F564" s="56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G564" s="56"/>
       <c r="H564" s="56"/>
@@ -17773,31 +17769,31 @@
         <v>2027</v>
       </c>
       <c r="I565" s="58">
-        <f t="shared" ref="I565" si="222">H565+1</f>
+        <f t="shared" ref="I565" si="227">H565+1</f>
         <v>2028</v>
       </c>
       <c r="J565" s="58">
-        <f t="shared" ref="J565" si="223">I565+1</f>
+        <f t="shared" ref="J565" si="228">I565+1</f>
         <v>2029</v>
       </c>
       <c r="K565" s="58">
-        <f t="shared" ref="K565" si="224">J565+1</f>
+        <f t="shared" ref="K565" si="229">J565+1</f>
         <v>2030</v>
       </c>
       <c r="L565" s="58">
-        <f t="shared" ref="L565" si="225">K565+1</f>
+        <f t="shared" ref="L565" si="230">K565+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="566" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B566" s="59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C566" s="59"/>
       <c r="D566" s="59"/>
       <c r="E566" s="59"/>
       <c r="F566" s="60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G566" s="60"/>
       <c r="H566" s="61"/>
@@ -17805,7 +17801,7 @@
       <c r="J566" s="61"/>
       <c r="K566" s="61"/>
       <c r="L566" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="567" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
@@ -17823,7 +17819,7 @@
     </row>
     <row r="568" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="B568" s="85" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C568" s="86"/>
       <c r="D568" s="87"/>
@@ -17851,7 +17847,7 @@
     </row>
     <row r="570" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B570" s="195" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C570" s="195"/>
       <c r="D570" s="195"/>
@@ -17876,7 +17872,7 @@
     </row>
     <row r="571" spans="1:12" ht="15.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B571" s="68" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C571" s="68"/>
       <c r="D571" s="68"/>
@@ -17906,7 +17902,7 @@
     </row>
     <row r="572" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B572" s="195" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C572" s="195"/>
       <c r="D572" s="195"/>
@@ -17918,7 +17914,7 @@
         <v>2105.7554509600027</v>
       </c>
       <c r="I572" s="67">
-        <f t="shared" ref="I572" si="226">I571*I570</f>
+        <f t="shared" ref="I572" si="231">I571*I570</f>
         <v>324.15703952696828</v>
       </c>
       <c r="J572" s="67">
@@ -17926,11 +17922,11 @@
         <v>0</v>
       </c>
       <c r="K572" s="67">
-        <f t="shared" ref="K572:L572" si="227">MAX(0, K571*K570)</f>
+        <f t="shared" ref="K572:L572" si="232">MAX(0, K571*K570)</f>
         <v>0</v>
       </c>
       <c r="L572" s="67">
-        <f t="shared" si="227"/>
+        <f t="shared" si="232"/>
         <v>0</v>
       </c>
     </row>
@@ -17949,7 +17945,7 @@
     </row>
     <row r="574" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="B574" s="85" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C574" s="86"/>
       <c r="D574" s="87"/>
@@ -17977,7 +17973,7 @@
     </row>
     <row r="576" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B576" s="195" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C576" s="195"/>
       <c r="D576" s="195"/>
@@ -17989,25 +17985,25 @@
         <v>35600</v>
       </c>
       <c r="I576" s="67">
-        <f t="shared" ref="I576:L576" si="228">H581</f>
+        <f t="shared" ref="I576:L576" si="233">H581</f>
         <v>39510.688694640005</v>
       </c>
       <c r="J576" s="67">
-        <f t="shared" si="228"/>
+        <f t="shared" si="233"/>
         <v>40112.694625190088</v>
       </c>
       <c r="K576" s="67">
-        <f t="shared" si="228"/>
+        <f t="shared" si="233"/>
         <v>39536.04618332105</v>
       </c>
       <c r="L576" s="67">
-        <f t="shared" si="228"/>
+        <f t="shared" si="233"/>
         <v>37285.248244714676</v>
       </c>
     </row>
     <row r="577" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B577" s="247" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C577" s="248"/>
       <c r="D577" s="248"/>
@@ -18037,7 +18033,7 @@
     </row>
     <row r="578" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B578" s="246" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C578" s="65"/>
       <c r="D578" s="65"/>
@@ -18049,25 +18045,25 @@
         <v>-2105.7554509600027</v>
       </c>
       <c r="I578" s="67">
-        <f t="shared" ref="I578:L578" si="229">-I572</f>
+        <f t="shared" ref="I578:L578" si="234">-I572</f>
         <v>-324.15703952696828</v>
       </c>
       <c r="J578" s="67">
-        <f t="shared" si="229"/>
+        <f t="shared" si="234"/>
         <v>0</v>
       </c>
       <c r="K578" s="67">
-        <f t="shared" si="229"/>
+        <f t="shared" si="234"/>
         <v>0</v>
       </c>
       <c r="L578" s="67">
-        <f t="shared" si="229"/>
+        <f t="shared" si="234"/>
         <v>0</v>
       </c>
     </row>
     <row r="579" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B579" s="246" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C579" s="65"/>
       <c r="D579" s="65"/>
@@ -18097,7 +18093,7 @@
     </row>
     <row r="580" spans="2:12" ht="15.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B580" s="250" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C580" s="72"/>
       <c r="D580" s="72"/>
@@ -18127,7 +18123,7 @@
     </row>
     <row r="581" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B581" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C581" s="65"/>
       <c r="D581" s="65"/>
@@ -18142,19 +18138,19 @@
         <v>39510.688694640005</v>
       </c>
       <c r="I581" s="67">
-        <f t="shared" ref="I581:L581" si="230">SUM(I576:I580)</f>
+        <f t="shared" ref="I581:L581" si="235">SUM(I576:I580)</f>
         <v>40112.694625190088</v>
       </c>
       <c r="J581" s="67">
-        <f t="shared" si="230"/>
+        <f t="shared" si="235"/>
         <v>39536.04618332105</v>
       </c>
       <c r="K581" s="67">
-        <f t="shared" si="230"/>
+        <f t="shared" si="235"/>
         <v>37285.248244714676</v>
       </c>
       <c r="L581" s="67">
-        <f t="shared" si="230"/>
+        <f t="shared" si="235"/>
         <v>33068.607595703274</v>
       </c>
     </row>

--- a/Solid State PLC.xlsx
+++ b/Solid State PLC.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b4a63f789af4ef06/Documents/Career/Career Development/Financial Statements/3 Statement Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{C42BB4A9-2FB9-4DC3-8217-8A7070EACCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9076EA1F-F59C-4259-A7F3-92765EB9EF91}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="8_{C42BB4A9-2FB9-4DC3-8217-8A7070EACCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE066FB8-4355-4B31-B6B1-519D92499C9F}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{C4FDF26E-8D02-42E6-9BA6-E8E4AB263931}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{C4FDF26E-8D02-42E6-9BA6-E8E4AB263931}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
     <sheet name="Assumptions" sheetId="3" r:id="rId2"/>
     <sheet name="Model" sheetId="2" r:id="rId3"/>
+    <sheet name="ANAV" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Model!$A$2:$M$737</definedName>
@@ -66,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="336">
   <si>
     <t>Financial Statements - Income Statement</t>
   </si>
@@ -323,9 +324,6 @@
     <t>ROU Additions</t>
   </si>
   <si>
-    <t>(£m in millions), unless stated otherwise</t>
-  </si>
-  <si>
     <t>ROU Depreciation</t>
   </si>
   <si>
@@ -1032,13 +1030,58 @@
   </si>
   <si>
     <t>Revenue Growth Rates</t>
+  </si>
+  <si>
+    <t>Adjusted Net Asset Value</t>
+  </si>
+  <si>
+    <t>Reported book</t>
+  </si>
+  <si>
+    <t>Stress %</t>
+  </si>
+  <si>
+    <t>Stress adjusted</t>
+  </si>
+  <si>
+    <t>Conservative %</t>
+  </si>
+  <si>
+    <t>Conservative adjusted</t>
+  </si>
+  <si>
+    <t>FY 2026 valuations</t>
+  </si>
+  <si>
+    <t>PP&amp;E</t>
+  </si>
+  <si>
+    <t>Assets / bridge (£000s)</t>
+  </si>
+  <si>
+    <t>Intangible assets excluded goodwill</t>
+  </si>
+  <si>
+    <t>TOTAL ASSETS</t>
+  </si>
+  <si>
+    <t>Corporate tax asset</t>
+  </si>
+  <si>
+    <t>Ordinary share outstanding</t>
+  </si>
+  <si>
+    <t>Implied ANAV per share</t>
+  </si>
+  <si>
+    <t>Total Liabilies (Book)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="39">
+  <numFmts count="41">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;p&quot;"/>
@@ -1078,8 +1121,10 @@
     <numFmt numFmtId="200" formatCode="0&quot; employees&quot;"/>
     <numFmt numFmtId="201" formatCode="&quot;£&quot;#,##0"/>
     <numFmt numFmtId="202" formatCode="0.0&quot; p&quot;;\(0.0&quot;p&quot;\);\-"/>
+    <numFmt numFmtId="203" formatCode="#,##0.00,,&quot;m&quot;;\(#,##0.00,,&quot;m&quot;\);\–"/>
+    <numFmt numFmtId="204" formatCode="&quot;£&quot;#,##0.00;\(&quot;£&quot;#,##0.00\);\–"/>
   </numFmts>
-  <fonts count="53" x14ac:knownFonts="1">
+  <fonts count="54" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1425,8 +1470,16 @@
       <name val="Open Sans"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1460,6 +1513,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1647,7 +1712,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="400">
+  <cellXfs count="411">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2142,12 +2207,157 @@
     <xf numFmtId="9" fontId="52" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="52" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="52" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="4" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="198" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="198" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="198" fontId="53" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="198" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="204" fontId="53" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="203" fontId="53" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.499984740745262"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="198" formatCode="&quot;£&quot;#,##0;\(&quot;£&quot;#,##0\);\–"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.499984740745262"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFF5D2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.499984740745262"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="198" formatCode="&quot;£&quot;#,##0;\(&quot;£&quot;#,##0\);\–"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.499984740745262"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFF5D2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.499984740745262"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="198" formatCode="&quot;£&quot;#,##0;\(&quot;£&quot;#,##0\);\–"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -2235,6 +2445,28 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A6A36497-4868-4758-952A-D9B88D1FAEE2}" name="Table1" displayName="Table1" ref="B6:G16" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="B6:G16" xr:uid="{A6A36497-4868-4758-952A-D9B88D1FAEE2}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{FC349116-5BFD-4345-8409-8795179AE82B}" name="Assets / bridge (£000s)"/>
+    <tableColumn id="2" xr3:uid="{ECE441C7-BA02-45E1-8553-734196B5D6B3}" name="Reported book" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{55EB2994-74F5-4FFD-82DA-D3852576EE1B}" name="Stress %" dataDxfId="3" dataCellStyle="Percent"/>
+    <tableColumn id="4" xr3:uid="{E92C9155-47EA-4A84-B185-AFF3FA9AE9A7}" name="Stress adjusted" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{A8979D33-7692-4065-9DBE-D896FD817AA6}" name="Conservative %" dataDxfId="1" dataCellStyle="Percent"/>
+    <tableColumn id="6" xr3:uid="{6BCA613E-3019-4E89-9DB9-6C8F7DC80AF7}" name="Conservative adjusted" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2584,7 +2816,7 @@
   <sheetData>
     <row r="2" spans="2:2" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
@@ -2627,7 +2859,7 @@
     <row r="3" spans="1:12" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="48"/>
       <c r="B3" s="52" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C3" s="53"/>
       <c r="D3" s="51"/>
@@ -2741,7 +2973,7 @@
     </row>
     <row r="9" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B9" s="124" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C9" s="41"/>
       <c r="D9" s="264"/>
@@ -2769,7 +3001,7 @@
     </row>
     <row r="12" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B12" s="284" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C12" s="285"/>
       <c r="D12" s="285"/>
@@ -2797,13 +3029,13 @@
     </row>
     <row r="14" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B14" s="371" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C14" s="65"/>
       <c r="D14" s="65"/>
       <c r="E14" s="65"/>
       <c r="F14" s="288" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G14" s="240"/>
       <c r="H14" s="289">
@@ -2833,7 +3065,7 @@
       <c r="D15" s="200"/>
       <c r="E15" s="240"/>
       <c r="F15" s="136" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G15" s="200"/>
       <c r="H15" s="239">
@@ -2858,7 +3090,7 @@
       <c r="D16" s="65"/>
       <c r="E16" s="268"/>
       <c r="F16" s="136" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G16" s="269"/>
       <c r="H16" s="239">
@@ -2883,7 +3115,7 @@
       <c r="D17" s="65"/>
       <c r="E17" s="268"/>
       <c r="F17" s="136" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G17" s="269"/>
       <c r="H17" s="239">
@@ -2917,13 +3149,13 @@
     </row>
     <row r="19" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B19" s="371" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C19" s="65"/>
       <c r="D19" s="65"/>
       <c r="E19" s="65"/>
       <c r="F19" s="288" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G19" s="240"/>
       <c r="H19" s="289">
@@ -2953,7 +3185,7 @@
       <c r="D20" s="200"/>
       <c r="E20" s="240"/>
       <c r="F20" s="136" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G20" s="200"/>
       <c r="H20" s="239">
@@ -2978,7 +3210,7 @@
       <c r="D21" s="65"/>
       <c r="E21" s="268"/>
       <c r="F21" s="136" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G21" s="269"/>
       <c r="H21" s="239">
@@ -3003,7 +3235,7 @@
       <c r="D22" s="65"/>
       <c r="E22" s="268"/>
       <c r="F22" s="136" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G22" s="269"/>
       <c r="H22" s="239">
@@ -3037,13 +3269,13 @@
     </row>
     <row r="24" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B24" s="371" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C24" s="65"/>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="288" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G24" s="240"/>
       <c r="H24" s="289">
@@ -3073,7 +3305,7 @@
       <c r="D25" s="200"/>
       <c r="E25" s="240"/>
       <c r="F25" s="136" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G25" s="200"/>
       <c r="H25" s="239">
@@ -3098,7 +3330,7 @@
       <c r="D26" s="65"/>
       <c r="E26" s="268"/>
       <c r="F26" s="136" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G26" s="269"/>
       <c r="H26" s="239">
@@ -3123,7 +3355,7 @@
       <c r="D27" s="65"/>
       <c r="E27" s="268"/>
       <c r="F27" s="136" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G27" s="269"/>
       <c r="H27" s="239">
@@ -3170,7 +3402,7 @@
     </row>
     <row r="30" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B30" s="284" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C30" s="285"/>
       <c r="D30" s="285"/>
@@ -3211,13 +3443,13 @@
     </row>
     <row r="33" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B33" s="371" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C33" s="65"/>
       <c r="D33" s="65"/>
       <c r="E33" s="268"/>
       <c r="F33" s="288" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G33" s="269"/>
       <c r="H33" s="289">
@@ -3247,7 +3479,7 @@
       <c r="D34" s="65"/>
       <c r="E34" s="268"/>
       <c r="F34" s="136" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G34" s="269"/>
       <c r="H34" s="395">
@@ -3272,7 +3504,7 @@
       <c r="D35" s="65"/>
       <c r="E35" s="65"/>
       <c r="F35" s="136" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G35" s="200"/>
       <c r="H35" s="395">
@@ -3297,7 +3529,7 @@
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="136" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G36" s="200"/>
       <c r="H36" s="395">
@@ -3331,13 +3563,13 @@
     </row>
     <row r="38" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B38" s="371" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C38" s="65"/>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
       <c r="F38" s="288" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G38" s="273"/>
       <c r="H38" s="289">
@@ -3367,7 +3599,7 @@
       <c r="D39" s="65"/>
       <c r="E39" s="65"/>
       <c r="F39" s="136" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G39" s="274"/>
       <c r="H39" s="179">
@@ -3392,7 +3624,7 @@
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
       <c r="F40" s="136" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G40" s="276"/>
       <c r="H40" s="179">
@@ -3417,7 +3649,7 @@
       <c r="D41" s="65"/>
       <c r="E41" s="65"/>
       <c r="F41" s="136" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G41" s="277"/>
       <c r="H41" s="179">
@@ -3449,13 +3681,13 @@
     </row>
     <row r="43" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B43" s="371" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C43" s="65"/>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="288" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G43" s="273"/>
       <c r="H43" s="289">
@@ -3485,7 +3717,7 @@
       <c r="D44" s="65"/>
       <c r="E44" s="65"/>
       <c r="F44" s="136" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G44" s="274"/>
       <c r="H44" s="395">
@@ -3510,7 +3742,7 @@
       <c r="D45" s="65"/>
       <c r="E45" s="65"/>
       <c r="F45" s="136" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G45" s="276"/>
       <c r="H45" s="395">
@@ -3535,7 +3767,7 @@
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
       <c r="F46" s="136" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G46" s="277"/>
       <c r="H46" s="395">
@@ -3567,13 +3799,13 @@
     </row>
     <row r="48" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B48" s="371" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C48" s="65"/>
       <c r="D48" s="65"/>
       <c r="E48" s="65"/>
       <c r="F48" s="288" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G48" s="273"/>
       <c r="H48" s="289">
@@ -3603,7 +3835,7 @@
       <c r="D49" s="65"/>
       <c r="E49" s="65"/>
       <c r="F49" s="136" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G49" s="274"/>
       <c r="H49" s="179">
@@ -3628,7 +3860,7 @@
       <c r="D50" s="65"/>
       <c r="E50" s="65"/>
       <c r="F50" s="136" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G50" s="276"/>
       <c r="H50" s="179">
@@ -3653,7 +3885,7 @@
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="136" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G51" s="277"/>
       <c r="H51" s="179">
@@ -4346,7 +4578,7 @@
     <row r="8" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="48"/>
       <c r="B8" s="59" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C8" s="59"/>
       <c r="D8" s="59"/>
@@ -4540,7 +4772,7 @@
     <row r="15" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="48"/>
       <c r="B15" s="72" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C15" s="73"/>
       <c r="D15" s="73"/>
@@ -4612,7 +4844,7 @@
     <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A17" s="48"/>
       <c r="B17" s="65" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C17" s="70"/>
       <c r="D17" s="70"/>
@@ -4663,7 +4895,7 @@
     <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A19" s="48"/>
       <c r="B19" s="65" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C19" s="65"/>
       <c r="D19" s="70"/>
@@ -4694,7 +4926,7 @@
     <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A20" s="48"/>
       <c r="B20" s="65" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C20" s="65"/>
       <c r="D20" s="70"/>
@@ -4787,7 +5019,7 @@
     <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A23" s="48"/>
       <c r="B23" s="70" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C23" s="70"/>
       <c r="D23" s="70"/>
@@ -4824,7 +5056,7 @@
     <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A24" s="48"/>
       <c r="B24" s="65" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C24" s="70"/>
       <c r="D24" s="70"/>
@@ -5012,7 +5244,7 @@
     <row r="31" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="48"/>
       <c r="B31" s="72" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C31" s="72"/>
       <c r="D31" s="72"/>
@@ -5202,7 +5434,7 @@
     <row r="38" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A38" s="48"/>
       <c r="B38" s="70" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C38" s="65"/>
       <c r="D38" s="291">
@@ -5361,7 +5593,7 @@
     <row r="47" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="48"/>
       <c r="B47" s="59" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C47" s="59"/>
       <c r="D47" s="59"/>
@@ -5495,7 +5727,7 @@
     <row r="53" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A53" s="48"/>
       <c r="B53" s="129" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C53" s="65"/>
       <c r="D53" s="65"/>
@@ -5741,7 +5973,7 @@
     <row r="61" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="48"/>
       <c r="B61" s="72" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C61" s="72"/>
       <c r="D61" s="72"/>
@@ -5892,7 +6124,7 @@
     <row r="67" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A67" s="48"/>
       <c r="B67" s="129" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C67" s="65"/>
       <c r="D67" s="65"/>
@@ -5927,7 +6159,7 @@
     <row r="68" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A68" s="48"/>
       <c r="B68" s="129" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C68" s="65"/>
       <c r="D68" s="65"/>
@@ -5962,7 +6194,7 @@
     <row r="69" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A69" s="48"/>
       <c r="B69" s="129" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C69" s="65"/>
       <c r="D69" s="65"/>
@@ -6032,7 +6264,7 @@
     <row r="71" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A71" s="48"/>
       <c r="B71" s="129" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C71" s="65"/>
       <c r="D71" s="65"/>
@@ -6104,7 +6336,7 @@
     <row r="73" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A73" s="48"/>
       <c r="B73" s="129" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C73" s="70"/>
       <c r="D73" s="65"/>
@@ -6124,7 +6356,7 @@
     <row r="74" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A74" s="48"/>
       <c r="B74" s="130" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C74" s="130"/>
       <c r="D74" s="130"/>
@@ -6196,7 +6428,7 @@
     <row r="76" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A76" s="48"/>
       <c r="B76" s="65" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C76" s="65"/>
       <c r="D76" s="65"/>
@@ -6231,7 +6463,7 @@
     <row r="77" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A77" s="48"/>
       <c r="B77" s="65" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C77" s="65"/>
       <c r="D77" s="65"/>
@@ -6266,7 +6498,7 @@
     <row r="78" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A78" s="48"/>
       <c r="B78" s="65" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C78" s="65"/>
       <c r="D78" s="65"/>
@@ -6373,7 +6605,7 @@
     <row r="81" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A81" s="48"/>
       <c r="B81" s="65" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C81" s="65"/>
       <c r="D81" s="65"/>
@@ -6408,7 +6640,7 @@
     <row r="82" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A82" s="48"/>
       <c r="B82" s="65" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C82" s="65"/>
       <c r="D82" s="65"/>
@@ -6443,7 +6675,7 @@
     <row r="83" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A83" s="48"/>
       <c r="B83" s="65" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C83" s="65"/>
       <c r="D83" s="65"/>
@@ -6478,7 +6710,7 @@
     <row r="84" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A84" s="48"/>
       <c r="B84" s="65" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C84" s="65"/>
       <c r="D84" s="65"/>
@@ -6513,7 +6745,7 @@
     <row r="85" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A85" s="48"/>
       <c r="B85" s="65" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C85" s="65"/>
       <c r="D85" s="65"/>
@@ -6620,7 +6852,7 @@
     <row r="88" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A88" s="48"/>
       <c r="B88" s="65" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C88" s="65"/>
       <c r="D88" s="65"/>
@@ -6671,7 +6903,7 @@
     <row r="90" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A90" s="48"/>
       <c r="B90" s="65" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C90" s="65"/>
       <c r="D90" s="65"/>
@@ -6843,7 +7075,7 @@
     <row r="100" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="48"/>
       <c r="B100" s="59" t="s">
-        <v>53</v>
+        <v>223</v>
       </c>
       <c r="C100" s="59"/>
       <c r="D100" s="59"/>
@@ -7000,7 +7232,7 @@
     <row r="107" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A107" s="48"/>
       <c r="B107" s="129" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C107" s="65"/>
       <c r="D107" s="65"/>
@@ -7093,7 +7325,7 @@
     <row r="110" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A110" s="48"/>
       <c r="B110" s="389" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C110" s="65"/>
       <c r="D110" s="65"/>
@@ -7124,7 +7356,7 @@
     <row r="111" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A111" s="48"/>
       <c r="B111" s="389" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C111" s="65"/>
       <c r="D111" s="65"/>
@@ -7171,7 +7403,7 @@
     <row r="113" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A113" s="48"/>
       <c r="B113" s="70" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C113" s="70"/>
       <c r="D113" s="70"/>
@@ -7785,6 +8017,15 @@
       <c r="C140" s="55"/>
       <c r="D140" s="55"/>
       <c r="E140" s="55"/>
+      <c r="F140" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="G140" s="56"/>
+      <c r="H140" s="56"/>
+      <c r="I140" s="56"/>
+      <c r="J140" s="56"/>
+      <c r="K140" s="56"/>
+      <c r="L140" s="56"/>
     </row>
     <row r="141" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A141" s="48"/>
@@ -7792,11 +8033,38 @@
       <c r="C141" s="55"/>
       <c r="D141" s="55"/>
       <c r="E141" s="55"/>
+      <c r="F141" s="57">
+        <v>2025</v>
+      </c>
+      <c r="G141" s="57">
+        <f>F141+1</f>
+        <v>2026</v>
+      </c>
+      <c r="H141" s="58">
+        <f>G141+1</f>
+        <v>2027</v>
+      </c>
+      <c r="I141" s="58">
+        <f t="shared" ref="I141" si="78">H141+1</f>
+        <v>2028</v>
+      </c>
+      <c r="J141" s="58">
+        <f t="shared" ref="J141" si="79">I141+1</f>
+        <v>2029</v>
+      </c>
+      <c r="K141" s="58">
+        <f t="shared" ref="K141" si="80">J141+1</f>
+        <v>2030</v>
+      </c>
+      <c r="L141" s="58">
+        <f t="shared" ref="L141" si="81">K141+1</f>
+        <v>2031</v>
+      </c>
     </row>
     <row r="142" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="48"/>
       <c r="B142" s="59" t="s">
-        <v>53</v>
+        <v>223</v>
       </c>
       <c r="C142" s="59"/>
       <c r="D142" s="59"/>
@@ -7830,7 +8098,7 @@
     <row r="144" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A144" s="48"/>
       <c r="B144" s="85" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C144" s="86"/>
       <c r="D144" s="87"/>
@@ -7860,7 +8128,7 @@
     <row r="146" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A146" s="48"/>
       <c r="B146" s="65" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C146" s="65"/>
       <c r="D146" s="65"/>
@@ -7871,134 +8139,134 @@
         <v>0.23252094927397174</v>
       </c>
       <c r="H146" s="64">
-        <f t="shared" ref="H146:L146" si="78">(H10-G10)/G10</f>
+        <f t="shared" ref="H146:L146" si="82">(H10-G10)/G10</f>
         <v>-3.0938981731367939E-2</v>
       </c>
       <c r="I146" s="64">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>2.3081002009777279E-2</v>
       </c>
       <c r="J146" s="64">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>7.9051148907853155E-2</v>
       </c>
       <c r="K146" s="64">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>7.5748515524765234E-2</v>
       </c>
       <c r="L146" s="64">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>7.609395270450596E-2</v>
       </c>
     </row>
     <row r="147" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A147" s="48"/>
       <c r="B147" s="65" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C147" s="65"/>
       <c r="D147" s="65"/>
       <c r="E147" s="65"/>
       <c r="F147" s="160">
-        <f t="shared" ref="F147:L147" si="79">F17</f>
+        <f t="shared" ref="F147:L147" si="83">F17</f>
         <v>1.0666538732169129E-2</v>
       </c>
       <c r="G147" s="160">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>4.5068247872119577E-2</v>
       </c>
       <c r="H147" s="160">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>6.5545519905328017E-2</v>
       </c>
       <c r="I147" s="160">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>1.233643062009334E-2</v>
       </c>
       <c r="J147" s="160">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>4.2297280694023769E-4</v>
       </c>
       <c r="K147" s="160">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>-7.0974152883583764E-3</v>
       </c>
       <c r="L147" s="160">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>-1.4776032930122062E-2</v>
       </c>
     </row>
     <row r="148" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A148" s="48"/>
       <c r="B148" s="65" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C148" s="65"/>
       <c r="D148" s="65"/>
       <c r="E148" s="65"/>
       <c r="F148" s="160">
-        <f t="shared" ref="F148:L148" si="80">F23/F10</f>
+        <f t="shared" ref="F148:L148" si="84">F23/F10</f>
         <v>1.0666538732169129E-2</v>
       </c>
       <c r="G148" s="160">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>4.5068247872119577E-2</v>
       </c>
       <c r="H148" s="160">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>9.0660047790238008E-2</v>
       </c>
       <c r="I148" s="160">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>4.3030611166416606E-2</v>
       </c>
       <c r="J148" s="160">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>3.5051306347034961E-2</v>
       </c>
       <c r="K148" s="160">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>3.1110124884861669E-2</v>
       </c>
       <c r="L148" s="160">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>2.6587253711317562E-2</v>
       </c>
     </row>
     <row r="149" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A149" s="48"/>
       <c r="B149" s="65" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C149" s="65"/>
       <c r="D149" s="65"/>
       <c r="E149" s="65"/>
       <c r="F149" s="122">
-        <f t="shared" ref="F149:L149" si="81">F33</f>
+        <f t="shared" ref="F149:L149" si="85">F33</f>
         <v>4.0939039211923493E-3</v>
       </c>
       <c r="G149" s="122">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>2.652065600996471E-2</v>
       </c>
       <c r="H149" s="257">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>4.0277466094085543E-2</v>
       </c>
       <c r="I149" s="257">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>6.0603770423566621E-3</v>
       </c>
       <c r="J149" s="257">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>-3.4968847792256996E-3</v>
       </c>
       <c r="K149" s="257">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>-1.2688081310958136E-2</v>
       </c>
       <c r="L149" s="257">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>-2.20889892936144E-2</v>
       </c>
       <c r="R149" s="40"/>
@@ -8006,7 +8274,7 @@
     <row r="150" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A150" s="48"/>
       <c r="B150" s="65" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C150" s="65"/>
       <c r="D150" s="65"/>
@@ -8016,27 +8284,27 @@
         <v>-0.6</v>
       </c>
       <c r="G150" s="258">
-        <f t="shared" ref="G150:L150" si="82">G536</f>
+        <f t="shared" ref="G150:L150" si="86">G536</f>
         <v>0.30059880239520959</v>
       </c>
       <c r="H150" s="145">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>0.3</v>
       </c>
       <c r="I150" s="145">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>0.3</v>
       </c>
       <c r="J150" s="145">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>0.3</v>
       </c>
       <c r="K150" s="145">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>0.3</v>
       </c>
       <c r="L150" s="145">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>0.3</v>
       </c>
     </row>
@@ -8057,7 +8325,7 @@
     <row r="152" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A152" s="48"/>
       <c r="B152" s="85" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C152" s="86"/>
       <c r="D152" s="87"/>
@@ -8087,81 +8355,81 @@
     <row r="154" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A154" s="48"/>
       <c r="B154" s="65" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C154" s="65"/>
       <c r="D154" s="65"/>
       <c r="E154" s="65"/>
       <c r="F154" s="259">
-        <f t="shared" ref="F154:L154" si="83">F16/ABS(F26)</f>
+        <f t="shared" ref="F154:L154" si="87">F16/ABS(F26)</f>
         <v>1.3155818540433926</v>
       </c>
       <c r="G154" s="259">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>6.3039927404718696</v>
       </c>
       <c r="H154" s="259">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>8.1867606916077698</v>
       </c>
       <c r="I154" s="259">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>3.3534307942054054</v>
       </c>
       <c r="J154" s="259">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0.10790514646067864</v>
       </c>
       <c r="K154" s="259">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>-1.2695115858589514</v>
       </c>
       <c r="L154" s="259">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>-2.0205279774246727</v>
       </c>
     </row>
     <row r="155" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A155" s="48"/>
       <c r="B155" s="65" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C155" s="65"/>
       <c r="D155" s="65"/>
       <c r="E155" s="65"/>
       <c r="F155" s="260" t="str">
-        <f t="shared" ref="F155:L155" si="84">IF(F507=0, "N/A", ABS(F23/F507))</f>
+        <f t="shared" ref="F155:L155" si="88">IF(F507=0, "N/A", ABS(F23/F507))</f>
         <v>N/A</v>
       </c>
       <c r="G155" s="260" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>N/A</v>
       </c>
       <c r="H155" s="260">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>14.913846495543153</v>
       </c>
       <c r="I155" s="260">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>29.612900034348847</v>
       </c>
       <c r="J155" s="260">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>25.250733338164736</v>
       </c>
       <c r="K155" s="260">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>10.77113606976663</v>
       </c>
       <c r="L155" s="260">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>5.9661128868484932</v>
       </c>
     </row>
     <row r="156" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A156" s="48"/>
       <c r="B156" s="65" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C156" s="65"/>
       <c r="D156" s="65"/>
@@ -8206,7 +8474,7 @@
     <row r="158" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A158" s="48"/>
       <c r="B158" s="85" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C158" s="86"/>
       <c r="D158" s="87"/>
@@ -8236,7 +8504,7 @@
     <row r="160" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A160" s="48"/>
       <c r="B160" s="65" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C160" s="65"/>
       <c r="D160" s="65"/>
@@ -8281,7 +8549,7 @@
     <row r="162" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A162" s="48"/>
       <c r="B162" s="85" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C162" s="86"/>
       <c r="D162" s="87"/>
@@ -8311,111 +8579,111 @@
     <row r="164" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A164" s="48"/>
       <c r="B164" s="65" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C164" s="70"/>
       <c r="D164" s="65"/>
       <c r="E164" s="65"/>
       <c r="F164" s="151">
-        <f t="shared" ref="F164:L164" si="85">F55/ABS(F72)</f>
+        <f t="shared" ref="F164:L164" si="89">F55/ABS(F72)</f>
         <v>2.1856126100768023</v>
       </c>
       <c r="G164" s="151">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>2.2903077100380318</v>
       </c>
       <c r="H164" s="151">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>2.1613270518242089</v>
       </c>
       <c r="I164" s="151">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>2.091539652248795</v>
       </c>
       <c r="J164" s="151">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>2.1154781886380443</v>
       </c>
       <c r="K164" s="151">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>2.1374291460832522</v>
       </c>
       <c r="L164" s="151">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>2.1529754766239533</v>
       </c>
     </row>
     <row r="165" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A165" s="48"/>
       <c r="B165" s="65" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C165" s="70"/>
       <c r="D165" s="65"/>
       <c r="E165" s="65"/>
       <c r="F165" s="151">
-        <f t="shared" ref="F165:L165" si="86">(F55-F51)/ABS(F72)</f>
+        <f t="shared" ref="F165:L165" si="90">(F55-F51)/ABS(F72)</f>
         <v>1.050102537295428</v>
       </c>
       <c r="G165" s="151">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>1.1185509584725903</v>
       </c>
       <c r="H165" s="151">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>1.0009696055174822</v>
       </c>
       <c r="I165" s="151">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>0.89960816767445739</v>
       </c>
       <c r="J165" s="151">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>0.91090478997089175</v>
       </c>
       <c r="K165" s="151">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>0.92300678315166973</v>
       </c>
       <c r="L165" s="151">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>0.93218045504891378</v>
       </c>
     </row>
     <row r="166" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A166" s="48"/>
       <c r="B166" s="65" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C166" s="70"/>
       <c r="D166" s="65"/>
       <c r="E166" s="65"/>
       <c r="F166" s="151">
-        <f t="shared" ref="F166:L166" si="87">F54/ABS(F72)</f>
+        <f t="shared" ref="F166:L166" si="91">F54/ABS(F72)</f>
         <v>0.14126020346616269</v>
       </c>
       <c r="G166" s="151">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0.25231454803887671</v>
       </c>
       <c r="H166" s="151">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0.18287939104601161</v>
       </c>
       <c r="I166" s="151">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0.11170234913746585</v>
       </c>
       <c r="J166" s="151">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0.11829624331667557</v>
       </c>
       <c r="K166" s="151">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0.12389168116883829</v>
       </c>
       <c r="L166" s="151">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0.12884243146877514</v>
       </c>
     </row>
@@ -8436,7 +8704,7 @@
     <row r="168" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A168" s="48"/>
       <c r="B168" s="85" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C168" s="86"/>
       <c r="D168" s="87"/>
@@ -8466,7 +8734,7 @@
     <row r="170" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A170" s="48"/>
       <c r="B170" s="65" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C170" s="65"/>
       <c r="D170" s="65"/>
@@ -8497,7 +8765,7 @@
     <row r="171" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A171" s="48"/>
       <c r="B171" s="65" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C171" s="65"/>
       <c r="D171" s="65"/>
@@ -8528,7 +8796,7 @@
     <row r="172" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A172" s="48"/>
       <c r="B172" s="65" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C172" s="65"/>
       <c r="D172" s="65"/>
@@ -8573,7 +8841,7 @@
     <row r="174" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A174" s="48"/>
       <c r="B174" s="85" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C174" s="86"/>
       <c r="D174" s="87"/>
@@ -8603,7 +8871,7 @@
     <row r="176" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A176" s="48"/>
       <c r="B176" s="65" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C176" s="65"/>
       <c r="D176" s="65"/>
@@ -8634,7 +8902,7 @@
     <row r="177" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A177" s="48"/>
       <c r="B177" s="65" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C177" s="65"/>
       <c r="D177" s="65"/>
@@ -8665,7 +8933,7 @@
     <row r="178" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A178" s="48"/>
       <c r="B178" s="65" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C178" s="65"/>
       <c r="D178" s="65"/>
@@ -8806,26 +9074,26 @@
         <v>2027</v>
       </c>
       <c r="I185" s="58">
-        <f t="shared" ref="I185" si="88">H185+1</f>
+        <f t="shared" ref="I185" si="92">H185+1</f>
         <v>2028</v>
       </c>
       <c r="J185" s="58">
-        <f t="shared" ref="J185" si="89">I185+1</f>
+        <f t="shared" ref="J185" si="93">I185+1</f>
         <v>2029</v>
       </c>
       <c r="K185" s="58">
-        <f t="shared" ref="K185" si="90">J185+1</f>
+        <f t="shared" ref="K185" si="94">J185+1</f>
         <v>2030</v>
       </c>
       <c r="L185" s="58">
-        <f t="shared" ref="L185" si="91">K185+1</f>
+        <f t="shared" ref="L185" si="95">K185+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="186" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="48"/>
       <c r="B186" s="59" t="s">
-        <v>53</v>
+        <v>223</v>
       </c>
       <c r="C186" s="59"/>
       <c r="D186" s="59"/>
@@ -8859,7 +9127,7 @@
     <row r="188" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A188" s="48"/>
       <c r="B188" s="85" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C188" s="86"/>
       <c r="D188" s="87"/>
@@ -8889,7 +9157,7 @@
     <row r="190" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A190" s="48"/>
       <c r="B190" s="65" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C190" s="70"/>
       <c r="D190" s="70"/>
@@ -8901,26 +9169,26 @@
         <v>21925</v>
       </c>
       <c r="I190" s="304">
-        <f t="shared" ref="I190:L190" si="92">H193</f>
+        <f t="shared" ref="I190:L190" si="96">H193</f>
         <v>23034.404999999999</v>
       </c>
       <c r="J190" s="304">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>24199.945893</v>
       </c>
       <c r="K190" s="304">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>25424.4631551858</v>
       </c>
       <c r="L190" s="304">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>26710.940990838204</v>
       </c>
     </row>
     <row r="191" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A191" s="48"/>
       <c r="B191" s="65" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C191" s="65"/>
       <c r="D191" s="65"/>
@@ -8951,7 +9219,7 @@
     <row r="192" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="48"/>
       <c r="B192" s="72" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C192" s="72"/>
       <c r="D192" s="72"/>
@@ -8977,7 +9245,7 @@
     <row r="193" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A193" s="48"/>
       <c r="B193" s="70" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C193" s="70"/>
       <c r="D193" s="70"/>
@@ -8993,19 +9261,19 @@
         <v>23034.404999999999</v>
       </c>
       <c r="I193" s="302">
-        <f t="shared" ref="I193:L193" si="93">I190*(1+I191)*(1+I192)</f>
+        <f t="shared" ref="I193:L193" si="97">I190*(1+I191)*(1+I192)</f>
         <v>24199.945893</v>
       </c>
       <c r="J193" s="302">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>25424.4631551858</v>
       </c>
       <c r="K193" s="302">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>26710.940990838204</v>
       </c>
       <c r="L193" s="302">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>28062.514604974618</v>
       </c>
     </row>
@@ -9026,7 +9294,7 @@
     <row r="195" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A195" s="48"/>
       <c r="B195" s="85" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C195" s="86"/>
       <c r="D195" s="87"/>
@@ -9056,7 +9324,7 @@
     <row r="197" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A197" s="48"/>
       <c r="B197" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C197" s="70"/>
       <c r="D197" s="70"/>
@@ -9071,26 +9339,26 @@
         <v>17292</v>
       </c>
       <c r="I197" s="302">
-        <f t="shared" ref="I197:L197" si="94">H200</f>
+        <f t="shared" ref="I197:L197" si="98">H200</f>
         <v>17990.596799999999</v>
       </c>
       <c r="J197" s="302">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>18717.416910720003</v>
       </c>
       <c r="K197" s="302">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>19473.600553913093</v>
       </c>
       <c r="L197" s="302">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>20260.334016291181</v>
       </c>
     </row>
     <row r="198" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A198" s="48"/>
       <c r="B198" s="156" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C198" s="79"/>
       <c r="D198" s="79"/>
@@ -9121,7 +9389,7 @@
     <row r="199" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A199" s="48"/>
       <c r="B199" s="74" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C199" s="74"/>
       <c r="D199" s="74"/>
@@ -9149,7 +9417,7 @@
     <row r="200" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A200" s="48"/>
       <c r="B200" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C200" s="65"/>
       <c r="D200" s="65"/>
@@ -9165,26 +9433,26 @@
         <v>17990.596799999999</v>
       </c>
       <c r="I200" s="304">
-        <f t="shared" ref="I200:L200" si="95">I197*(1+I198)*(1+I199)</f>
+        <f t="shared" ref="I200:L200" si="99">I197*(1+I198)*(1+I199)</f>
         <v>18717.416910720003</v>
       </c>
       <c r="J200" s="304">
-        <f t="shared" si="95"/>
+        <f t="shared" si="99"/>
         <v>19473.600553913093</v>
       </c>
       <c r="K200" s="304">
-        <f t="shared" si="95"/>
+        <f t="shared" si="99"/>
         <v>20260.334016291181</v>
       </c>
       <c r="L200" s="304">
-        <f t="shared" si="95"/>
+        <f t="shared" si="99"/>
         <v>21078.851510549346</v>
       </c>
     </row>
     <row r="201" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A201" s="48"/>
       <c r="B201" s="65" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C201" s="65"/>
       <c r="D201" s="65"/>
@@ -9195,23 +9463,23 @@
         <v>-0.12666666666666668</v>
       </c>
       <c r="H201" s="145">
-        <f t="shared" ref="H201:L201" si="96">(H200-G200)/G200</f>
+        <f t="shared" ref="H201:L201" si="100">(H200-G200)/G200</f>
         <v>4.0399999999999964E-2</v>
       </c>
       <c r="I201" s="145">
-        <f t="shared" si="96"/>
+        <f t="shared" si="100"/>
         <v>4.0400000000000214E-2</v>
       </c>
       <c r="J201" s="145">
-        <f t="shared" si="96"/>
+        <f t="shared" si="100"/>
         <v>4.0400000000000082E-2</v>
       </c>
       <c r="K201" s="145">
-        <f t="shared" si="96"/>
+        <f t="shared" si="100"/>
         <v>4.039999999999995E-2</v>
       </c>
       <c r="L201" s="145">
-        <f t="shared" si="96"/>
+        <f t="shared" si="100"/>
         <v>4.0400000000000075E-2</v>
       </c>
     </row>
@@ -9232,7 +9500,7 @@
     <row r="203" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A203" s="48"/>
       <c r="B203" s="65" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C203" s="65"/>
       <c r="D203" s="65"/>
@@ -9260,7 +9528,7 @@
     <row r="204" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A204" s="48"/>
       <c r="B204" s="65" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C204" s="65"/>
       <c r="D204" s="65"/>
@@ -9288,7 +9556,7 @@
     <row r="205" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="48"/>
       <c r="B205" s="72" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C205" s="72"/>
       <c r="D205" s="72"/>
@@ -9316,7 +9584,7 @@
     <row r="206" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A206" s="48"/>
       <c r="B206" s="70" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C206" s="70"/>
       <c r="D206" s="70"/>
@@ -9333,19 +9601,19 @@
         <v>25990.596799999999</v>
       </c>
       <c r="I206" s="308">
-        <f t="shared" ref="I206:L206" si="97">I200+SUM(I203:I205)</f>
+        <f t="shared" ref="I206:L206" si="101">I200+SUM(I203:I205)</f>
         <v>18717.416910720003</v>
       </c>
       <c r="J206" s="308">
-        <f t="shared" si="97"/>
+        <f t="shared" si="101"/>
         <v>19473.600553913093</v>
       </c>
       <c r="K206" s="308">
-        <f t="shared" si="97"/>
+        <f t="shared" si="101"/>
         <v>20260.334016291181</v>
       </c>
       <c r="L206" s="308">
-        <f t="shared" si="97"/>
+        <f t="shared" si="101"/>
         <v>21078.851510549346</v>
       </c>
     </row>
@@ -9363,23 +9631,23 @@
         <v>1.0501010101010102</v>
       </c>
       <c r="H207" s="160">
-        <f t="shared" ref="H207:L207" si="98">(H206-G206)/G206</f>
+        <f t="shared" ref="H207:L207" si="102">(H206-G206)/G206</f>
         <v>-0.35971135199054005</v>
       </c>
       <c r="I207" s="160">
-        <f t="shared" si="98"/>
+        <f t="shared" si="102"/>
         <v>-0.27983889501452297</v>
       </c>
       <c r="J207" s="160">
-        <f t="shared" si="98"/>
+        <f t="shared" si="102"/>
         <v>4.0400000000000082E-2</v>
       </c>
       <c r="K207" s="160">
-        <f t="shared" si="98"/>
+        <f t="shared" si="102"/>
         <v>4.039999999999995E-2</v>
       </c>
       <c r="L207" s="160">
-        <f t="shared" si="98"/>
+        <f t="shared" si="102"/>
         <v>4.0400000000000075E-2</v>
       </c>
     </row>
@@ -9400,7 +9668,7 @@
     <row r="209" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A209" s="48"/>
       <c r="B209" s="85" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C209" s="86"/>
       <c r="D209" s="87"/>
@@ -9430,7 +9698,7 @@
     <row r="211" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A211" s="48"/>
       <c r="B211" s="65" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C211" s="65"/>
       <c r="D211" s="65"/>
@@ -9441,30 +9709,30 @@
         <v>29041</v>
       </c>
       <c r="H211" s="311">
-        <f t="shared" ref="H211:L211" si="99">G214</f>
+        <f t="shared" ref="H211:L211" si="103">G214</f>
         <v>31794</v>
       </c>
       <c r="I211" s="311">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>35024.270400000001</v>
       </c>
       <c r="J211" s="311">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>38582.736272640002</v>
       </c>
       <c r="K211" s="311">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>42502.742277940233</v>
       </c>
       <c r="L211" s="311">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>46604.256907761461</v>
       </c>
     </row>
     <row r="212" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A212" s="48"/>
       <c r="B212" s="65" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C212" s="65"/>
       <c r="D212" s="65"/>
@@ -9495,7 +9763,7 @@
     <row r="213" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="48"/>
       <c r="B213" s="72" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C213" s="72"/>
       <c r="D213" s="72"/>
@@ -9521,7 +9789,7 @@
     <row r="214" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A214" s="48"/>
       <c r="B214" s="70" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C214" s="70"/>
       <c r="D214" s="70"/>
@@ -9537,19 +9805,19 @@
         <v>35024.270400000001</v>
       </c>
       <c r="I214" s="311">
-        <f t="shared" ref="I214:L214" si="100">I211*(1+I212)*(1+I213)</f>
+        <f t="shared" ref="I214:L214" si="104">I211*(1+I212)*(1+I213)</f>
         <v>38582.736272640002</v>
       </c>
       <c r="J214" s="311">
-        <f t="shared" si="100"/>
+        <f t="shared" si="104"/>
         <v>42502.742277940233</v>
       </c>
       <c r="K214" s="311">
-        <f t="shared" si="100"/>
+        <f t="shared" si="104"/>
         <v>46604.256907761461</v>
       </c>
       <c r="L214" s="311">
-        <f t="shared" si="100"/>
+        <f t="shared" si="104"/>
         <v>51101.567699360443</v>
       </c>
     </row>
@@ -9567,23 +9835,23 @@
         <v>9.4797011122206537E-2</v>
       </c>
       <c r="H215" s="160">
-        <f t="shared" ref="H215:L215" si="101">(H214-G214)/G214</f>
+        <f t="shared" ref="H215:L215" si="105">(H214-G214)/G214</f>
         <v>0.10160000000000004</v>
       </c>
       <c r="I215" s="160">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>0.10160000000000002</v>
       </c>
       <c r="J215" s="160">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>0.10160000000000016</v>
       </c>
       <c r="K215" s="160">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>9.6499999999999878E-2</v>
       </c>
       <c r="L215" s="160">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>9.650000000000003E-2</v>
       </c>
     </row>
@@ -9604,7 +9872,7 @@
     <row r="217" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A217" s="48"/>
       <c r="B217" s="85" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C217" s="86"/>
       <c r="D217" s="87"/>
@@ -9634,7 +9902,7 @@
     <row r="219" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A219" s="48"/>
       <c r="B219" s="65" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C219" s="65"/>
       <c r="D219" s="65"/>
@@ -9654,22 +9922,22 @@
         <v>65325.669400000006</v>
       </c>
       <c r="J219" s="311">
-        <f t="shared" ref="J219:L219" si="102">I222</f>
+        <f t="shared" ref="J219:L219" si="106">I222</f>
         <v>71322.56585092</v>
       </c>
       <c r="K219" s="311">
-        <f t="shared" si="102"/>
+        <f t="shared" si="106"/>
         <v>77502.666181902227</v>
       </c>
       <c r="L219" s="311">
-        <f t="shared" si="102"/>
+        <f t="shared" si="106"/>
         <v>83819.133475727256</v>
       </c>
     </row>
     <row r="220" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A220" s="48"/>
       <c r="B220" s="65" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C220" s="65"/>
       <c r="D220" s="65"/>
@@ -9700,7 +9968,7 @@
     <row r="221" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="48"/>
       <c r="B221" s="72" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C221" s="72"/>
       <c r="D221" s="72"/>
@@ -9726,7 +9994,7 @@
     <row r="222" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A222" s="48"/>
       <c r="B222" s="70" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C222" s="65"/>
       <c r="D222" s="65"/>
@@ -9736,7 +10004,7 @@
         <v>53924</v>
       </c>
       <c r="G222" s="311">
-        <f t="shared" ref="G222" si="103">G219</f>
+        <f t="shared" ref="G222" si="107">G219</f>
         <v>59833</v>
       </c>
       <c r="H222" s="311">
@@ -9744,19 +10012,19 @@
         <v>65325.669400000006</v>
       </c>
       <c r="I222" s="311">
-        <f t="shared" ref="I222:L222" si="104">I219*(1+I220)*(1+I221)</f>
+        <f t="shared" ref="I222:L222" si="108">I219*(1+I220)*(1+I221)</f>
         <v>71322.56585092</v>
       </c>
       <c r="J222" s="311">
-        <f t="shared" si="104"/>
+        <f t="shared" si="108"/>
         <v>77502.666181902227</v>
       </c>
       <c r="K222" s="311">
-        <f t="shared" si="104"/>
+        <f t="shared" si="108"/>
         <v>83819.133475727256</v>
       </c>
       <c r="L222" s="311">
-        <f t="shared" si="104"/>
+        <f t="shared" si="108"/>
         <v>90650.39285399903</v>
       </c>
     </row>
@@ -9774,23 +10042,23 @@
         <v>0.10958014984051628</v>
       </c>
       <c r="H223" s="160">
-        <f t="shared" ref="H223:L223" si="105">(H222-G222)/G222</f>
+        <f t="shared" ref="H223:L223" si="109">(H222-G222)/G222</f>
         <v>9.1800000000000104E-2</v>
       </c>
       <c r="I223" s="160">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>9.1799999999999896E-2</v>
       </c>
       <c r="J223" s="160">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>8.6650000000000116E-2</v>
       </c>
       <c r="K223" s="160">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>8.1499999999999975E-2</v>
       </c>
       <c r="L223" s="160">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>8.1500000000000031E-2</v>
       </c>
     </row>
@@ -9811,7 +10079,7 @@
     <row r="225" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A225" s="48"/>
       <c r="B225" s="319" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C225" s="320"/>
       <c r="D225" s="321"/>
@@ -9841,7 +10109,7 @@
     <row r="227" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A227" s="48"/>
       <c r="B227" s="129" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C227" s="70"/>
       <c r="D227" s="65"/>
@@ -9851,44 +10119,44 @@
         <v>22299</v>
       </c>
       <c r="G227" s="193">
-        <f t="shared" ref="G227:L227" si="106">G193</f>
+        <f t="shared" ref="G227:L227" si="110">G193</f>
         <v>21925</v>
       </c>
       <c r="H227" s="193">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>23034.404999999999</v>
       </c>
       <c r="I227" s="193">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>24199.945893</v>
       </c>
       <c r="J227" s="193">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>25424.4631551858</v>
       </c>
       <c r="K227" s="193">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>26710.940990838204</v>
       </c>
       <c r="L227" s="193">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>28062.514604974618</v>
       </c>
     </row>
     <row r="228" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A228" s="48"/>
       <c r="B228" s="129" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C228" s="65"/>
       <c r="D228" s="65"/>
       <c r="E228" s="65"/>
       <c r="F228" s="193">
-        <f t="shared" ref="F228:L228" si="107">F206</f>
+        <f t="shared" ref="F228:L228" si="111">F206</f>
         <v>19800</v>
       </c>
       <c r="G228" s="193">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>40592</v>
       </c>
       <c r="H228" s="311">
@@ -9896,63 +10164,63 @@
         <v>25990.596799999999</v>
       </c>
       <c r="I228" s="311">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>18717.416910720003</v>
       </c>
       <c r="J228" s="311">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>19473.600553913093</v>
       </c>
       <c r="K228" s="311">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>20260.334016291181</v>
       </c>
       <c r="L228" s="311">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>21078.851510549346</v>
       </c>
     </row>
     <row r="229" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A229" s="48"/>
       <c r="B229" s="129" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C229" s="65"/>
       <c r="D229" s="65"/>
       <c r="E229" s="65"/>
       <c r="F229" s="193">
-        <f t="shared" ref="F229:L229" si="108">F214</f>
+        <f t="shared" ref="F229:L229" si="112">F214</f>
         <v>29041</v>
       </c>
       <c r="G229" s="193">
-        <f t="shared" si="108"/>
+        <f t="shared" si="112"/>
         <v>31794</v>
       </c>
       <c r="H229" s="311">
-        <f t="shared" si="108"/>
+        <f t="shared" si="112"/>
         <v>35024.270400000001</v>
       </c>
       <c r="I229" s="311">
-        <f t="shared" si="108"/>
+        <f t="shared" si="112"/>
         <v>38582.736272640002</v>
       </c>
       <c r="J229" s="311">
-        <f t="shared" si="108"/>
+        <f t="shared" si="112"/>
         <v>42502.742277940233</v>
       </c>
       <c r="K229" s="311">
-        <f t="shared" si="108"/>
+        <f t="shared" si="112"/>
         <v>46604.256907761461</v>
       </c>
       <c r="L229" s="311">
-        <f t="shared" si="108"/>
+        <f t="shared" si="112"/>
         <v>51101.567699360443</v>
       </c>
     </row>
     <row r="230" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="48"/>
       <c r="B230" s="347" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C230" s="72"/>
       <c r="D230" s="72"/>
@@ -9962,7 +10230,7 @@
         <v>53924</v>
       </c>
       <c r="G230" s="316">
-        <f t="shared" ref="G230" si="109">G222</f>
+        <f t="shared" ref="G230" si="113">G222</f>
         <v>59833</v>
       </c>
       <c r="H230" s="326">
@@ -9970,19 +10238,19 @@
         <v>65325.669400000006</v>
       </c>
       <c r="I230" s="326">
-        <f t="shared" ref="I230:L230" si="110">I222</f>
+        <f t="shared" ref="I230:L230" si="114">I222</f>
         <v>71322.56585092</v>
       </c>
       <c r="J230" s="326">
-        <f t="shared" si="110"/>
+        <f t="shared" si="114"/>
         <v>77502.666181902227</v>
       </c>
       <c r="K230" s="326">
-        <f t="shared" si="110"/>
+        <f t="shared" si="114"/>
         <v>83819.133475727256</v>
       </c>
       <c r="L230" s="326">
-        <f t="shared" si="110"/>
+        <f t="shared" si="114"/>
         <v>90650.39285399903</v>
       </c>
     </row>
@@ -10007,19 +10275,19 @@
         <v>149374.94160000002</v>
       </c>
       <c r="I231" s="311">
-        <f t="shared" ref="I231:L231" si="111">SUM(I227:I230)</f>
+        <f t="shared" ref="I231:L231" si="115">SUM(I227:I230)</f>
         <v>152822.66492727998</v>
       </c>
       <c r="J231" s="311">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>164903.47216894134</v>
       </c>
       <c r="K231" s="311">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>177394.66539061809</v>
       </c>
       <c r="L231" s="311">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>190893.32666888344</v>
       </c>
     </row>
@@ -10037,23 +10305,23 @@
         <v>0.23252094927397174</v>
       </c>
       <c r="H232" s="197">
-        <f t="shared" ref="H232:L232" si="112">(H231-G231)/G231</f>
+        <f t="shared" ref="H232:L232" si="116">(H231-G231)/G231</f>
         <v>-3.0938981731367939E-2</v>
       </c>
       <c r="I232" s="197">
-        <f t="shared" si="112"/>
+        <f t="shared" si="116"/>
         <v>2.3081002009777279E-2</v>
       </c>
       <c r="J232" s="197">
-        <f t="shared" si="112"/>
+        <f t="shared" si="116"/>
         <v>7.9051148907853155E-2</v>
       </c>
       <c r="K232" s="197">
-        <f t="shared" si="112"/>
+        <f t="shared" si="116"/>
         <v>7.5748515524765234E-2</v>
       </c>
       <c r="L232" s="197">
-        <f t="shared" si="112"/>
+        <f t="shared" si="116"/>
         <v>7.609395270450596E-2</v>
       </c>
     </row>
@@ -10074,7 +10342,7 @@
     <row r="234" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A234" s="48"/>
       <c r="B234" s="65" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C234" s="70"/>
       <c r="D234" s="70"/>
@@ -10090,7 +10358,7 @@
     <row r="235" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A235" s="48"/>
       <c r="B235" s="129" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C235" s="70"/>
       <c r="D235" s="70"/>
@@ -10100,7 +10368,7 @@
         <v>0.33661965073882172</v>
       </c>
       <c r="G235" s="108">
-        <f t="shared" ref="G235:L235" si="113">SUM(G227, G228)/G$231</f>
+        <f t="shared" ref="G235:L235" si="117">SUM(G227, G228)/G$231</f>
         <v>0.40557530620718291</v>
       </c>
       <c r="H235" s="108">
@@ -10108,93 +10376,93 @@
         <v>0.32820097718451585</v>
       </c>
       <c r="I235" s="108">
-        <f t="shared" si="113"/>
+        <f t="shared" si="117"/>
         <v>0.28083113734564208</v>
       </c>
       <c r="J235" s="108">
-        <f t="shared" si="113"/>
+        <f t="shared" si="117"/>
         <v>0.27226875892037883</v>
       </c>
       <c r="K235" s="108">
-        <f t="shared" si="113"/>
+        <f t="shared" si="117"/>
         <v>0.26478403340765605</v>
       </c>
       <c r="L235" s="108">
-        <f t="shared" si="113"/>
+        <f t="shared" si="117"/>
         <v>0.25742841288927182</v>
       </c>
     </row>
     <row r="236" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A236" s="48"/>
       <c r="B236" s="129" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C236" s="70"/>
       <c r="D236" s="70"/>
       <c r="E236" s="70"/>
       <c r="F236" s="108">
-        <f t="shared" ref="F236:L237" si="114">F229/F$231</f>
+        <f t="shared" ref="F236:L237" si="118">F229/F$231</f>
         <v>0.23220910893622465</v>
       </c>
       <c r="G236" s="108">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>0.20626167739256798</v>
       </c>
       <c r="H236" s="108">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>0.23447219476603295</v>
       </c>
       <c r="I236" s="108">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>0.25246736988259844</v>
       </c>
       <c r="J236" s="108">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>0.25774316161394561</v>
       </c>
       <c r="K236" s="108">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>0.26271509802811821</v>
       </c>
       <c r="L236" s="108">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>0.26769698339428777</v>
       </c>
     </row>
     <row r="237" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A237" s="48"/>
       <c r="B237" s="129" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C237" s="70"/>
       <c r="D237" s="70"/>
       <c r="E237" s="70"/>
       <c r="F237" s="108">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>0.43117124032495363</v>
       </c>
       <c r="G237" s="108">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>0.38816301640024914</v>
       </c>
       <c r="H237" s="108">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>0.43732682804945106</v>
       </c>
       <c r="I237" s="108">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>0.4667014927717596</v>
       </c>
       <c r="J237" s="108">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>0.46998807946567561</v>
       </c>
       <c r="K237" s="108">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>0.4725008685642258</v>
       </c>
       <c r="L237" s="108">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>0.47487460371644041</v>
       </c>
     </row>
@@ -10297,26 +10565,26 @@
         <v>2027</v>
       </c>
       <c r="I243" s="58">
-        <f t="shared" ref="I243" si="115">H243+1</f>
+        <f t="shared" ref="I243" si="119">H243+1</f>
         <v>2028</v>
       </c>
       <c r="J243" s="58">
-        <f t="shared" ref="J243" si="116">I243+1</f>
+        <f t="shared" ref="J243" si="120">I243+1</f>
         <v>2029</v>
       </c>
       <c r="K243" s="58">
-        <f t="shared" ref="K243" si="117">J243+1</f>
+        <f t="shared" ref="K243" si="121">J243+1</f>
         <v>2030</v>
       </c>
       <c r="L243" s="58">
-        <f t="shared" ref="L243" si="118">K243+1</f>
+        <f t="shared" ref="L243" si="122">K243+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="244" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="48"/>
       <c r="B244" s="59" t="s">
-        <v>53</v>
+        <v>223</v>
       </c>
       <c r="C244" s="59"/>
       <c r="D244" s="59"/>
@@ -10350,7 +10618,7 @@
     <row r="246" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A246" s="48"/>
       <c r="B246" s="85" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C246" s="86"/>
       <c r="D246" s="87"/>
@@ -10380,15 +10648,15 @@
     <row r="248" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A248" s="48"/>
       <c r="B248" s="65" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C248" s="70"/>
       <c r="D248" s="65"/>
       <c r="E248" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="F248" s="365" t="s">
         <v>297</v>
-      </c>
-      <c r="F248" s="365" t="s">
-        <v>298</v>
       </c>
       <c r="G248" s="91"/>
       <c r="H248" s="92"/>
@@ -10400,7 +10668,7 @@
     <row r="249" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A249" s="48"/>
       <c r="B249" s="129" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C249" s="70"/>
       <c r="D249" s="65"/>
@@ -10420,7 +10688,7 @@
     <row r="250" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A250" s="48"/>
       <c r="B250" s="129" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C250" s="70"/>
       <c r="D250" s="65"/>
@@ -10440,7 +10708,7 @@
     <row r="251" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A251" s="48"/>
       <c r="B251" s="129" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C251" s="70"/>
       <c r="D251" s="65"/>
@@ -10474,7 +10742,7 @@
     <row r="253" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A253" s="48"/>
       <c r="B253" s="65" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C253" s="70"/>
       <c r="D253" s="65"/>
@@ -10505,7 +10773,7 @@
     <row r="254" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A254" s="48"/>
       <c r="B254" s="65" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C254" s="70"/>
       <c r="D254" s="65"/>
@@ -10536,7 +10804,7 @@
     <row r="255" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A255" s="48"/>
       <c r="B255" s="65" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C255" s="70"/>
       <c r="D255" s="65"/>
@@ -10567,7 +10835,7 @@
     <row r="256" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A256" s="48"/>
       <c r="B256" s="65" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C256" s="70"/>
       <c r="D256" s="65"/>
@@ -10599,7 +10867,7 @@
     <row r="257" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A257" s="48"/>
       <c r="B257" s="132" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C257" s="131"/>
       <c r="D257" s="131"/>
@@ -10633,7 +10901,7 @@
     <row r="258" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A258" s="48"/>
       <c r="B258" s="65" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C258" s="70"/>
       <c r="D258" s="70"/>
@@ -10667,7 +10935,7 @@
     <row r="259" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A259" s="48"/>
       <c r="B259" s="74" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C259" s="78"/>
       <c r="D259" s="78"/>
@@ -10701,7 +10969,7 @@
     <row r="260" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A260" s="48"/>
       <c r="B260" s="65" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C260" s="70"/>
       <c r="D260" s="65"/>
@@ -10715,19 +10983,19 @@
         <v>22527.543999999998</v>
       </c>
       <c r="I260" s="193">
-        <f t="shared" ref="I260:L260" si="119">SUM(I257:I259)</f>
+        <f t="shared" ref="I260:L260" si="123">SUM(I257:I259)</f>
         <v>23938.793486399998</v>
       </c>
       <c r="J260" s="193">
-        <f t="shared" si="119"/>
+        <f t="shared" si="123"/>
         <v>25316.756118994857</v>
       </c>
       <c r="K260" s="193">
-        <f t="shared" si="119"/>
+        <f t="shared" si="123"/>
         <v>26645.327458196167</v>
       </c>
       <c r="L260" s="193">
-        <f t="shared" si="119"/>
+        <f t="shared" si="123"/>
         <v>28044.28333899278</v>
       </c>
       <c r="Q260" s="35"/>
@@ -10749,15 +11017,15 @@
     <row r="262" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A262" s="48"/>
       <c r="B262" s="65" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C262" s="70"/>
       <c r="D262" s="65"/>
       <c r="E262" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="F262" s="365" t="s">
         <v>297</v>
-      </c>
-      <c r="F262" s="365" t="s">
-        <v>298</v>
       </c>
       <c r="G262" s="309"/>
       <c r="H262" s="193"/>
@@ -10769,7 +11037,7 @@
     <row r="263" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A263" s="48"/>
       <c r="B263" s="129" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C263" s="70"/>
       <c r="D263" s="65"/>
@@ -10789,7 +11057,7 @@
     <row r="264" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A264" s="48"/>
       <c r="B264" s="129" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C264" s="70"/>
       <c r="D264" s="65"/>
@@ -10809,7 +11077,7 @@
     <row r="265" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A265" s="48"/>
       <c r="B265" s="129" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C265" s="70"/>
       <c r="D265" s="65"/>
@@ -10843,7 +11111,7 @@
     <row r="267" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A267" s="48"/>
       <c r="B267" s="65" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C267" s="70"/>
       <c r="D267" s="65"/>
@@ -10874,7 +11142,7 @@
     <row r="268" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A268" s="48"/>
       <c r="B268" s="65" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C268" s="70"/>
       <c r="D268" s="65"/>
@@ -10905,7 +11173,7 @@
     <row r="269" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A269" s="48"/>
       <c r="B269" s="65" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C269" s="70"/>
       <c r="D269" s="65"/>
@@ -10936,7 +11204,7 @@
     <row r="270" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A270" s="48"/>
       <c r="B270" s="65" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C270" s="70"/>
       <c r="D270" s="65"/>
@@ -10967,7 +11235,7 @@
     <row r="271" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A271" s="48"/>
       <c r="B271" s="132" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C271" s="131"/>
       <c r="D271" s="131"/>
@@ -10982,26 +11250,26 @@
         <v>33774.890240000001</v>
       </c>
       <c r="I271" s="352">
-        <f t="shared" ref="I271:L271" si="120">H271*(1+(I267*$F263))*(1+I268)</f>
+        <f t="shared" ref="I271:L271" si="124">H271*(1+(I267*$F263))*(1+I268)</f>
         <v>37233.439000576</v>
       </c>
       <c r="J271" s="352">
-        <f t="shared" si="120"/>
+        <f t="shared" si="124"/>
         <v>40656.122880703944</v>
       </c>
       <c r="K271" s="352">
-        <f t="shared" si="120"/>
+        <f t="shared" si="124"/>
         <v>43969.596895481314</v>
       </c>
       <c r="L271" s="352">
-        <f t="shared" si="120"/>
+        <f t="shared" si="124"/>
         <v>47553.119042463048</v>
       </c>
     </row>
     <row r="272" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A272" s="48"/>
       <c r="B272" s="65" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C272" s="70"/>
       <c r="D272" s="70"/>
@@ -11016,26 +11284,26 @@
         <v>9431.4787840000008</v>
       </c>
       <c r="I272" s="311">
-        <f t="shared" ref="I272:L272" si="121">H272*(1+(I267*$F264))*(1+I269)</f>
+        <f t="shared" ref="I272:L272" si="125">H272*(1+(I267*$F264))*(1+I269)</f>
         <v>10161.852501032961</v>
       </c>
       <c r="J272" s="311">
-        <f t="shared" si="121"/>
+        <f t="shared" si="125"/>
         <v>10864.595410741895</v>
       </c>
       <c r="K272" s="311">
-        <f t="shared" si="121"/>
+        <f t="shared" si="125"/>
         <v>11526.249271256076</v>
       </c>
       <c r="L272" s="311">
-        <f t="shared" si="121"/>
+        <f t="shared" si="125"/>
         <v>12228.197851875573</v>
       </c>
     </row>
     <row r="273" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A273" s="48"/>
       <c r="B273" s="74" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C273" s="78"/>
       <c r="D273" s="78"/>
@@ -11050,26 +11318,26 @@
         <v>4688.4281600000004</v>
       </c>
       <c r="I273" s="353">
-        <f t="shared" ref="I273:L273" si="122">H273*(1+(I267*$F265))*(1+I270)</f>
+        <f t="shared" ref="I273:L273" si="126">H273*(1+(I267*$F265))*(1+I270)</f>
         <v>5022.2442449920009</v>
       </c>
       <c r="J273" s="353">
-        <f t="shared" si="122"/>
+        <f t="shared" si="126"/>
         <v>5340.9684203898059</v>
       </c>
       <c r="K273" s="353">
-        <f t="shared" si="122"/>
+        <f t="shared" si="126"/>
         <v>5638.727409826538</v>
       </c>
       <c r="L273" s="353">
-        <f t="shared" si="122"/>
+        <f t="shared" si="126"/>
         <v>5953.0864629243679</v>
       </c>
     </row>
     <row r="274" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A274" s="48"/>
       <c r="B274" s="65" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C274" s="70"/>
       <c r="D274" s="65"/>
@@ -11083,19 +11351,19 @@
         <v>47894.797184000003</v>
       </c>
       <c r="I274" s="193">
-        <f t="shared" ref="I274" si="123">SUM(I271:I273)</f>
+        <f t="shared" ref="I274" si="127">SUM(I271:I273)</f>
         <v>52417.535746600959</v>
       </c>
       <c r="J274" s="193">
-        <f t="shared" ref="J274" si="124">SUM(J271:J273)</f>
+        <f t="shared" ref="J274" si="128">SUM(J271:J273)</f>
         <v>56861.686711835646</v>
       </c>
       <c r="K274" s="193">
-        <f t="shared" ref="K274" si="125">SUM(K271:K273)</f>
+        <f t="shared" ref="K274" si="129">SUM(K271:K273)</f>
         <v>61134.573576563933</v>
       </c>
       <c r="L274" s="193">
-        <f t="shared" ref="L274" si="126">SUM(L271:L273)</f>
+        <f t="shared" ref="L274" si="130">SUM(L271:L273)</f>
         <v>65734.403357262985</v>
       </c>
     </row>
@@ -11116,15 +11384,15 @@
     <row r="276" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A276" s="48"/>
       <c r="B276" s="65" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C276" s="70"/>
       <c r="D276" s="65"/>
       <c r="E276" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="F276" s="365" t="s">
         <v>297</v>
-      </c>
-      <c r="F276" s="365" t="s">
-        <v>298</v>
       </c>
       <c r="G276" s="309"/>
       <c r="H276" s="193"/>
@@ -11136,7 +11404,7 @@
     <row r="277" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A277" s="48"/>
       <c r="B277" s="129" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C277" s="70"/>
       <c r="D277" s="65"/>
@@ -11156,7 +11424,7 @@
     <row r="278" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A278" s="48"/>
       <c r="B278" s="129" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C278" s="70"/>
       <c r="D278" s="65"/>
@@ -11176,7 +11444,7 @@
     <row r="279" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A279" s="48"/>
       <c r="B279" s="129" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C279" s="70"/>
       <c r="D279" s="65"/>
@@ -11210,7 +11478,7 @@
     <row r="281" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A281" s="48"/>
       <c r="B281" s="65" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C281" s="70"/>
       <c r="D281" s="65"/>
@@ -11241,7 +11509,7 @@
     <row r="282" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A282" s="48"/>
       <c r="B282" s="65" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C282" s="70"/>
       <c r="D282" s="65"/>
@@ -11272,7 +11540,7 @@
     <row r="283" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A283" s="48"/>
       <c r="B283" s="65" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C283" s="70"/>
       <c r="D283" s="65"/>
@@ -11303,7 +11571,7 @@
     <row r="284" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A284" s="48"/>
       <c r="B284" s="65" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C284" s="70"/>
       <c r="D284" s="65"/>
@@ -11334,7 +11602,7 @@
     <row r="285" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A285" s="48"/>
       <c r="B285" s="132" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C285" s="131"/>
       <c r="D285" s="131"/>
@@ -11349,26 +11617,26 @@
         <v>16048.730880000001</v>
       </c>
       <c r="I285" s="352">
-        <f t="shared" ref="I285:L285" si="127">H285*(1+(I281*$F277))*(1+I282)</f>
+        <f t="shared" ref="I285:L285" si="131">H285*(1+(I281*$F277))*(1+I282)</f>
         <v>18025.934524416003</v>
       </c>
       <c r="J285" s="352">
-        <f t="shared" si="127"/>
+        <f t="shared" si="131"/>
         <v>20149.389611392209</v>
       </c>
       <c r="K285" s="352">
-        <f t="shared" si="127"/>
+        <f t="shared" si="131"/>
         <v>22310.411647214023</v>
       </c>
       <c r="L285" s="352">
-        <f t="shared" si="127"/>
+        <f t="shared" si="131"/>
         <v>24703.203296377727</v>
       </c>
     </row>
     <row r="286" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A286" s="48"/>
       <c r="B286" s="65" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C286" s="70"/>
       <c r="D286" s="70"/>
@@ -11383,26 +11651,26 @@
         <v>4449.4894080000004</v>
       </c>
       <c r="I286" s="311">
-        <f t="shared" ref="I286:L286" si="128">H286*(1+(I281*$F278))*(1+I283)</f>
+        <f t="shared" ref="I286:L286" si="132">H286*(1+(I281*$F278))*(1+I283)</f>
         <v>4849.5874955673607</v>
       </c>
       <c r="J286" s="311">
-        <f t="shared" si="128"/>
+        <f t="shared" si="132"/>
         <v>5260.2505646920054</v>
       </c>
       <c r="K286" s="311">
-        <f t="shared" si="128"/>
+        <f t="shared" si="132"/>
         <v>5661.8706953062392</v>
       </c>
       <c r="L286" s="311">
-        <f t="shared" si="128"/>
+        <f t="shared" si="132"/>
         <v>6094.1545228928699</v>
       </c>
     </row>
     <row r="287" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A287" s="48"/>
       <c r="B287" s="74" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C287" s="78"/>
       <c r="D287" s="78"/>
@@ -11417,26 +11685,26 @@
         <v>2207.7619199999999</v>
       </c>
       <c r="I287" s="353">
-        <f t="shared" ref="I287:L287" si="129">H287*(1+(I281*$F279))*(1+I284)</f>
+        <f t="shared" ref="I287:L287" si="133">H287*(1+(I281*$F279))*(1+I284)</f>
         <v>2387.9152926720003</v>
       </c>
       <c r="J287" s="353">
-        <f t="shared" si="129"/>
+        <f t="shared" si="133"/>
         <v>2570.3520210321412</v>
       </c>
       <c r="K287" s="353">
-        <f t="shared" si="129"/>
+        <f t="shared" si="133"/>
         <v>2746.742428475472</v>
       </c>
       <c r="L287" s="353">
-        <f t="shared" si="129"/>
+        <f t="shared" si="133"/>
         <v>2935.2376276296018</v>
       </c>
     </row>
     <row r="288" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A288" s="48"/>
       <c r="B288" s="65" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C288" s="70"/>
       <c r="D288" s="65"/>
@@ -11450,19 +11718,19 @@
         <v>22705.982208000001</v>
       </c>
       <c r="I288" s="193">
-        <f t="shared" ref="I288" si="130">SUM(I285:I287)</f>
+        <f t="shared" ref="I288" si="134">SUM(I285:I287)</f>
         <v>25263.437312655366</v>
       </c>
       <c r="J288" s="193">
-        <f t="shared" ref="J288" si="131">SUM(J285:J287)</f>
+        <f t="shared" ref="J288" si="135">SUM(J285:J287)</f>
         <v>27979.992197116353</v>
       </c>
       <c r="K288" s="193">
-        <f t="shared" ref="K288" si="132">SUM(K285:K287)</f>
+        <f t="shared" ref="K288" si="136">SUM(K285:K287)</f>
         <v>30719.024770995733</v>
       </c>
       <c r="L288" s="193">
-        <f t="shared" ref="L288" si="133">SUM(L285:L287)</f>
+        <f t="shared" ref="L288" si="137">SUM(L285:L287)</f>
         <v>33732.595446900203</v>
       </c>
     </row>
@@ -11483,136 +11751,136 @@
     <row r="290" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A290" s="48"/>
       <c r="B290" s="65" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C290" s="70"/>
       <c r="D290" s="65"/>
       <c r="E290" s="65"/>
       <c r="F290" s="193"/>
       <c r="G290" s="193">
-        <f t="shared" ref="G290:L290" si="134">G260</f>
+        <f t="shared" ref="G290:L290" si="138">G260</f>
         <v>21200</v>
       </c>
       <c r="H290" s="193">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>22527.543999999998</v>
       </c>
       <c r="I290" s="193">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>23938.793486399998</v>
       </c>
       <c r="J290" s="193">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>25316.756118994857</v>
       </c>
       <c r="K290" s="193">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>26645.327458196167</v>
       </c>
       <c r="L290" s="193">
-        <f t="shared" si="134"/>
+        <f t="shared" si="138"/>
         <v>28044.28333899278</v>
       </c>
     </row>
     <row r="291" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A291" s="48"/>
       <c r="B291" s="65" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C291" s="70"/>
       <c r="D291" s="65"/>
       <c r="E291" s="65"/>
       <c r="F291" s="193"/>
       <c r="G291" s="193">
-        <f t="shared" ref="G291:L291" si="135">G274</f>
+        <f t="shared" ref="G291:L291" si="139">G274</f>
         <v>43768</v>
       </c>
       <c r="H291" s="193">
-        <f t="shared" si="135"/>
+        <f t="shared" si="139"/>
         <v>47894.797184000003</v>
       </c>
       <c r="I291" s="193">
-        <f t="shared" si="135"/>
+        <f t="shared" si="139"/>
         <v>52417.535746600959</v>
       </c>
       <c r="J291" s="193">
-        <f t="shared" si="135"/>
+        <f t="shared" si="139"/>
         <v>56861.686711835646</v>
       </c>
       <c r="K291" s="193">
-        <f t="shared" si="135"/>
+        <f t="shared" si="139"/>
         <v>61134.573576563933</v>
       </c>
       <c r="L291" s="193">
-        <f t="shared" si="135"/>
+        <f t="shared" si="139"/>
         <v>65734.403357262985</v>
       </c>
     </row>
     <row r="292" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="48"/>
       <c r="B292" s="72" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C292" s="72"/>
       <c r="D292" s="72"/>
       <c r="E292" s="72"/>
       <c r="F292" s="316"/>
       <c r="G292" s="316">
-        <f t="shared" ref="G292:L292" si="136">G288</f>
+        <f t="shared" ref="G292:L292" si="140">G288</f>
         <v>20412</v>
       </c>
       <c r="H292" s="316">
-        <f t="shared" si="136"/>
+        <f t="shared" si="140"/>
         <v>22705.982208000001</v>
       </c>
       <c r="I292" s="316">
-        <f t="shared" si="136"/>
+        <f t="shared" si="140"/>
         <v>25263.437312655366</v>
       </c>
       <c r="J292" s="316">
-        <f t="shared" si="136"/>
+        <f t="shared" si="140"/>
         <v>27979.992197116353</v>
       </c>
       <c r="K292" s="316">
-        <f t="shared" si="136"/>
+        <f t="shared" si="140"/>
         <v>30719.024770995733</v>
       </c>
       <c r="L292" s="316">
-        <f t="shared" si="136"/>
+        <f t="shared" si="140"/>
         <v>33732.595446900203</v>
       </c>
     </row>
     <row r="293" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A293" s="48"/>
       <c r="B293" s="65" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C293" s="65"/>
       <c r="D293" s="65"/>
       <c r="E293" s="65"/>
       <c r="F293" s="193"/>
       <c r="G293" s="193">
-        <f t="shared" ref="G293:L293" si="137">SUM(G290:G292)</f>
+        <f t="shared" ref="G293:L293" si="141">SUM(G290:G292)</f>
         <v>85380</v>
       </c>
       <c r="H293" s="193">
-        <f t="shared" si="137"/>
+        <f t="shared" si="141"/>
         <v>93128.323392000006</v>
       </c>
       <c r="I293" s="193">
-        <f t="shared" si="137"/>
+        <f t="shared" si="141"/>
         <v>101619.76654565633</v>
       </c>
       <c r="J293" s="193">
-        <f t="shared" si="137"/>
+        <f t="shared" si="141"/>
         <v>110158.43502794686</v>
       </c>
       <c r="K293" s="193">
-        <f t="shared" si="137"/>
+        <f t="shared" si="141"/>
         <v>118498.92580575583</v>
       </c>
       <c r="L293" s="193">
-        <f t="shared" si="137"/>
+        <f t="shared" si="141"/>
         <v>127511.28214315597</v>
       </c>
     </row>
@@ -11647,7 +11915,7 @@
     <row r="296" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A296" s="48"/>
       <c r="B296" s="85" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C296" s="86"/>
       <c r="D296" s="87"/>
@@ -11691,7 +11959,7 @@
     <row r="299" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A299" s="48"/>
       <c r="B299" s="195" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C299" s="195"/>
       <c r="D299" s="195"/>
@@ -11703,26 +11971,26 @@
         <v>44669</v>
       </c>
       <c r="I299" s="359">
-        <f t="shared" ref="I299:L299" si="138">H303</f>
+        <f t="shared" ref="I299:L299" si="142">H303</f>
         <v>46455.76</v>
       </c>
       <c r="J299" s="359">
-        <f t="shared" si="138"/>
+        <f t="shared" si="142"/>
         <v>49317.612178570496</v>
       </c>
       <c r="K299" s="359">
-        <f t="shared" si="138"/>
+        <f t="shared" si="142"/>
         <v>54675.28745649699</v>
       </c>
       <c r="L299" s="359">
-        <f t="shared" si="138"/>
+        <f t="shared" si="142"/>
         <v>60154.783195078846</v>
       </c>
     </row>
     <row r="300" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A300" s="48"/>
       <c r="B300" s="195" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C300" s="195"/>
       <c r="D300" s="195"/>
@@ -11784,7 +12052,7 @@
     <row r="302" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A302" s="48"/>
       <c r="B302" s="355" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C302" s="195"/>
       <c r="D302" s="195"/>
@@ -11810,7 +12078,7 @@
     <row r="303" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A303" s="48"/>
       <c r="B303" s="356" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C303" s="357"/>
       <c r="D303" s="357"/>
@@ -11828,19 +12096,19 @@
         <v>46455.76</v>
       </c>
       <c r="I303" s="358">
-        <f t="shared" ref="I303:L303" si="139">I299*(1+(MAX(I301, 0)*I302))*(1+I300)</f>
+        <f t="shared" ref="I303:L303" si="143">I299*(1+(MAX(I301, 0)*I302))*(1+I300)</f>
         <v>49317.612178570496</v>
       </c>
       <c r="J303" s="358">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>54675.28745649699</v>
       </c>
       <c r="K303" s="358">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>60154.783195078846</v>
       </c>
       <c r="L303" s="358">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>66202.690606727439</v>
       </c>
     </row>
@@ -12041,26 +12309,26 @@
         <v>2027</v>
       </c>
       <c r="I316" s="58">
-        <f t="shared" ref="I316" si="140">H316+1</f>
+        <f t="shared" ref="I316" si="144">H316+1</f>
         <v>2028</v>
       </c>
       <c r="J316" s="58">
-        <f t="shared" ref="J316" si="141">I316+1</f>
+        <f t="shared" ref="J316" si="145">I316+1</f>
         <v>2029</v>
       </c>
       <c r="K316" s="58">
-        <f t="shared" ref="K316" si="142">J316+1</f>
+        <f t="shared" ref="K316" si="146">J316+1</f>
         <v>2030</v>
       </c>
       <c r="L316" s="58">
-        <f t="shared" ref="L316" si="143">K316+1</f>
+        <f t="shared" ref="L316" si="147">K316+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="317" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A317" s="48"/>
       <c r="B317" s="59" t="s">
-        <v>53</v>
+        <v>223</v>
       </c>
       <c r="C317" s="59"/>
       <c r="D317" s="59"/>
@@ -12094,7 +12362,7 @@
     <row r="319" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A319" s="48"/>
       <c r="B319" s="65" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C319" s="70"/>
       <c r="D319" s="70"/>
@@ -12126,7 +12394,7 @@
     <row r="321" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A321" s="48"/>
       <c r="B321" s="85" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C321" s="86"/>
       <c r="D321" s="87"/>
@@ -12174,19 +12442,19 @@
         <v>19533.362945240817</v>
       </c>
       <c r="I323" s="193">
-        <f t="shared" ref="I323:L323" si="144">I338*I335</f>
+        <f t="shared" ref="I323:L323" si="148">I338*I335</f>
         <v>19984.212534637631</v>
       </c>
       <c r="J323" s="193">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>21563.987495519454</v>
       </c>
       <c r="K323" s="193">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>23197.427537099655</v>
       </c>
       <c r="L323" s="193">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>24962.611490973919</v>
       </c>
     </row>
@@ -12211,26 +12479,26 @@
         <v>27705.603543449441</v>
       </c>
       <c r="I324" s="193">
-        <f t="shared" ref="I324:L324" si="145">ABS(I339*I336)</f>
+        <f t="shared" ref="I324:L324" si="149">ABS(I339*I336)</f>
         <v>30231.801256004303</v>
       </c>
       <c r="J324" s="193">
-        <f t="shared" si="145"/>
+        <f t="shared" si="149"/>
         <v>32772.048466979119</v>
       </c>
       <c r="K324" s="193">
-        <f t="shared" si="145"/>
+        <f t="shared" si="149"/>
         <v>35253.337965503713</v>
       </c>
       <c r="L324" s="193">
-        <f t="shared" si="145"/>
+        <f t="shared" si="149"/>
         <v>37934.506943767003</v>
       </c>
     </row>
     <row r="325" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A325" s="48"/>
       <c r="B325" s="132" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C325" s="132"/>
       <c r="D325" s="132"/>
@@ -12240,27 +12508,27 @@
         <v>49855</v>
       </c>
       <c r="G325" s="314">
-        <f t="shared" ref="G325:L325" si="146">SUM(G323:G324)</f>
+        <f t="shared" ref="G325:L325" si="150">SUM(G323:G324)</f>
         <v>50659</v>
       </c>
       <c r="H325" s="314">
-        <f t="shared" si="146"/>
+        <f t="shared" si="150"/>
         <v>47238.966488690261</v>
       </c>
       <c r="I325" s="314">
-        <f t="shared" si="146"/>
+        <f t="shared" si="150"/>
         <v>50216.013790641933</v>
       </c>
       <c r="J325" s="314">
-        <f t="shared" si="146"/>
+        <f t="shared" si="150"/>
         <v>54336.035962498572</v>
       </c>
       <c r="K325" s="314">
-        <f t="shared" si="146"/>
+        <f t="shared" si="150"/>
         <v>58450.765502603368</v>
       </c>
       <c r="L325" s="314">
-        <f t="shared" si="146"/>
+        <f t="shared" si="150"/>
         <v>62897.118434740922</v>
       </c>
     </row>
@@ -12285,26 +12553,26 @@
         <v>15447.813240556181</v>
       </c>
       <c r="I326" s="193">
-        <f t="shared" ref="I326:L326" si="147">I340*ABS(I336)</f>
+        <f t="shared" ref="I326:L326" si="151">I340*ABS(I336)</f>
         <v>16856.345287550495</v>
       </c>
       <c r="J326" s="193">
-        <f t="shared" si="147"/>
+        <f t="shared" si="151"/>
         <v>18272.710913314339</v>
       </c>
       <c r="K326" s="193">
-        <f t="shared" si="147"/>
+        <f t="shared" si="151"/>
         <v>19656.203487617913</v>
       </c>
       <c r="L326" s="193">
-        <f t="shared" si="147"/>
+        <f t="shared" si="151"/>
         <v>21151.142862521981</v>
       </c>
     </row>
     <row r="327" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A327" s="48"/>
       <c r="B327" s="281" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C327" s="78"/>
       <c r="D327" s="78"/>
@@ -12322,26 +12590,26 @@
         <v>6083.7650726904722</v>
       </c>
       <c r="I327" s="315">
-        <f t="shared" ref="I327:L327" si="148">I335*I341</f>
+        <f t="shared" ref="I327:L327" si="152">I335*I341</f>
         <v>6224.1844665602539</v>
       </c>
       <c r="J327" s="315">
-        <f t="shared" si="148"/>
+        <f t="shared" si="152"/>
         <v>6716.2133996562543</v>
       </c>
       <c r="K327" s="315">
-        <f t="shared" si="148"/>
+        <f t="shared" si="152"/>
         <v>7224.9565946277526</v>
       </c>
       <c r="L327" s="315">
-        <f t="shared" si="148"/>
+        <f t="shared" si="152"/>
         <v>7774.7321000314651</v>
       </c>
     </row>
     <row r="328" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A328" s="48"/>
       <c r="B328" s="233" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C328" s="73"/>
       <c r="D328" s="73"/>
@@ -12359,26 +12627,26 @@
         <v>21531.578313246653</v>
       </c>
       <c r="I328" s="316">
-        <f t="shared" ref="I328:L328" si="149">SUM(I326:I327)</f>
+        <f t="shared" ref="I328:L328" si="153">SUM(I326:I327)</f>
         <v>23080.52975411075</v>
       </c>
       <c r="J328" s="316">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>24988.924312970594</v>
       </c>
       <c r="K328" s="316">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>26881.160082245668</v>
       </c>
       <c r="L328" s="316">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>28925.874962553447</v>
       </c>
     </row>
     <row r="329" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A329" s="48"/>
       <c r="B329" s="65" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C329" s="70"/>
       <c r="D329" s="70"/>
@@ -12396,19 +12664,19 @@
         <v>25707.388175443608</v>
       </c>
       <c r="I329" s="193">
-        <f t="shared" ref="I329:L329" si="150">I325-I328</f>
+        <f t="shared" ref="I329:L329" si="154">I325-I328</f>
         <v>27135.484036531183</v>
       </c>
       <c r="J329" s="193">
-        <f t="shared" si="150"/>
+        <f t="shared" si="154"/>
         <v>29347.111649527978</v>
       </c>
       <c r="K329" s="193">
-        <f t="shared" si="150"/>
+        <f t="shared" si="154"/>
         <v>31569.6054203577</v>
       </c>
       <c r="L329" s="193">
-        <f t="shared" si="150"/>
+        <f t="shared" si="154"/>
         <v>33971.243472187474</v>
       </c>
     </row>
@@ -12427,19 +12695,19 @@
         <v>1666.6118245563921</v>
       </c>
       <c r="I330" s="193">
-        <f t="shared" ref="I330:L330" si="151">H329-I329</f>
+        <f t="shared" ref="I330:L330" si="155">H329-I329</f>
         <v>-1428.095861087575</v>
       </c>
       <c r="J330" s="193">
-        <f t="shared" si="151"/>
+        <f t="shared" si="155"/>
         <v>-2211.6276129967955</v>
       </c>
       <c r="K330" s="193">
-        <f t="shared" si="151"/>
+        <f t="shared" si="155"/>
         <v>-2222.4937708297221</v>
       </c>
       <c r="L330" s="193">
-        <f t="shared" si="151"/>
+        <f t="shared" si="155"/>
         <v>-2401.6380518297738</v>
       </c>
     </row>
@@ -12474,7 +12742,7 @@
     <row r="333" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A333" s="48"/>
       <c r="B333" s="85" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C333" s="86"/>
       <c r="D333" s="87"/>
@@ -12510,68 +12778,68 @@
       <c r="D335" s="65"/>
       <c r="E335" s="65"/>
       <c r="F335" s="366">
-        <f t="shared" ref="F335:L336" si="152">F10</f>
+        <f t="shared" ref="F335:L336" si="156">F10</f>
         <v>125064</v>
       </c>
       <c r="G335" s="366">
-        <f t="shared" si="152"/>
+        <f t="shared" si="156"/>
         <v>154144</v>
       </c>
       <c r="H335" s="366">
-        <f t="shared" si="152"/>
+        <f t="shared" si="156"/>
         <v>149374.94160000002</v>
       </c>
       <c r="I335" s="366">
-        <f t="shared" si="152"/>
+        <f t="shared" si="156"/>
         <v>152822.66492727998</v>
       </c>
       <c r="J335" s="366">
-        <f t="shared" si="152"/>
+        <f t="shared" si="156"/>
         <v>164903.47216894134</v>
       </c>
       <c r="K335" s="366">
-        <f t="shared" si="152"/>
+        <f t="shared" si="156"/>
         <v>177394.66539061809</v>
       </c>
       <c r="L335" s="366">
-        <f t="shared" si="152"/>
+        <f t="shared" si="156"/>
         <v>190893.32666888344</v>
       </c>
     </row>
     <row r="336" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A336" s="48"/>
       <c r="B336" s="65" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C336" s="65"/>
       <c r="D336" s="65"/>
       <c r="E336" s="65"/>
       <c r="F336" s="366">
-        <f t="shared" si="152"/>
+        <f t="shared" si="156"/>
         <v>-85737</v>
       </c>
       <c r="G336" s="366">
-        <f t="shared" si="152"/>
+        <f t="shared" si="156"/>
         <v>-102528</v>
       </c>
       <c r="H336" s="366">
-        <f t="shared" si="152"/>
+        <f t="shared" si="156"/>
         <v>-93128.323392000006</v>
       </c>
       <c r="I336" s="366">
-        <f t="shared" si="152"/>
+        <f t="shared" si="156"/>
         <v>-101619.76654565633</v>
       </c>
       <c r="J336" s="366">
-        <f t="shared" si="152"/>
+        <f t="shared" si="156"/>
         <v>-110158.43502794686</v>
       </c>
       <c r="K336" s="366">
-        <f t="shared" si="152"/>
+        <f t="shared" si="156"/>
         <v>-118498.92580575583</v>
       </c>
       <c r="L336" s="366">
-        <f t="shared" si="152"/>
+        <f t="shared" si="156"/>
         <v>-127511.28214315597</v>
       </c>
     </row>
@@ -12592,7 +12860,7 @@
     <row r="338" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A338" s="48"/>
       <c r="B338" s="65" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C338" s="65"/>
       <c r="D338" s="65"/>
@@ -12610,26 +12878,26 @@
         <v>0.13076733444052316</v>
       </c>
       <c r="I338" s="192">
-        <f t="shared" ref="I338:L338" si="153">H338</f>
+        <f t="shared" ref="I338:L338" si="157">H338</f>
         <v>0.13076733444052316</v>
       </c>
       <c r="J338" s="192">
-        <f t="shared" si="153"/>
+        <f t="shared" si="157"/>
         <v>0.13076733444052316</v>
       </c>
       <c r="K338" s="192">
-        <f t="shared" si="153"/>
+        <f t="shared" si="157"/>
         <v>0.13076733444052316</v>
       </c>
       <c r="L338" s="192">
-        <f t="shared" si="153"/>
+        <f t="shared" si="157"/>
         <v>0.13076733444052316</v>
       </c>
     </row>
     <row r="339" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A339" s="48"/>
       <c r="B339" s="65" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C339" s="65"/>
       <c r="D339" s="65"/>
@@ -12647,26 +12915,26 @@
         <v>0.29749921972534332</v>
       </c>
       <c r="I339" s="192">
-        <f t="shared" ref="I339:L341" si="154">H339</f>
+        <f t="shared" ref="I339:L341" si="158">H339</f>
         <v>0.29749921972534332</v>
       </c>
       <c r="J339" s="192">
-        <f t="shared" si="154"/>
+        <f t="shared" si="158"/>
         <v>0.29749921972534332</v>
       </c>
       <c r="K339" s="192">
-        <f t="shared" si="154"/>
+        <f t="shared" si="158"/>
         <v>0.29749921972534332</v>
       </c>
       <c r="L339" s="192">
-        <f t="shared" si="154"/>
+        <f t="shared" si="158"/>
         <v>0.29749921972534332</v>
       </c>
     </row>
     <row r="340" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A340" s="48"/>
       <c r="B340" s="65" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C340" s="48"/>
       <c r="D340" s="48"/>
@@ -12684,26 +12952,26 @@
         <v>0.16587663857677903</v>
       </c>
       <c r="I340" s="201">
-        <f t="shared" si="154"/>
+        <f t="shared" si="158"/>
         <v>0.16587663857677903</v>
       </c>
       <c r="J340" s="201">
-        <f t="shared" si="154"/>
+        <f t="shared" si="158"/>
         <v>0.16587663857677903</v>
       </c>
       <c r="K340" s="201">
-        <f t="shared" si="154"/>
+        <f t="shared" si="158"/>
         <v>0.16587663857677903</v>
       </c>
       <c r="L340" s="201">
-        <f t="shared" si="154"/>
+        <f t="shared" si="158"/>
         <v>0.16587663857677903</v>
       </c>
     </row>
     <row r="341" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A341" s="48"/>
       <c r="B341" s="65" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C341" s="48"/>
       <c r="D341" s="48"/>
@@ -12713,7 +12981,7 @@
         <v>4.6752062943772786E-2</v>
       </c>
       <c r="G341" s="160">
-        <f t="shared" ref="G341" si="155">G327/G335</f>
+        <f t="shared" ref="G341" si="159">G327/G335</f>
         <v>4.072815030101723E-2</v>
       </c>
       <c r="H341" s="201">
@@ -12721,19 +12989,19 @@
         <v>4.072815030101723E-2</v>
       </c>
       <c r="I341" s="201">
-        <f t="shared" si="154"/>
+        <f t="shared" si="158"/>
         <v>4.072815030101723E-2</v>
       </c>
       <c r="J341" s="201">
-        <f t="shared" si="154"/>
+        <f t="shared" si="158"/>
         <v>4.072815030101723E-2</v>
       </c>
       <c r="K341" s="201">
-        <f t="shared" si="154"/>
+        <f t="shared" si="158"/>
         <v>4.072815030101723E-2</v>
       </c>
       <c r="L341" s="201">
-        <f t="shared" si="154"/>
+        <f t="shared" si="158"/>
         <v>4.072815030101723E-2</v>
       </c>
     </row>
@@ -12754,44 +13022,44 @@
     <row r="343" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A343" s="48"/>
       <c r="B343" s="65" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C343" s="48"/>
       <c r="D343" s="48"/>
       <c r="E343" s="48"/>
       <c r="F343" s="317">
-        <f t="shared" ref="F343:L343" si="156">F323/F335*$G$319</f>
+        <f t="shared" ref="F343:L343" si="160">F323/F335*$G$319</f>
         <v>63.086419753086417</v>
       </c>
       <c r="G343" s="317">
-        <f t="shared" si="156"/>
+        <f t="shared" si="160"/>
         <v>47.730077070790955</v>
       </c>
       <c r="H343" s="317">
-        <f t="shared" si="156"/>
+        <f t="shared" si="160"/>
         <v>47.730077070790955</v>
       </c>
       <c r="I343" s="317">
-        <f t="shared" si="156"/>
+        <f t="shared" si="160"/>
         <v>47.730077070790955</v>
       </c>
       <c r="J343" s="317">
-        <f t="shared" si="156"/>
+        <f t="shared" si="160"/>
         <v>47.730077070790955</v>
       </c>
       <c r="K343" s="317">
-        <f t="shared" si="156"/>
+        <f t="shared" si="160"/>
         <v>47.730077070790955</v>
       </c>
       <c r="L343" s="317">
-        <f t="shared" si="156"/>
+        <f t="shared" si="160"/>
         <v>47.730077070790955</v>
       </c>
     </row>
     <row r="344" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A344" s="48"/>
       <c r="B344" s="65" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C344" s="48"/>
       <c r="D344" s="48"/>
@@ -12809,63 +13077,63 @@
         <v>108.58721519975032</v>
       </c>
       <c r="I344" s="317">
-        <f t="shared" ref="I344:L344" si="157">H344</f>
+        <f t="shared" ref="I344:L344" si="161">H344</f>
         <v>108.58721519975032</v>
       </c>
       <c r="J344" s="317">
-        <f t="shared" si="157"/>
+        <f t="shared" si="161"/>
         <v>108.58721519975032</v>
       </c>
       <c r="K344" s="317">
-        <f t="shared" si="157"/>
+        <f t="shared" si="161"/>
         <v>108.58721519975032</v>
       </c>
       <c r="L344" s="317">
-        <f t="shared" si="157"/>
+        <f t="shared" si="161"/>
         <v>108.58721519975032</v>
       </c>
     </row>
     <row r="345" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A345" s="48"/>
       <c r="B345" s="65" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C345" s="48"/>
       <c r="D345" s="48"/>
       <c r="E345" s="48"/>
       <c r="F345" s="317">
-        <f t="shared" ref="F345:L345" si="158">F326/ABS(F336)*$G$319</f>
+        <f t="shared" ref="F345:L345" si="162">F326/ABS(F336)*$G$319</f>
         <v>72.457632060837213</v>
       </c>
       <c r="G345" s="317">
-        <f t="shared" si="158"/>
+        <f t="shared" si="162"/>
         <v>60.54497308052435</v>
       </c>
       <c r="H345" s="317">
-        <f t="shared" si="158"/>
+        <f t="shared" si="162"/>
         <v>60.54497308052435</v>
       </c>
       <c r="I345" s="317">
-        <f t="shared" si="158"/>
+        <f t="shared" si="162"/>
         <v>60.54497308052435</v>
       </c>
       <c r="J345" s="317">
-        <f t="shared" si="158"/>
+        <f t="shared" si="162"/>
         <v>60.54497308052435</v>
       </c>
       <c r="K345" s="317">
-        <f t="shared" si="158"/>
+        <f t="shared" si="162"/>
         <v>60.54497308052435</v>
       </c>
       <c r="L345" s="317">
-        <f t="shared" si="158"/>
+        <f t="shared" si="162"/>
         <v>60.54497308052435</v>
       </c>
     </row>
     <row r="346" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A346" s="48"/>
       <c r="B346" s="65" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C346" s="48"/>
       <c r="D346" s="48"/>
@@ -12875,7 +13143,7 @@
         <v>17.064502974477065</v>
       </c>
       <c r="G346" s="317">
-        <f t="shared" ref="G346" si="159">(G327/G335)*$G$319</f>
+        <f t="shared" ref="G346" si="163">(G327/G335)*$G$319</f>
         <v>14.865774859871289</v>
       </c>
       <c r="H346" s="317">
@@ -12883,19 +13151,19 @@
         <v>14.865774859871289</v>
       </c>
       <c r="I346" s="317">
-        <f t="shared" ref="I346:L346" si="160">H346</f>
+        <f t="shared" ref="I346:L346" si="164">H346</f>
         <v>14.865774859871289</v>
       </c>
       <c r="J346" s="317">
-        <f t="shared" si="160"/>
+        <f t="shared" si="164"/>
         <v>14.865774859871289</v>
       </c>
       <c r="K346" s="317">
-        <f t="shared" si="160"/>
+        <f t="shared" si="164"/>
         <v>14.865774859871289</v>
       </c>
       <c r="L346" s="317">
-        <f t="shared" si="160"/>
+        <f t="shared" si="164"/>
         <v>14.865774859871289</v>
       </c>
     </row>
@@ -13026,26 +13294,26 @@
         <v>2027</v>
       </c>
       <c r="I354" s="58">
-        <f t="shared" ref="I354" si="161">H354+1</f>
+        <f t="shared" ref="I354" si="165">H354+1</f>
         <v>2028</v>
       </c>
       <c r="J354" s="58">
-        <f t="shared" ref="J354" si="162">I354+1</f>
+        <f t="shared" ref="J354" si="166">I354+1</f>
         <v>2029</v>
       </c>
       <c r="K354" s="58">
-        <f t="shared" ref="K354" si="163">J354+1</f>
+        <f t="shared" ref="K354" si="167">J354+1</f>
         <v>2030</v>
       </c>
       <c r="L354" s="58">
-        <f t="shared" ref="L354" si="164">K354+1</f>
+        <f t="shared" ref="L354" si="168">K354+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="355" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A355" s="48"/>
       <c r="B355" s="59" t="s">
-        <v>85</v>
+        <v>223</v>
       </c>
       <c r="C355" s="59"/>
       <c r="D355" s="59"/>
@@ -13183,7 +13451,7 @@
     <row r="363" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A363" s="48"/>
       <c r="B363" s="65" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C363" s="65"/>
       <c r="D363" s="65"/>
@@ -13201,14 +13469,14 @@
     <row r="364" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A364" s="48"/>
       <c r="B364" s="65" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C364" s="65"/>
       <c r="D364" s="65"/>
       <c r="E364" s="65"/>
       <c r="F364" s="91"/>
       <c r="G364" s="173" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H364" s="172"/>
       <c r="I364" s="172"/>
@@ -13370,7 +13638,7 @@
     <row r="371" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A371" s="48"/>
       <c r="B371" s="132" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C371" s="65"/>
       <c r="D371" s="132"/>
@@ -13382,15 +13650,15 @@
         <v>150</v>
       </c>
       <c r="I371" s="314">
-        <f t="shared" ref="I371:K371" si="165">SUM(I366:I370)</f>
+        <f t="shared" ref="I371:K371" si="169">SUM(I366:I370)</f>
         <v>500</v>
       </c>
       <c r="J371" s="314">
-        <f t="shared" si="165"/>
+        <f t="shared" si="169"/>
         <v>900</v>
       </c>
       <c r="K371" s="314">
-        <f t="shared" si="165"/>
+        <f t="shared" si="169"/>
         <v>1300</v>
       </c>
       <c r="L371" s="314">
@@ -13401,7 +13669,7 @@
     <row r="372" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A372" s="48"/>
       <c r="B372" s="65" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C372" s="65"/>
       <c r="D372" s="65"/>
@@ -13432,7 +13700,7 @@
     <row r="373" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A373" s="48"/>
       <c r="B373" s="156" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C373" s="156"/>
       <c r="D373" s="156"/>
@@ -13444,19 +13712,19 @@
         <v>1262.5999999999999</v>
       </c>
       <c r="I373" s="328">
-        <f t="shared" ref="I373:L373" si="166">SUM(I371:I372)</f>
+        <f t="shared" ref="I373:L373" si="170">SUM(I371:I372)</f>
         <v>1612.6</v>
       </c>
       <c r="J373" s="328">
-        <f t="shared" si="166"/>
+        <f t="shared" si="170"/>
         <v>2012.6</v>
       </c>
       <c r="K373" s="328">
-        <f t="shared" si="166"/>
+        <f t="shared" si="170"/>
         <v>2412.6</v>
       </c>
       <c r="L373" s="328">
-        <f t="shared" si="166"/>
+        <f t="shared" si="170"/>
         <v>2812.6</v>
       </c>
     </row>
@@ -13491,7 +13759,7 @@
     <row r="376" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A376" s="48"/>
       <c r="B376" s="85" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C376" s="86"/>
       <c r="D376" s="87"/>
@@ -13521,7 +13789,7 @@
     <row r="378" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A378" s="48"/>
       <c r="B378" s="65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C378" s="65"/>
       <c r="D378" s="65"/>
@@ -13537,15 +13805,15 @@
         <v>5800.4</v>
       </c>
       <c r="J378" s="331">
-        <f t="shared" ref="J378:L378" si="167">I381</f>
+        <f t="shared" ref="J378:L378" si="171">I381</f>
         <v>6187.7999999999993</v>
       </c>
       <c r="K378" s="331">
-        <f t="shared" si="167"/>
+        <f t="shared" si="171"/>
         <v>6175.1999999999989</v>
       </c>
       <c r="L378" s="331">
-        <f t="shared" si="167"/>
+        <f t="shared" si="171"/>
         <v>5762.5999999999985</v>
       </c>
     </row>
@@ -13564,26 +13832,26 @@
         <v>1500</v>
       </c>
       <c r="I379" s="332">
-        <f t="shared" ref="I379:L379" si="168">I359</f>
+        <f t="shared" ref="I379:L379" si="172">I359</f>
         <v>2000</v>
       </c>
       <c r="J379" s="332">
-        <f t="shared" si="168"/>
+        <f t="shared" si="172"/>
         <v>2000</v>
       </c>
       <c r="K379" s="332">
-        <f t="shared" si="168"/>
+        <f t="shared" si="172"/>
         <v>2000</v>
       </c>
       <c r="L379" s="332">
-        <f t="shared" si="168"/>
+        <f t="shared" si="172"/>
         <v>2000</v>
       </c>
     </row>
     <row r="380" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A380" s="48"/>
       <c r="B380" s="74" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C380" s="74"/>
       <c r="D380" s="74"/>
@@ -13595,19 +13863,19 @@
         <v>-1262.5999999999999</v>
       </c>
       <c r="I380" s="392">
-        <f t="shared" ref="I380:L380" si="169">-I373</f>
+        <f t="shared" ref="I380:L380" si="173">-I373</f>
         <v>-1612.6</v>
       </c>
       <c r="J380" s="392">
-        <f t="shared" si="169"/>
+        <f t="shared" si="173"/>
         <v>-2012.6</v>
       </c>
       <c r="K380" s="392">
-        <f t="shared" si="169"/>
+        <f t="shared" si="173"/>
         <v>-2412.6</v>
       </c>
       <c r="L380" s="392">
-        <f t="shared" si="169"/>
+        <f t="shared" si="173"/>
         <v>-2812.6</v>
       </c>
     </row>
@@ -13659,7 +13927,7 @@
     <row r="383" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A383" s="48"/>
       <c r="B383" s="85" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C383" s="86"/>
       <c r="D383" s="87"/>
@@ -13689,7 +13957,7 @@
     <row r="385" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A385" s="48"/>
       <c r="B385" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C385" s="70"/>
       <c r="D385" s="65"/>
@@ -13701,26 +13969,26 @@
         <v>-5893</v>
       </c>
       <c r="I385" s="193">
-        <f t="shared" ref="I385:L385" si="170">I389</f>
+        <f t="shared" ref="I385:L385" si="174">I389</f>
         <v>-6396.58</v>
       </c>
       <c r="J385" s="193">
-        <f t="shared" si="170"/>
+        <f t="shared" si="174"/>
         <v>-7430.3747999999996</v>
       </c>
       <c r="K385" s="193">
-        <f t="shared" si="170"/>
+        <f t="shared" si="174"/>
         <v>-8526.1972879999994</v>
       </c>
       <c r="L385" s="193">
-        <f t="shared" si="170"/>
+        <f t="shared" si="174"/>
         <v>-9687.7691252799996</v>
       </c>
     </row>
     <row r="386" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A386" s="48"/>
       <c r="B386" s="65" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C386" s="70"/>
       <c r="D386" s="65"/>
@@ -13746,7 +14014,7 @@
     <row r="387" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A387" s="48"/>
       <c r="B387" s="132" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C387" s="131"/>
       <c r="D387" s="132"/>
@@ -13758,19 +14026,19 @@
         <v>-353.58</v>
       </c>
       <c r="I387" s="314">
-        <f t="shared" ref="I387:L387" si="171">I385*I386</f>
+        <f t="shared" ref="I387:L387" si="175">I385*I386</f>
         <v>-383.79480000000001</v>
       </c>
       <c r="J387" s="314">
-        <f t="shared" si="171"/>
+        <f t="shared" si="175"/>
         <v>-445.82248799999996</v>
       </c>
       <c r="K387" s="314">
-        <f t="shared" si="171"/>
+        <f t="shared" si="175"/>
         <v>-511.57183727999995</v>
       </c>
       <c r="L387" s="314">
-        <f t="shared" si="171"/>
+        <f t="shared" si="175"/>
         <v>-581.26614751679995</v>
       </c>
     </row>
@@ -13791,7 +14059,7 @@
     <row r="389" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A389" s="48"/>
       <c r="B389" s="65" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C389" s="65"/>
       <c r="D389" s="65"/>
@@ -13807,22 +14075,22 @@
         <v>-6396.58</v>
       </c>
       <c r="J389" s="331">
-        <f t="shared" ref="J389:L389" si="172">I393</f>
+        <f t="shared" ref="J389:L389" si="176">I393</f>
         <v>-7430.3747999999996</v>
       </c>
       <c r="K389" s="331">
-        <f t="shared" si="172"/>
+        <f t="shared" si="176"/>
         <v>-8526.1972879999994</v>
       </c>
       <c r="L389" s="331">
-        <f t="shared" si="172"/>
+        <f t="shared" si="176"/>
         <v>-9687.7691252799996</v>
       </c>
     </row>
     <row r="390" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A390" s="48"/>
       <c r="B390" s="65" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C390" s="65"/>
       <c r="D390" s="65"/>
@@ -13853,7 +14121,7 @@
     <row r="391" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A391" s="48"/>
       <c r="B391" s="65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C391" s="70"/>
       <c r="D391" s="70"/>
@@ -13865,26 +14133,26 @@
         <v>-353.58</v>
       </c>
       <c r="I391" s="331">
-        <f t="shared" ref="I391:L391" si="173">I387</f>
+        <f t="shared" ref="I391:L391" si="177">I387</f>
         <v>-383.79480000000001</v>
       </c>
       <c r="J391" s="331">
-        <f t="shared" si="173"/>
+        <f t="shared" si="177"/>
         <v>-445.82248799999996</v>
       </c>
       <c r="K391" s="331">
-        <f t="shared" si="173"/>
+        <f t="shared" si="177"/>
         <v>-511.57183727999995</v>
       </c>
       <c r="L391" s="331">
-        <f t="shared" si="173"/>
+        <f t="shared" si="177"/>
         <v>-581.26614751679995</v>
       </c>
     </row>
     <row r="392" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A392" s="48"/>
       <c r="B392" s="65" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C392" s="65"/>
       <c r="D392" s="65"/>
@@ -13910,7 +14178,7 @@
     <row r="393" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A393" s="48"/>
       <c r="B393" s="156" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C393" s="156"/>
       <c r="D393" s="156"/>
@@ -13922,19 +14190,19 @@
         <v>-6396.58</v>
       </c>
       <c r="I393" s="331">
-        <f t="shared" ref="I393:L393" si="174">SUM(I389:I392)</f>
+        <f t="shared" ref="I393:L393" si="178">SUM(I389:I392)</f>
         <v>-7430.3747999999996</v>
       </c>
       <c r="J393" s="331">
-        <f t="shared" si="174"/>
+        <f t="shared" si="178"/>
         <v>-8526.1972879999994</v>
       </c>
       <c r="K393" s="331">
-        <f t="shared" si="174"/>
+        <f t="shared" si="178"/>
         <v>-9687.7691252799996</v>
       </c>
       <c r="L393" s="331">
-        <f t="shared" si="174"/>
+        <f t="shared" si="178"/>
         <v>-10919.0352727968</v>
       </c>
     </row>
@@ -13955,7 +14223,7 @@
     <row r="395" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A395" s="48"/>
       <c r="B395" s="65" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C395" s="65"/>
       <c r="D395" s="65"/>
@@ -13967,19 +14235,19 @@
         <v>996.42000000000007</v>
       </c>
       <c r="I395" s="331">
-        <f t="shared" ref="I395:L395" si="175">I392+I391</f>
+        <f t="shared" ref="I395:L395" si="179">I392+I391</f>
         <v>966.20519999999999</v>
       </c>
       <c r="J395" s="331">
-        <f t="shared" si="175"/>
+        <f t="shared" si="179"/>
         <v>904.17751199999998</v>
       </c>
       <c r="K395" s="331">
-        <f t="shared" si="175"/>
+        <f t="shared" si="179"/>
         <v>838.42816272000005</v>
       </c>
       <c r="L395" s="331">
-        <f t="shared" si="175"/>
+        <f t="shared" si="179"/>
         <v>768.73385248320005</v>
       </c>
     </row>
@@ -14000,7 +14268,7 @@
     <row r="397" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A397" s="48"/>
       <c r="B397" s="65" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C397" s="65"/>
       <c r="D397" s="65"/>
@@ -14031,7 +14299,7 @@
     <row r="398" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A398" s="48"/>
       <c r="B398" s="65" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C398" s="65"/>
       <c r="D398" s="65"/>
@@ -14200,26 +14468,26 @@
         <v>2027</v>
       </c>
       <c r="I407" s="58">
-        <f t="shared" ref="I407" si="176">H407+1</f>
+        <f t="shared" ref="I407" si="180">H407+1</f>
         <v>2028</v>
       </c>
       <c r="J407" s="58">
-        <f t="shared" ref="J407" si="177">I407+1</f>
+        <f t="shared" ref="J407" si="181">I407+1</f>
         <v>2029</v>
       </c>
       <c r="K407" s="58">
-        <f t="shared" ref="K407" si="178">J407+1</f>
+        <f t="shared" ref="K407" si="182">J407+1</f>
         <v>2030</v>
       </c>
       <c r="L407" s="58">
-        <f t="shared" ref="L407" si="179">K407+1</f>
+        <f t="shared" ref="L407" si="183">K407+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="408" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A408" s="48"/>
       <c r="B408" s="59" t="s">
-        <v>53</v>
+        <v>223</v>
       </c>
       <c r="C408" s="59"/>
       <c r="D408" s="59"/>
@@ -14253,7 +14521,7 @@
     <row r="410" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A410" s="48"/>
       <c r="B410" s="65" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C410" s="65"/>
       <c r="D410" s="65"/>
@@ -14288,7 +14556,7 @@
     <row r="411" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A411" s="48"/>
       <c r="B411" s="65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C411" s="70"/>
       <c r="D411" s="70"/>
@@ -14334,7 +14602,7 @@
     <row r="413" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A413" s="48"/>
       <c r="B413" s="65" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C413" s="70"/>
       <c r="D413" s="70"/>
@@ -14369,7 +14637,7 @@
     <row r="414" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A414" s="48"/>
       <c r="B414" s="65" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C414" s="70"/>
       <c r="D414" s="70"/>
@@ -14415,7 +14683,7 @@
     <row r="416" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A416" s="48"/>
       <c r="B416" s="85" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C416" s="86"/>
       <c r="D416" s="87"/>
@@ -14445,7 +14713,7 @@
     <row r="418" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A418" s="48"/>
       <c r="B418" s="65" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C418" s="65"/>
       <c r="D418" s="65"/>
@@ -14463,14 +14731,14 @@
     <row r="419" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A419" s="48"/>
       <c r="B419" s="65" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C419" s="65"/>
       <c r="D419" s="65"/>
       <c r="E419" s="185"/>
       <c r="F419" s="117"/>
       <c r="G419" s="182" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H419" s="118"/>
       <c r="I419" s="118"/>
@@ -14632,7 +14900,7 @@
     <row r="426" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A426" s="48"/>
       <c r="B426" s="132" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C426" s="131"/>
       <c r="D426" s="132"/>
@@ -14640,19 +14908,19 @@
       <c r="F426" s="183"/>
       <c r="G426" s="183"/>
       <c r="H426" s="337">
-        <f t="shared" ref="H426:K426" si="180">SUM(H421:H425)</f>
+        <f t="shared" ref="H426:K426" si="184">SUM(H421:H425)</f>
         <v>141.90619452000001</v>
       </c>
       <c r="I426" s="337">
-        <f t="shared" si="180"/>
+        <f t="shared" si="184"/>
         <v>428.99392072091598</v>
       </c>
       <c r="J426" s="337">
-        <f t="shared" si="180"/>
+        <f t="shared" si="184"/>
         <v>730.83375096232623</v>
       </c>
       <c r="K426" s="337">
-        <f t="shared" si="180"/>
+        <f t="shared" si="184"/>
         <v>1056.0169816439077</v>
       </c>
       <c r="L426" s="337">
@@ -14663,7 +14931,7 @@
     <row r="427" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A427" s="48"/>
       <c r="B427" s="65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C427" s="65"/>
       <c r="D427" s="65"/>
@@ -14706,19 +14974,19 @@
         <v>777.30619451999996</v>
       </c>
       <c r="I428" s="337">
-        <f t="shared" ref="I428:L428" si="181">SUM(I426:I427)</f>
+        <f t="shared" ref="I428:L428" si="185">SUM(I426:I427)</f>
         <v>1064.393920720916</v>
       </c>
       <c r="J428" s="337">
-        <f t="shared" si="181"/>
+        <f t="shared" si="185"/>
         <v>1366.2337509623262</v>
       </c>
       <c r="K428" s="337">
-        <f t="shared" si="181"/>
+        <f t="shared" si="185"/>
         <v>1691.4169816439075</v>
       </c>
       <c r="L428" s="337">
-        <f t="shared" si="181"/>
+        <f t="shared" si="185"/>
         <v>2041.2905741004342</v>
       </c>
     </row>
@@ -14739,7 +15007,7 @@
     <row r="430" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A430" s="48"/>
       <c r="B430" s="85" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C430" s="86"/>
       <c r="D430" s="87"/>
@@ -14769,7 +15037,7 @@
     <row r="432" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A432" s="48"/>
       <c r="B432" s="65" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C432" s="70"/>
       <c r="D432" s="70"/>
@@ -14785,15 +15053,15 @@
         <v>8414.8176958799995</v>
       </c>
       <c r="J432" s="193">
-        <f t="shared" ref="J432:L432" si="182">I435</f>
+        <f t="shared" ref="J432:L432" si="186">I435</f>
         <v>10254.054408777403</v>
       </c>
       <c r="K432" s="193">
-        <f t="shared" si="182"/>
+        <f t="shared" si="186"/>
         <v>12020.986629024961</v>
       </c>
       <c r="L432" s="193">
-        <f t="shared" si="182"/>
+        <f t="shared" si="186"/>
         <v>13700.068289802797</v>
       </c>
     </row>
@@ -14812,19 +15080,19 @@
         <v>2838.1238904000002</v>
       </c>
       <c r="I433" s="193">
-        <f t="shared" ref="I433:L433" si="183">I410</f>
+        <f t="shared" ref="I433:L433" si="187">I410</f>
         <v>2903.6306336183197</v>
       </c>
       <c r="J433" s="193">
-        <f t="shared" si="183"/>
+        <f t="shared" si="187"/>
         <v>3133.1659712098854</v>
       </c>
       <c r="K433" s="193">
-        <f t="shared" si="183"/>
+        <f t="shared" si="187"/>
         <v>3370.4986424217436</v>
       </c>
       <c r="L433" s="193">
-        <f t="shared" si="183"/>
+        <f t="shared" si="187"/>
         <v>3626.9732067087853</v>
       </c>
     </row>
@@ -14843,26 +15111,26 @@
         <v>-777.30619451999996</v>
       </c>
       <c r="I434" s="329">
-        <f t="shared" ref="I434:L434" si="184">-I428</f>
+        <f t="shared" ref="I434:L434" si="188">-I428</f>
         <v>-1064.393920720916</v>
       </c>
       <c r="J434" s="329">
-        <f t="shared" si="184"/>
+        <f t="shared" si="188"/>
         <v>-1366.2337509623262</v>
       </c>
       <c r="K434" s="329">
-        <f t="shared" si="184"/>
+        <f t="shared" si="188"/>
         <v>-1691.4169816439075</v>
       </c>
       <c r="L434" s="329">
-        <f t="shared" si="184"/>
+        <f t="shared" si="188"/>
         <v>-2041.2905741004342</v>
       </c>
     </row>
     <row r="435" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A435" s="48"/>
       <c r="B435" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C435" s="65"/>
       <c r="D435" s="65"/>
@@ -14937,7 +15205,7 @@
     <row r="439" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A439" s="48"/>
       <c r="B439" s="70" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C439" s="70"/>
       <c r="D439" s="65"/>
@@ -14953,7 +15221,7 @@
     <row r="440" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A440" s="48"/>
       <c r="B440" s="65" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C440" s="70"/>
       <c r="D440" s="65"/>
@@ -14983,7 +15251,7 @@
     <row r="442" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A442" s="48"/>
       <c r="B442" s="65" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C442" s="65"/>
       <c r="D442" s="65"/>
@@ -15001,14 +15269,14 @@
     <row r="443" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A443" s="48"/>
       <c r="B443" s="70" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C443" s="70"/>
       <c r="D443" s="70"/>
       <c r="E443" s="70"/>
       <c r="F443" s="70"/>
       <c r="G443" s="182" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H443" s="102"/>
       <c r="I443" s="102"/>
@@ -15170,7 +15438,7 @@
     <row r="450" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A450" s="48"/>
       <c r="B450" s="132" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C450" s="131"/>
       <c r="D450" s="131"/>
@@ -15178,19 +15446,19 @@
       <c r="F450" s="186"/>
       <c r="G450" s="186"/>
       <c r="H450" s="337">
-        <f t="shared" ref="H450:K450" si="185">SUM(H445:H449)</f>
+        <f t="shared" ref="H450:K450" si="189">SUM(H445:H449)</f>
         <v>149.37494160000003</v>
       </c>
       <c r="I450" s="337">
-        <f t="shared" si="185"/>
+        <f t="shared" si="189"/>
         <v>451.57254812728002</v>
       </c>
       <c r="J450" s="337">
-        <f t="shared" si="185"/>
+        <f t="shared" si="189"/>
         <v>769.29868522350137</v>
       </c>
       <c r="K450" s="337">
-        <f t="shared" si="185"/>
+        <f t="shared" si="189"/>
         <v>1111.5968227830608</v>
       </c>
       <c r="L450" s="337">
@@ -15201,7 +15469,7 @@
     <row r="451" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A451" s="48"/>
       <c r="B451" s="126" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C451" s="187"/>
       <c r="D451" s="187"/>
@@ -15232,7 +15500,7 @@
     <row r="452" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A452" s="48"/>
       <c r="B452" s="65" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C452" s="70"/>
       <c r="D452" s="70"/>
@@ -15244,19 +15512,19 @@
         <v>1711.5749416000001</v>
       </c>
       <c r="I452" s="337">
-        <f t="shared" ref="I452:L452" si="186">SUM(I450:I451)</f>
+        <f t="shared" ref="I452:L452" si="190">SUM(I450:I451)</f>
         <v>2013.7725481272801</v>
       </c>
       <c r="J452" s="337">
-        <f t="shared" si="186"/>
+        <f t="shared" si="190"/>
         <v>2331.4986852235015</v>
       </c>
       <c r="K452" s="337">
-        <f t="shared" si="186"/>
+        <f t="shared" si="190"/>
         <v>2673.7968227830606</v>
       </c>
       <c r="L452" s="337">
-        <f t="shared" si="186"/>
+        <f t="shared" si="190"/>
         <v>3042.0848148425621</v>
       </c>
     </row>
@@ -15277,7 +15545,7 @@
     <row r="454" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A454" s="48"/>
       <c r="B454" s="85" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C454" s="86"/>
       <c r="D454" s="87"/>
@@ -15307,7 +15575,7 @@
     <row r="456" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A456" s="48"/>
       <c r="B456" s="65" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C456" s="70"/>
       <c r="D456" s="70"/>
@@ -15323,22 +15591,22 @@
         <v>34425.174474400003</v>
       </c>
       <c r="J456" s="193">
-        <f t="shared" ref="J456:L456" si="187">I462</f>
+        <f t="shared" ref="J456:L456" si="191">I462</f>
         <v>33939.628575545525</v>
       </c>
       <c r="K456" s="193">
-        <f t="shared" si="187"/>
+        <f t="shared" si="191"/>
         <v>33257.164612011438</v>
       </c>
       <c r="L456" s="193">
-        <f t="shared" si="187"/>
+        <f t="shared" si="191"/>
         <v>32357.314443134557</v>
       </c>
     </row>
     <row r="457" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A457" s="48"/>
       <c r="B457" s="74" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C457" s="78"/>
       <c r="D457" s="78"/>
@@ -15353,22 +15621,22 @@
         <v>26832</v>
       </c>
       <c r="J457" s="315">
-        <f t="shared" ref="J457:L457" si="188">I457</f>
+        <f t="shared" ref="J457:L457" si="192">I457</f>
         <v>26832</v>
       </c>
       <c r="K457" s="315">
-        <f t="shared" si="188"/>
+        <f t="shared" si="192"/>
         <v>26832</v>
       </c>
       <c r="L457" s="315">
-        <f t="shared" si="188"/>
+        <f t="shared" si="192"/>
         <v>26832</v>
       </c>
     </row>
     <row r="458" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A458" s="48"/>
       <c r="B458" s="65" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C458" s="70"/>
       <c r="D458" s="70"/>
@@ -15380,19 +15648,19 @@
         <v>7811</v>
       </c>
       <c r="I458" s="193">
-        <f t="shared" ref="I458:L458" si="189">I456-I457</f>
+        <f t="shared" ref="I458:L458" si="193">I456-I457</f>
         <v>7593.1744744000025</v>
       </c>
       <c r="J458" s="193">
-        <f t="shared" si="189"/>
+        <f t="shared" si="193"/>
         <v>7107.6285755455247</v>
       </c>
       <c r="K458" s="193">
-        <f t="shared" si="189"/>
+        <f t="shared" si="193"/>
         <v>6425.1646120114383</v>
       </c>
       <c r="L458" s="193">
-        <f t="shared" si="189"/>
+        <f t="shared" si="193"/>
         <v>5525.3144431345572</v>
       </c>
     </row>
@@ -15442,26 +15710,26 @@
         <v>-1711.5749416000001</v>
       </c>
       <c r="I460" s="193">
-        <f t="shared" ref="I460:L460" si="190">-I452</f>
+        <f t="shared" ref="I460:L460" si="194">-I452</f>
         <v>-2013.7725481272801</v>
       </c>
       <c r="J460" s="193">
-        <f t="shared" si="190"/>
+        <f t="shared" si="194"/>
         <v>-2331.4986852235015</v>
       </c>
       <c r="K460" s="193">
-        <f t="shared" si="190"/>
+        <f t="shared" si="194"/>
         <v>-2673.7968227830606</v>
       </c>
       <c r="L460" s="193">
-        <f t="shared" si="190"/>
+        <f t="shared" si="194"/>
         <v>-3042.0848148425621</v>
       </c>
     </row>
     <row r="461" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A461" s="48"/>
       <c r="B461" s="156" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C461" s="156"/>
       <c r="D461" s="156"/>
@@ -15473,26 +15741,26 @@
         <v>7593.1744744000007</v>
       </c>
       <c r="I461" s="328">
-        <f t="shared" ref="I461:L461" si="191">SUM(I458:I460)</f>
+        <f t="shared" ref="I461:L461" si="195">SUM(I458:I460)</f>
         <v>7107.6285755455219</v>
       </c>
       <c r="J461" s="328">
-        <f t="shared" si="191"/>
+        <f t="shared" si="195"/>
         <v>6425.1646120114365</v>
       </c>
       <c r="K461" s="328">
-        <f t="shared" si="191"/>
+        <f t="shared" si="195"/>
         <v>5525.314443134559</v>
       </c>
       <c r="L461" s="328">
-        <f t="shared" si="191"/>
+        <f t="shared" si="195"/>
         <v>4392.1628949808301</v>
       </c>
     </row>
     <row r="462" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A462" s="48"/>
       <c r="B462" s="65" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C462" s="70"/>
       <c r="D462" s="70"/>
@@ -15504,19 +15772,19 @@
         <v>34425.174474400003</v>
       </c>
       <c r="I462" s="193">
-        <f t="shared" ref="I462:L462" si="192">I461+I457</f>
+        <f t="shared" ref="I462:L462" si="196">I461+I457</f>
         <v>33939.628575545525</v>
       </c>
       <c r="J462" s="193">
-        <f t="shared" si="192"/>
+        <f t="shared" si="196"/>
         <v>33257.164612011438</v>
       </c>
       <c r="K462" s="193">
-        <f t="shared" si="192"/>
+        <f t="shared" si="196"/>
         <v>32357.314443134557</v>
       </c>
       <c r="L462" s="193">
-        <f t="shared" si="192"/>
+        <f t="shared" si="196"/>
         <v>31224.162894980829</v>
       </c>
     </row>
@@ -15568,7 +15836,7 @@
     <row r="466" spans="1:12" ht="21" x14ac:dyDescent="0.5">
       <c r="A466" s="48"/>
       <c r="B466" s="52" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C466" s="53"/>
       <c r="D466" s="51"/>
@@ -15633,26 +15901,26 @@
         <v>2027</v>
       </c>
       <c r="I469" s="58">
-        <f t="shared" ref="I469" si="193">H469+1</f>
+        <f t="shared" ref="I469" si="197">H469+1</f>
         <v>2028</v>
       </c>
       <c r="J469" s="58">
-        <f t="shared" ref="J469" si="194">I469+1</f>
+        <f t="shared" ref="J469" si="198">I469+1</f>
         <v>2029</v>
       </c>
       <c r="K469" s="58">
-        <f t="shared" ref="K469" si="195">J469+1</f>
+        <f t="shared" ref="K469" si="199">J469+1</f>
         <v>2030</v>
       </c>
       <c r="L469" s="58">
-        <f t="shared" ref="L469" si="196">K469+1</f>
+        <f t="shared" ref="L469" si="200">K469+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="470" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A470" s="48"/>
       <c r="B470" s="59" t="s">
-        <v>53</v>
+        <v>223</v>
       </c>
       <c r="C470" s="59"/>
       <c r="D470" s="59"/>
@@ -15686,7 +15954,7 @@
     <row r="472" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A472" s="48"/>
       <c r="B472" s="65" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C472" s="70"/>
       <c r="D472" s="70"/>
@@ -15717,7 +15985,7 @@
     <row r="473" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A473" s="48"/>
       <c r="B473" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C473" s="70"/>
       <c r="D473" s="70"/>
@@ -15743,7 +16011,7 @@
     <row r="474" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A474" s="48"/>
       <c r="B474" s="65" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C474" s="70"/>
       <c r="D474" s="70"/>
@@ -15774,7 +16042,7 @@
     <row r="475" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A475" s="48"/>
       <c r="B475" s="132" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C475" s="132"/>
       <c r="D475" s="131"/>
@@ -15786,26 +16054,26 @@
         <v>2833.6264599999995</v>
       </c>
       <c r="I475" s="314">
-        <f t="shared" ref="I475:L475" si="197">I472-I474</f>
+        <f t="shared" ref="I475:L475" si="201">I472-I474</f>
         <v>546.00500585799819</v>
       </c>
       <c r="J475" s="314">
-        <f t="shared" si="197"/>
+        <f t="shared" si="201"/>
         <v>-1289.4011197639511</v>
       </c>
       <c r="K475" s="314">
-        <f t="shared" si="197"/>
+        <f t="shared" si="201"/>
         <v>-1216.4573425419194</v>
       </c>
       <c r="L475" s="314">
-        <f t="shared" si="197"/>
+        <f t="shared" si="201"/>
         <v>-1175.8946946766337</v>
       </c>
     </row>
     <row r="476" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A476" s="48"/>
       <c r="B476" s="65" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C476" s="65"/>
       <c r="D476" s="65"/>
@@ -15836,7 +16104,7 @@
     <row r="477" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A477" s="48"/>
       <c r="B477" s="132" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C477" s="131"/>
       <c r="D477" s="132"/>
@@ -15848,26 +16116,26 @@
         <v>12183.290259876399</v>
       </c>
       <c r="I477" s="315">
-        <f t="shared" ref="I477:L477" si="198">SUM(I475:I476)</f>
+        <f t="shared" ref="I477:L477" si="202">SUM(I475:I476)</f>
         <v>302.98130080455121</v>
       </c>
       <c r="J477" s="315">
-        <f t="shared" si="198"/>
+        <f t="shared" si="202"/>
         <v>-3149.5454313432574</v>
       </c>
       <c r="K477" s="315">
-        <f t="shared" si="198"/>
+        <f t="shared" si="202"/>
         <v>-4056.3805438789714</v>
       </c>
       <c r="L477" s="315">
-        <f t="shared" si="198"/>
+        <f t="shared" si="202"/>
         <v>-5434.1044799724332</v>
       </c>
     </row>
     <row r="478" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A478" s="48"/>
       <c r="B478" s="79" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C478" s="156"/>
       <c r="D478" s="156"/>
@@ -15879,19 +16147,19 @@
         <v>12183.290259876399</v>
       </c>
       <c r="I478" s="340">
-        <f t="shared" ref="I478:L478" si="199">I477</f>
+        <f t="shared" ref="I478:L478" si="203">I477</f>
         <v>302.98130080455121</v>
       </c>
       <c r="J478" s="340">
-        <f t="shared" si="199"/>
+        <f t="shared" si="203"/>
         <v>-3149.5454313432574</v>
       </c>
       <c r="K478" s="340">
-        <f t="shared" si="199"/>
+        <f t="shared" si="203"/>
         <v>-4056.3805438789714</v>
       </c>
       <c r="L478" s="340">
-        <f t="shared" si="199"/>
+        <f t="shared" si="203"/>
         <v>-5434.1044799724332</v>
       </c>
     </row>
@@ -15912,7 +16180,7 @@
     <row r="480" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A480" s="48"/>
       <c r="B480" s="205" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C480" s="70"/>
       <c r="D480" s="70"/>
@@ -15928,7 +16196,7 @@
     <row r="481" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A481" s="48"/>
       <c r="B481" s="65" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C481" s="65"/>
       <c r="D481" s="70"/>
@@ -15956,7 +16224,7 @@
         <v>0</v>
       </c>
       <c r="R481" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="482" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
@@ -16006,7 +16274,7 @@
     <row r="485" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A485" s="48"/>
       <c r="B485" s="208" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C485" s="65"/>
       <c r="D485" s="65"/>
@@ -16022,7 +16290,7 @@
     <row r="486" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A486" s="48"/>
       <c r="B486" s="156" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C486" s="156"/>
       <c r="D486" s="156"/>
@@ -16038,22 +16306,22 @@
         <v>1710.0832801236011</v>
       </c>
       <c r="J486" s="203">
-        <f t="shared" ref="J486:L486" si="200">I489</f>
+        <f t="shared" ref="J486:L486" si="204">I489</f>
         <v>1710.0832801236011</v>
       </c>
       <c r="K486" s="203">
-        <f t="shared" si="200"/>
+        <f t="shared" si="204"/>
         <v>4859.6287114668585</v>
       </c>
       <c r="L486" s="203">
-        <f t="shared" si="200"/>
+        <f t="shared" si="204"/>
         <v>8916.0092553458308</v>
       </c>
     </row>
     <row r="487" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A487" s="48"/>
       <c r="B487" s="65" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C487" s="70"/>
       <c r="D487" s="70"/>
@@ -16065,26 +16333,26 @@
         <v>0</v>
       </c>
       <c r="I487" s="92">
-        <f t="shared" ref="I487:L487" si="201">MIN(MAX(0, -I478), I491-I486)</f>
+        <f t="shared" ref="I487:L487" si="205">MIN(MAX(0, -I478), I491-I486)</f>
         <v>0</v>
       </c>
       <c r="J487" s="92">
-        <f t="shared" si="201"/>
+        <f t="shared" si="205"/>
         <v>3149.5454313432574</v>
       </c>
       <c r="K487" s="92">
-        <f t="shared" si="201"/>
+        <f t="shared" si="205"/>
         <v>4056.3805438789714</v>
       </c>
       <c r="L487" s="92">
-        <f t="shared" si="201"/>
+        <f t="shared" si="205"/>
         <v>5434.1044799724332</v>
       </c>
     </row>
     <row r="488" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A488" s="48"/>
       <c r="B488" s="74" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C488" s="78"/>
       <c r="D488" s="78"/>
@@ -16096,26 +16364,26 @@
         <v>-8448.9167198763989</v>
       </c>
       <c r="I488" s="199">
-        <f t="shared" ref="I488:L488" si="202">I481</f>
+        <f t="shared" ref="I488:L488" si="206">I481</f>
         <v>0</v>
       </c>
       <c r="J488" s="199">
-        <f t="shared" si="202"/>
+        <f t="shared" si="206"/>
         <v>0</v>
       </c>
       <c r="K488" s="199">
-        <f t="shared" si="202"/>
+        <f t="shared" si="206"/>
         <v>0</v>
       </c>
       <c r="L488" s="199">
-        <f t="shared" si="202"/>
+        <f t="shared" si="206"/>
         <v>0</v>
       </c>
     </row>
     <row r="489" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A489" s="48"/>
       <c r="B489" s="65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C489" s="70"/>
       <c r="D489" s="65"/>
@@ -16129,19 +16397,19 @@
         <v>1710.0832801236011</v>
       </c>
       <c r="I489" s="202">
-        <f t="shared" ref="I489:L489" si="203">SUM(I486:I488)</f>
+        <f t="shared" ref="I489:L489" si="207">SUM(I486:I488)</f>
         <v>1710.0832801236011</v>
       </c>
       <c r="J489" s="202">
-        <f t="shared" si="203"/>
+        <f t="shared" si="207"/>
         <v>4859.6287114668585</v>
       </c>
       <c r="K489" s="202">
-        <f t="shared" si="203"/>
+        <f t="shared" si="207"/>
         <v>8916.0092553458308</v>
       </c>
       <c r="L489" s="202">
-        <f t="shared" si="203"/>
+        <f t="shared" si="207"/>
         <v>14350.113735318264</v>
       </c>
     </row>
@@ -16162,7 +16430,7 @@
     <row r="491" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A491" s="48"/>
       <c r="B491" s="65" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C491" s="70"/>
       <c r="D491" s="65"/>
@@ -16176,26 +16444,26 @@
         <v>15000</v>
       </c>
       <c r="I491" s="193">
-        <f t="shared" ref="I491:L491" si="204">H491</f>
+        <f t="shared" ref="I491:L491" si="208">H491</f>
         <v>15000</v>
       </c>
       <c r="J491" s="193">
-        <f t="shared" si="204"/>
+        <f t="shared" si="208"/>
         <v>15000</v>
       </c>
       <c r="K491" s="193">
-        <f t="shared" si="204"/>
+        <f t="shared" si="208"/>
         <v>15000</v>
       </c>
       <c r="L491" s="193">
-        <f t="shared" si="204"/>
+        <f t="shared" si="208"/>
         <v>15000</v>
       </c>
     </row>
     <row r="492" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A492" s="48"/>
       <c r="B492" s="65" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C492" s="65"/>
       <c r="D492" s="65"/>
@@ -16206,23 +16474,23 @@
         <v>4841</v>
       </c>
       <c r="H492" s="193">
-        <f t="shared" ref="H492:L492" si="205">H491-H489</f>
+        <f t="shared" ref="H492:L492" si="209">H491-H489</f>
         <v>13289.916719876399</v>
       </c>
       <c r="I492" s="193">
-        <f t="shared" si="205"/>
+        <f t="shared" si="209"/>
         <v>13289.916719876399</v>
       </c>
       <c r="J492" s="193">
-        <f t="shared" si="205"/>
+        <f t="shared" si="209"/>
         <v>10140.371288533141</v>
       </c>
       <c r="K492" s="193">
-        <f t="shared" si="205"/>
+        <f t="shared" si="209"/>
         <v>6083.9907446541692</v>
       </c>
       <c r="L492" s="193">
-        <f t="shared" si="205"/>
+        <f t="shared" si="209"/>
         <v>649.88626468173607</v>
       </c>
     </row>
@@ -16243,7 +16511,7 @@
     <row r="494" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="48"/>
       <c r="B494" s="85" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C494" s="86"/>
       <c r="D494" s="87"/>
@@ -16273,7 +16541,7 @@
     <row r="496" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="48"/>
       <c r="B496" s="65" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C496" s="65"/>
       <c r="D496" s="65"/>
@@ -16314,22 +16582,22 @@
         <v>0.01</v>
       </c>
       <c r="J497" s="223">
-        <f t="shared" ref="J497:L497" si="206">I497</f>
+        <f t="shared" ref="J497:L497" si="210">I497</f>
         <v>0.01</v>
       </c>
       <c r="K497" s="223">
-        <f t="shared" si="206"/>
+        <f t="shared" si="210"/>
         <v>0.01</v>
       </c>
       <c r="L497" s="223">
-        <f t="shared" si="206"/>
+        <f t="shared" si="210"/>
         <v>0.01</v>
       </c>
     </row>
     <row r="498" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A498" s="48"/>
       <c r="B498" s="65" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C498" s="65"/>
       <c r="D498" s="65"/>
@@ -16344,15 +16612,15 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="J498" s="225">
-        <f t="shared" ref="J498:L498" si="207">I498</f>
+        <f t="shared" ref="J498:L498" si="211">I498</f>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="K498" s="225">
-        <f t="shared" si="207"/>
+        <f t="shared" si="211"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L498" s="225">
-        <f t="shared" si="207"/>
+        <f t="shared" si="211"/>
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
@@ -16373,7 +16641,7 @@
     <row r="500" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A500" s="48"/>
       <c r="B500" s="65" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C500" s="65"/>
       <c r="D500" s="65"/>
@@ -16418,7 +16686,7 @@
     <row r="502" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A502" s="48"/>
       <c r="B502" s="85" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C502" s="86"/>
       <c r="D502" s="87"/>
@@ -16448,7 +16716,7 @@
     <row r="504" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A504" s="48"/>
       <c r="B504" s="65" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C504" s="65"/>
       <c r="D504" s="65"/>
@@ -16456,7 +16724,7 @@
       <c r="F504" s="65"/>
       <c r="G504" s="120"/>
       <c r="H504" s="92">
-        <f t="shared" ref="H504" si="208">G492*H498</f>
+        <f t="shared" ref="H504" si="212">G492*H498</f>
         <v>24.205000000000002</v>
       </c>
       <c r="I504" s="92">
@@ -16464,15 +16732,15 @@
         <v>66.449583599381995</v>
       </c>
       <c r="J504" s="92">
-        <f t="shared" ref="J504:L504" si="209">I492*J498</f>
+        <f t="shared" ref="J504:L504" si="213">I492*J498</f>
         <v>66.449583599381995</v>
       </c>
       <c r="K504" s="92">
-        <f t="shared" si="209"/>
+        <f t="shared" si="213"/>
         <v>50.701856442665701</v>
       </c>
       <c r="L504" s="92">
-        <f t="shared" si="209"/>
+        <f t="shared" si="213"/>
         <v>30.419953723270847</v>
       </c>
     </row>
@@ -16493,7 +16761,7 @@
     <row r="506" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A506" s="48"/>
       <c r="B506" s="65" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C506" s="65"/>
       <c r="D506" s="65"/>
@@ -16505,26 +16773,26 @@
         <v>883.83299999999997</v>
       </c>
       <c r="I506" s="92">
-        <f t="shared" ref="I506:L506" si="210">I500*I486</f>
+        <f t="shared" ref="I506:L506" si="214">I500*I486</f>
         <v>155.61757849124768</v>
       </c>
       <c r="J506" s="92">
-        <f t="shared" si="210"/>
+        <f t="shared" si="214"/>
         <v>162.45791161174211</v>
       </c>
       <c r="K506" s="92">
-        <f t="shared" si="210"/>
+        <f t="shared" si="214"/>
         <v>461.66472758935157</v>
       </c>
       <c r="L506" s="92">
-        <f t="shared" si="210"/>
+        <f t="shared" si="214"/>
         <v>820.27285149181637</v>
       </c>
     </row>
     <row r="507" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A507" s="48"/>
       <c r="B507" s="156" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C507" s="156"/>
       <c r="D507" s="156"/>
@@ -16536,19 +16804,19 @@
         <v>908.03800000000001</v>
       </c>
       <c r="I507" s="238">
-        <f t="shared" ref="I507:L507" si="211">SUM(I504:I506)</f>
+        <f t="shared" ref="I507:L507" si="215">SUM(I504:I506)</f>
         <v>222.06716209062967</v>
       </c>
       <c r="J507" s="238">
-        <f t="shared" si="211"/>
+        <f t="shared" si="215"/>
         <v>228.90749521112411</v>
       </c>
       <c r="K507" s="238">
-        <f t="shared" si="211"/>
+        <f t="shared" si="215"/>
         <v>512.36658403201727</v>
       </c>
       <c r="L507" s="238">
-        <f t="shared" si="211"/>
+        <f t="shared" si="215"/>
         <v>850.69280521508722</v>
       </c>
     </row>
@@ -16569,7 +16837,7 @@
     <row r="509" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A509" s="48"/>
       <c r="B509" s="85" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C509" s="86"/>
       <c r="D509" s="87"/>
@@ -16644,7 +16912,7 @@
     <row r="513" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A513" s="48"/>
       <c r="B513" s="156" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C513" s="156"/>
       <c r="D513" s="156"/>
@@ -16656,19 +16924,19 @@
         <v>65.680000000000007</v>
       </c>
       <c r="I513" s="238">
-        <f t="shared" ref="I513" si="212">SUM(I512)</f>
+        <f t="shared" ref="I513" si="216">SUM(I512)</f>
         <v>43.665716290399978</v>
       </c>
       <c r="J513" s="238">
-        <f t="shared" ref="J513" si="213">SUM(J512)</f>
+        <f t="shared" ref="J513" si="217">SUM(J512)</f>
         <v>28.331856844595823</v>
       </c>
       <c r="K513" s="238">
-        <f t="shared" ref="K513" si="214">SUM(K512)</f>
+        <f t="shared" ref="K513" si="218">SUM(K512)</f>
         <v>32.18409292223533</v>
       </c>
       <c r="L513" s="238">
-        <f t="shared" ref="L513" si="215">SUM(L512)</f>
+        <f t="shared" ref="L513" si="219">SUM(L512)</f>
         <v>35.964384720454525</v>
       </c>
     </row>
@@ -16689,7 +16957,7 @@
     <row r="515" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A515" s="48"/>
       <c r="B515" s="85" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C515" s="86"/>
       <c r="D515" s="87"/>
@@ -16724,19 +16992,19 @@
       <c r="E517" s="209"/>
       <c r="F517" s="209"/>
       <c r="G517" s="209" t="s">
+        <v>151</v>
+      </c>
+      <c r="H517" s="209" t="s">
+        <v>156</v>
+      </c>
+      <c r="I517" s="210" t="s">
         <v>152</v>
       </c>
-      <c r="H517" s="209" t="s">
-        <v>157</v>
-      </c>
-      <c r="I517" s="210" t="s">
+      <c r="J517" s="210" t="s">
         <v>153</v>
       </c>
-      <c r="J517" s="210" t="s">
-        <v>154</v>
-      </c>
       <c r="K517" s="210" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L517" s="210" t="s">
         <v>14</v>
@@ -16750,22 +17018,22 @@
       <c r="E518" s="212"/>
       <c r="F518" s="212"/>
       <c r="G518" s="212" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H518" s="212" t="s">
+        <v>157</v>
+      </c>
+      <c r="I518" s="213" t="s">
         <v>158</v>
       </c>
-      <c r="I518" s="213" t="s">
-        <v>159</v>
-      </c>
       <c r="J518" s="213" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K518" s="213" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L518" s="213" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="519" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
@@ -16785,7 +17053,7 @@
     <row r="520" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A520" s="48"/>
       <c r="B520" s="216" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C520" s="216"/>
       <c r="D520" s="216"/>
@@ -16798,13 +17066,13 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="I520" s="217" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J520" s="217" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K520" s="217" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L520" s="219">
         <v>1</v>
@@ -16949,26 +17217,26 @@
         <v>2027</v>
       </c>
       <c r="I529" s="58">
-        <f t="shared" ref="I529" si="216">H529+1</f>
+        <f t="shared" ref="I529" si="220">H529+1</f>
         <v>2028</v>
       </c>
       <c r="J529" s="58">
-        <f t="shared" ref="J529" si="217">I529+1</f>
+        <f t="shared" ref="J529" si="221">I529+1</f>
         <v>2029</v>
       </c>
       <c r="K529" s="58">
-        <f t="shared" ref="K529" si="218">J529+1</f>
+        <f t="shared" ref="K529" si="222">J529+1</f>
         <v>2030</v>
       </c>
       <c r="L529" s="58">
-        <f t="shared" ref="L529" si="219">K529+1</f>
+        <f t="shared" ref="L529" si="223">K529+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="530" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A530" s="48"/>
       <c r="B530" s="59" t="s">
-        <v>53</v>
+        <v>223</v>
       </c>
       <c r="C530" s="59"/>
       <c r="D530" s="59"/>
@@ -17002,7 +17270,7 @@
     <row r="532" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A532" s="48"/>
       <c r="B532" s="85" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C532" s="86"/>
       <c r="D532" s="87"/>
@@ -17038,38 +17306,38 @@
       <c r="D534" s="65"/>
       <c r="E534" s="65"/>
       <c r="F534" s="293">
-        <f t="shared" ref="F534:L534" si="220">F29</f>
+        <f t="shared" ref="F534:L534" si="224">F29</f>
         <v>320</v>
       </c>
       <c r="G534" s="293">
-        <f t="shared" si="220"/>
+        <f t="shared" si="224"/>
         <v>5845</v>
       </c>
       <c r="H534" s="304">
-        <f t="shared" si="220"/>
+        <f t="shared" si="224"/>
         <v>8594.9202080000123</v>
       </c>
       <c r="I534" s="304">
-        <f t="shared" si="220"/>
+        <f t="shared" si="224"/>
         <v>1323.0899572529318</v>
       </c>
       <c r="J534" s="304">
-        <f t="shared" si="220"/>
+        <f t="shared" si="224"/>
         <v>-576.64844186903974</v>
       </c>
       <c r="K534" s="304">
-        <f t="shared" si="220"/>
+        <f t="shared" si="224"/>
         <v>-2250.7979386063735</v>
       </c>
       <c r="L534" s="304">
-        <f t="shared" si="220"/>
+        <f t="shared" si="224"/>
         <v>-4216.6406490114023</v>
       </c>
     </row>
     <row r="535" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A535" s="48"/>
       <c r="B535" s="65" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C535" s="65"/>
       <c r="D535" s="65"/>
@@ -17099,7 +17367,7 @@
     <row r="536" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A536" s="48"/>
       <c r="B536" s="72" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C536" s="73"/>
       <c r="D536" s="73"/>
@@ -17131,7 +17399,7 @@
     <row r="537" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A537" s="48"/>
       <c r="B537" s="371" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C537" s="70"/>
       <c r="D537" s="70"/>
@@ -17162,7 +17430,7 @@
     <row r="538" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A538" s="48"/>
       <c r="B538" s="374" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C538" s="70"/>
       <c r="D538" s="70"/>
@@ -17188,7 +17456,7 @@
     <row r="539" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A539" s="48"/>
       <c r="B539" s="377" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C539" s="73"/>
       <c r="D539" s="73"/>
@@ -17200,19 +17468,19 @@
         <v>-2247</v>
       </c>
       <c r="I539" s="379">
-        <f t="shared" ref="I539:L539" si="221">I544</f>
+        <f t="shared" ref="I539:L539" si="225">I544</f>
         <v>0</v>
       </c>
       <c r="J539" s="379">
-        <f t="shared" si="221"/>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
       <c r="K539" s="379">
-        <f t="shared" si="221"/>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
       <c r="L539" s="379">
-        <f t="shared" si="221"/>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
     </row>
@@ -17264,7 +17532,7 @@
     <row r="542" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A542" s="48"/>
       <c r="B542" s="85" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C542" s="86"/>
       <c r="D542" s="87"/>
@@ -17294,7 +17562,7 @@
     <row r="544" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A544" s="48"/>
       <c r="B544" s="65" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C544" s="65"/>
       <c r="D544" s="65"/>
@@ -17325,7 +17593,7 @@
     <row r="545" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A545" s="48"/>
       <c r="B545" s="65" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C545" s="65"/>
       <c r="D545" s="65"/>
@@ -17368,26 +17636,26 @@
         <v>-331.47606240000368</v>
       </c>
       <c r="I546" s="379">
-        <f t="shared" ref="I546:L546" si="222">-I540</f>
+        <f t="shared" ref="I546:L546" si="226">-I540</f>
         <v>-396.9269871758795</v>
       </c>
       <c r="J546" s="379">
-        <f t="shared" si="222"/>
+        <f t="shared" si="226"/>
         <v>0</v>
       </c>
       <c r="K546" s="379">
-        <f t="shared" si="222"/>
+        <f t="shared" si="226"/>
         <v>0</v>
       </c>
       <c r="L546" s="379">
-        <f t="shared" si="222"/>
+        <f t="shared" si="226"/>
         <v>0</v>
       </c>
     </row>
     <row r="547" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A547" s="48"/>
       <c r="B547" s="70" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C547" s="70"/>
       <c r="D547" s="70"/>
@@ -17399,19 +17667,19 @@
         <v>0</v>
       </c>
       <c r="I547" s="381">
-        <f t="shared" ref="I547:L547" si="223">SUM(I544:I546)</f>
+        <f t="shared" ref="I547:L547" si="227">SUM(I544:I546)</f>
         <v>0</v>
       </c>
       <c r="J547" s="381">
-        <f t="shared" si="223"/>
+        <f t="shared" si="227"/>
         <v>0</v>
       </c>
       <c r="K547" s="381">
-        <f t="shared" si="223"/>
+        <f t="shared" si="227"/>
         <v>0</v>
       </c>
       <c r="L547" s="381">
-        <f t="shared" si="223"/>
+        <f t="shared" si="227"/>
         <v>0</v>
       </c>
     </row>
@@ -17432,7 +17700,7 @@
     <row r="549" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A549" s="48"/>
       <c r="B549" s="382" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C549" s="86"/>
       <c r="D549" s="87"/>
@@ -17462,7 +17730,7 @@
     <row r="551" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A551" s="48"/>
       <c r="B551" s="371" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C551" s="65"/>
       <c r="D551" s="65"/>
@@ -17478,7 +17746,7 @@
     <row r="552" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A552" s="48"/>
       <c r="B552" s="156" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C552" s="156"/>
       <c r="D552" s="156"/>
@@ -17509,7 +17777,7 @@
     <row r="553" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A553" s="48"/>
       <c r="B553" s="385" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C553" s="74"/>
       <c r="D553" s="74"/>
@@ -17540,7 +17808,7 @@
     <row r="554" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A554" s="48"/>
       <c r="B554" s="371" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C554" s="371"/>
       <c r="D554" s="371"/>
@@ -17552,26 +17820,26 @@
         <v>-749</v>
       </c>
       <c r="I554" s="383">
-        <f t="shared" ref="I554:L554" si="224">SUM(I552:I553)</f>
+        <f t="shared" ref="I554:L554" si="228">SUM(I552:I553)</f>
         <v>-749</v>
       </c>
       <c r="J554" s="383">
-        <f t="shared" si="224"/>
+        <f t="shared" si="228"/>
         <v>-749</v>
       </c>
       <c r="K554" s="383">
-        <f t="shared" si="224"/>
+        <f t="shared" si="228"/>
         <v>-749</v>
       </c>
       <c r="L554" s="383">
-        <f t="shared" si="224"/>
+        <f t="shared" si="228"/>
         <v>-749</v>
       </c>
     </row>
     <row r="555" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A555" s="48"/>
       <c r="B555" s="74" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C555" s="74"/>
       <c r="D555" s="74"/>
@@ -17583,26 +17851,26 @@
         <v>0</v>
       </c>
       <c r="I555" s="384">
-        <f t="shared" ref="I555:L555" si="225">I538</f>
+        <f t="shared" ref="I555:L555" si="229">I538</f>
         <v>0</v>
       </c>
       <c r="J555" s="384">
-        <f t="shared" si="225"/>
+        <f t="shared" si="229"/>
         <v>0</v>
       </c>
       <c r="K555" s="384">
-        <f t="shared" si="225"/>
+        <f t="shared" si="229"/>
         <v>0</v>
       </c>
       <c r="L555" s="384">
-        <f t="shared" si="225"/>
+        <f t="shared" si="229"/>
         <v>0</v>
       </c>
     </row>
     <row r="556" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A556" s="48"/>
       <c r="B556" s="371" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C556" s="371"/>
       <c r="D556" s="371"/>
@@ -17614,19 +17882,19 @@
         <v>-749</v>
       </c>
       <c r="I556" s="383">
-        <f t="shared" ref="I556:L556" si="226">SUM(I554:I555)</f>
+        <f t="shared" ref="I556:L556" si="230">SUM(I554:I555)</f>
         <v>-749</v>
       </c>
       <c r="J556" s="383">
-        <f t="shared" si="226"/>
+        <f t="shared" si="230"/>
         <v>-749</v>
       </c>
       <c r="K556" s="383">
-        <f t="shared" si="226"/>
+        <f t="shared" si="230"/>
         <v>-749</v>
       </c>
       <c r="L556" s="383">
-        <f t="shared" si="226"/>
+        <f t="shared" si="230"/>
         <v>-749</v>
       </c>
     </row>
@@ -17706,7 +17974,7 @@
     <row r="562" spans="1:12" ht="21" x14ac:dyDescent="0.5">
       <c r="A562" s="48"/>
       <c r="B562" s="52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C562" s="53"/>
       <c r="D562" s="51"/>
@@ -17769,25 +18037,25 @@
         <v>2027</v>
       </c>
       <c r="I565" s="58">
-        <f t="shared" ref="I565" si="227">H565+1</f>
+        <f t="shared" ref="I565" si="231">H565+1</f>
         <v>2028</v>
       </c>
       <c r="J565" s="58">
-        <f t="shared" ref="J565" si="228">I565+1</f>
+        <f t="shared" ref="J565" si="232">I565+1</f>
         <v>2029</v>
       </c>
       <c r="K565" s="58">
-        <f t="shared" ref="K565" si="229">J565+1</f>
+        <f t="shared" ref="K565" si="233">J565+1</f>
         <v>2030</v>
       </c>
       <c r="L565" s="58">
-        <f t="shared" ref="L565" si="230">K565+1</f>
+        <f t="shared" ref="L565" si="234">K565+1</f>
         <v>2031</v>
       </c>
     </row>
     <row r="566" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B566" s="59" t="s">
-        <v>53</v>
+        <v>223</v>
       </c>
       <c r="C566" s="59"/>
       <c r="D566" s="59"/>
@@ -17847,7 +18115,7 @@
     </row>
     <row r="570" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B570" s="195" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C570" s="195"/>
       <c r="D570" s="195"/>
@@ -17902,7 +18170,7 @@
     </row>
     <row r="572" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B572" s="195" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C572" s="195"/>
       <c r="D572" s="195"/>
@@ -17914,7 +18182,7 @@
         <v>2105.7554509600027</v>
       </c>
       <c r="I572" s="67">
-        <f t="shared" ref="I572" si="231">I571*I570</f>
+        <f t="shared" ref="I572" si="235">I571*I570</f>
         <v>324.15703952696828</v>
       </c>
       <c r="J572" s="67">
@@ -17922,11 +18190,11 @@
         <v>0</v>
       </c>
       <c r="K572" s="67">
-        <f t="shared" ref="K572:L572" si="232">MAX(0, K571*K570)</f>
+        <f t="shared" ref="K572:L572" si="236">MAX(0, K571*K570)</f>
         <v>0</v>
       </c>
       <c r="L572" s="67">
-        <f t="shared" si="232"/>
+        <f t="shared" si="236"/>
         <v>0</v>
       </c>
     </row>
@@ -17945,7 +18213,7 @@
     </row>
     <row r="574" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
       <c r="B574" s="85" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C574" s="86"/>
       <c r="D574" s="87"/>
@@ -17973,7 +18241,7 @@
     </row>
     <row r="576" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B576" s="195" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C576" s="195"/>
       <c r="D576" s="195"/>
@@ -17985,25 +18253,25 @@
         <v>35600</v>
       </c>
       <c r="I576" s="67">
-        <f t="shared" ref="I576:L576" si="233">H581</f>
+        <f t="shared" ref="I576:L576" si="237">H581</f>
         <v>39510.688694640005</v>
       </c>
       <c r="J576" s="67">
-        <f t="shared" si="233"/>
+        <f t="shared" si="237"/>
         <v>40112.694625190088</v>
       </c>
       <c r="K576" s="67">
-        <f t="shared" si="233"/>
+        <f t="shared" si="237"/>
         <v>39536.04618332105</v>
       </c>
       <c r="L576" s="67">
-        <f t="shared" si="233"/>
+        <f t="shared" si="237"/>
         <v>37285.248244714676</v>
       </c>
     </row>
     <row r="577" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B577" s="247" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C577" s="248"/>
       <c r="D577" s="248"/>
@@ -18033,7 +18301,7 @@
     </row>
     <row r="578" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B578" s="246" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C578" s="65"/>
       <c r="D578" s="65"/>
@@ -18045,25 +18313,25 @@
         <v>-2105.7554509600027</v>
       </c>
       <c r="I578" s="67">
-        <f t="shared" ref="I578:L578" si="234">-I572</f>
+        <f t="shared" ref="I578:L578" si="238">-I572</f>
         <v>-324.15703952696828</v>
       </c>
       <c r="J578" s="67">
-        <f t="shared" si="234"/>
+        <f t="shared" si="238"/>
         <v>0</v>
       </c>
       <c r="K578" s="67">
-        <f t="shared" si="234"/>
+        <f t="shared" si="238"/>
         <v>0</v>
       </c>
       <c r="L578" s="67">
-        <f t="shared" si="234"/>
+        <f t="shared" si="238"/>
         <v>0</v>
       </c>
     </row>
     <row r="579" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B579" s="246" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C579" s="65"/>
       <c r="D579" s="65"/>
@@ -18093,7 +18361,7 @@
     </row>
     <row r="580" spans="2:12" ht="15.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B580" s="250" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C580" s="72"/>
       <c r="D580" s="72"/>
@@ -18123,7 +18391,7 @@
     </row>
     <row r="581" spans="2:12" ht="15" x14ac:dyDescent="0.35">
       <c r="B581" s="65" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C581" s="65"/>
       <c r="D581" s="65"/>
@@ -18138,19 +18406,19 @@
         <v>39510.688694640005</v>
       </c>
       <c r="I581" s="67">
-        <f t="shared" ref="I581:L581" si="235">SUM(I576:I580)</f>
+        <f t="shared" ref="I581:L581" si="239">SUM(I576:I580)</f>
         <v>40112.694625190088</v>
       </c>
       <c r="J581" s="67">
-        <f t="shared" si="235"/>
+        <f t="shared" si="239"/>
         <v>39536.04618332105</v>
       </c>
       <c r="K581" s="67">
-        <f t="shared" si="235"/>
+        <f t="shared" si="239"/>
         <v>37285.248244714676</v>
       </c>
       <c r="L581" s="67">
-        <f t="shared" si="235"/>
+        <f t="shared" si="239"/>
         <v>33068.607595703274</v>
       </c>
     </row>
@@ -19736,4 +20004,379 @@
     <brk id="134" max="11" man="1"/>
   </rowBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92995373-322E-4852-9E4E-2C39CF53EA60}">
+  <dimension ref="A2:J24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="35.77734375" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.5546875" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" customWidth="1"/>
+    <col min="8" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" ht="28.8" x14ac:dyDescent="0.65">
+      <c r="A2" s="48"/>
+      <c r="B2" s="49" t="str">
+        <f>Cover!$B$2</f>
+        <v>Solid State PLC</v>
+      </c>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="400"/>
+      <c r="I2" s="400"/>
+      <c r="J2" s="400"/>
+    </row>
+    <row r="3" spans="1:10" ht="21" x14ac:dyDescent="0.5">
+      <c r="A3" s="48"/>
+      <c r="B3" s="52" t="s">
+        <v>321</v>
+      </c>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="278" t="str">
+        <f>"Currently Running: "&amp;CHOOSE(Assumptions!$B$10,Assumptions!$F$15,Assumptions!$F$16,Assumptions!$F$17)&amp;"Scenario"</f>
+        <v>Currently Running: Base Scenario</v>
+      </c>
+      <c r="H3" s="400"/>
+      <c r="I3" s="400"/>
+      <c r="J3" s="401"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="402" t="s">
+        <v>329</v>
+      </c>
+      <c r="C6" s="402" t="s">
+        <v>322</v>
+      </c>
+      <c r="D6" s="402" t="s">
+        <v>323</v>
+      </c>
+      <c r="E6" s="402" t="s">
+        <v>324</v>
+      </c>
+      <c r="F6" s="402" t="s">
+        <v>325</v>
+      </c>
+      <c r="G6" s="402" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="405">
+        <f>Model!G54</f>
+        <v>6568</v>
+      </c>
+      <c r="D7" s="404">
+        <v>1</v>
+      </c>
+      <c r="E7" s="405">
+        <f>D7*C7</f>
+        <v>6568</v>
+      </c>
+      <c r="F7" s="404">
+        <v>1</v>
+      </c>
+      <c r="G7" s="405">
+        <f>F7*C7</f>
+        <v>6568</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="405">
+        <f>Model!G52</f>
+        <v>20157</v>
+      </c>
+      <c r="D8" s="404">
+        <v>0.85</v>
+      </c>
+      <c r="E8" s="405">
+        <f t="shared" ref="E8:E15" si="0">D8*C8</f>
+        <v>17133.45</v>
+      </c>
+      <c r="F8" s="404">
+        <v>0.95</v>
+      </c>
+      <c r="G8" s="405">
+        <f t="shared" ref="G8:G15" si="1">F8*C8</f>
+        <v>19149.149999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="405">
+        <f>Model!G51</f>
+        <v>30502</v>
+      </c>
+      <c r="D9" s="404">
+        <v>0.6</v>
+      </c>
+      <c r="E9" s="405">
+        <f t="shared" si="0"/>
+        <v>18301.2</v>
+      </c>
+      <c r="F9" s="404">
+        <v>0.8</v>
+      </c>
+      <c r="G9" s="405">
+        <f t="shared" si="1"/>
+        <v>24401.600000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>328</v>
+      </c>
+      <c r="C10" s="405">
+        <f>Model!G58</f>
+        <v>6354</v>
+      </c>
+      <c r="D10" s="404">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="405">
+        <f t="shared" si="0"/>
+        <v>3177</v>
+      </c>
+      <c r="F10" s="404">
+        <v>0.75</v>
+      </c>
+      <c r="G10" s="405">
+        <f t="shared" si="1"/>
+        <v>4765.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="405">
+        <f>Model!G60</f>
+        <v>5563</v>
+      </c>
+      <c r="D11" s="404">
+        <v>0</v>
+      </c>
+      <c r="E11" s="405">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="404">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="405">
+        <f t="shared" si="1"/>
+        <v>2781.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C12" s="405">
+        <f>Model!H457</f>
+        <v>26832</v>
+      </c>
+      <c r="D12" s="404">
+        <v>0</v>
+      </c>
+      <c r="E12" s="405">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="404">
+        <v>0</v>
+      </c>
+      <c r="G12" s="405">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>330</v>
+      </c>
+      <c r="C13" s="405">
+        <f>Model!H456-Model!H457</f>
+        <v>7811</v>
+      </c>
+      <c r="D13" s="404">
+        <v>0</v>
+      </c>
+      <c r="E13" s="405">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="404">
+        <v>0.25</v>
+      </c>
+      <c r="G13" s="405">
+        <f t="shared" si="1"/>
+        <v>1952.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>332</v>
+      </c>
+      <c r="C14" s="405">
+        <v>2392</v>
+      </c>
+      <c r="D14" s="404">
+        <v>0</v>
+      </c>
+      <c r="E14" s="405">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="404">
+        <v>0.75</v>
+      </c>
+      <c r="G14" s="405">
+        <f t="shared" si="1"/>
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C15" s="405">
+        <v>1035</v>
+      </c>
+      <c r="D15" s="404">
+        <v>0</v>
+      </c>
+      <c r="E15" s="405">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="404">
+        <v>0</v>
+      </c>
+      <c r="G15" s="405">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="403" t="s">
+        <v>331</v>
+      </c>
+      <c r="C16" s="406">
+        <f>SUM(C7:C15)</f>
+        <v>107214</v>
+      </c>
+      <c r="D16" s="403"/>
+      <c r="E16" s="406">
+        <f>SUM(E7:E15)</f>
+        <v>45179.65</v>
+      </c>
+      <c r="F16" s="403"/>
+      <c r="G16" s="406">
+        <f>SUM(G7:G15)</f>
+        <v>61412.5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="402" t="s">
+        <v>335</v>
+      </c>
+      <c r="C18" s="407">
+        <f>-Model!$G$80</f>
+        <v>43900</v>
+      </c>
+      <c r="D18" s="407"/>
+      <c r="E18" s="407">
+        <f>-Model!$G$80</f>
+        <v>43900</v>
+      </c>
+      <c r="F18" s="407"/>
+      <c r="G18" s="407">
+        <f>-Model!$G$80</f>
+        <v>43900</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C19" s="408"/>
+      <c r="D19" s="408"/>
+      <c r="E19" s="408"/>
+      <c r="F19" s="408"/>
+      <c r="G19" s="408"/>
+    </row>
+    <row r="20" spans="2:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="402" t="s">
+        <v>321</v>
+      </c>
+      <c r="C20" s="407">
+        <f>C16-C18</f>
+        <v>63314</v>
+      </c>
+      <c r="D20" s="402"/>
+      <c r="E20" s="407">
+        <f>E16-E18</f>
+        <v>1279.6500000000015</v>
+      </c>
+      <c r="F20" s="402"/>
+      <c r="G20" s="407">
+        <f>G16-G18</f>
+        <v>17512.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="402" t="s">
+        <v>333</v>
+      </c>
+      <c r="C22" s="410">
+        <f>Model!D38</f>
+        <v>57080000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="402" t="s">
+        <v>334</v>
+      </c>
+      <c r="C24" s="409">
+        <f>(C20*1000)/$C$22</f>
+        <v>1.1092151366503153</v>
+      </c>
+      <c r="D24" s="409"/>
+      <c r="E24" s="409">
+        <f>(E20*1000)/$C$22</f>
+        <v>2.2418535388927845E-2</v>
+      </c>
+      <c r="F24" s="409"/>
+      <c r="G24" s="409">
+        <f>(G20*1000)/$C$22</f>
+        <v>0.30680623686054659</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>